--- a/CPRD Raw Analysis/Results/Output_costs_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_costs_Raw.xlsx
@@ -7,9 +7,10 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="overall_summary_costs_pa_df" sheetId="1" r:id="rId1"/>
-    <sheet name="user_only_cost_summary" sheetId="2" r:id="rId2"/>
-    <sheet name="all_cost_summary" sheetId="3" r:id="rId3"/>
+    <sheet name="user_cost_summary_statistics" sheetId="1" r:id="rId1"/>
+    <sheet name="all_cost_summary_statistics" sheetId="2" r:id="rId2"/>
+    <sheet name="user_only_cost_summary" sheetId="3" r:id="rId3"/>
+    <sheet name="all_cost_summary" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -353,79 +354,67 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Statistic</t>
+          <t>mean_visit_per_year</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>min_visit_per_year</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>max_visit_per_year</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sd_visit_per_year</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>median_visit_per_year</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>lower_q_visits_per_year</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>upper_q_visits_per_year</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Min.</t>
-        </is>
+      <c r="A2">
+        <v>550.0429584984093</v>
       </c>
       <c r="B2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1st Qu.</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Median</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>54.03698630136986</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Mean</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>278.9329502841351</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>3rd Qu.</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>410.0231106612686</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Max.</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>14022.79038461539</v>
+        <v>3.102123287671233</v>
+      </c>
+      <c r="C2">
+        <v>16654.69759615385</v>
+      </c>
+      <c r="D2">
+        <v>674.2</v>
+      </c>
+      <c r="E2">
+        <v>459.7</v>
+      </c>
+      <c r="F2">
+        <v>261.8</v>
+      </c>
+      <c r="G2">
+        <v>788.7</v>
       </c>
     </row>
   </sheetData>
@@ -435,1732 +424,67 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>specialty</t>
+          <t>mean_visit_per_year</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>tot_visits_costs</t>
+          <t>min_visit_per_year</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean_visits_per_year</t>
+          <t>max_visit_per_year</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>sd_cost_visits_per_year</t>
+          <t>sd_visit_per_year</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>min_cost_visits_per_year</t>
+          <t>median_visit_per_year</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>max_cost_visits_per_year</t>
+          <t>lower_q_visits_per_year</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>num_subjects_visited</t>
+          <t>upper_q_visits_per_year</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Advanced Practitioner</t>
-        </is>
+      <c r="A2">
+        <v>545.120679330498</v>
       </c>
       <c r="B2">
-        <v>13987.84846938776</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>50.62</v>
+        <v>16654.69759615385</v>
       </c>
       <c r="D2">
-        <v>68.14</v>
+        <v>673.3</v>
       </c>
       <c r="E2">
-        <v>13.38</v>
+        <v>450.3</v>
       </c>
       <c r="F2">
-        <v>449.1</v>
+        <v>252.2</v>
       </c>
       <c r="G2">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Art Therapist</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>8195</v>
-      </c>
-      <c r="C3">
-        <v>217.8</v>
-      </c>
-      <c r="D3">
-        <v>365.2</v>
-      </c>
-      <c r="E3">
-        <v>27.52</v>
-      </c>
-      <c r="F3">
-        <v>1435</v>
-      </c>
-      <c r="G3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Art Therapist Consultant</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>550</v>
-      </c>
-      <c r="C4">
-        <v>62.02</v>
-      </c>
-      <c r="D4">
-        <v>45.12</v>
-      </c>
-      <c r="E4">
-        <v>27.52</v>
-      </c>
-      <c r="F4">
-        <v>137.6</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Art Therapist Specialist Practitioner</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>880</v>
-      </c>
-      <c r="C5">
-        <v>73.38</v>
-      </c>
-      <c r="D5">
-        <v>41.43</v>
-      </c>
-      <c r="E5">
-        <v>27.52</v>
-      </c>
-      <c r="F5">
-        <v>137.6</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Associate Practitioner</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>12204.44166666667</v>
-      </c>
-      <c r="C6">
-        <v>41.45</v>
-      </c>
-      <c r="D6">
-        <v>53.31</v>
-      </c>
-      <c r="E6">
-        <v>15.38</v>
-      </c>
-      <c r="F6">
-        <v>337.4</v>
-      </c>
-      <c r="G6">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Associate Practitioner - General Practitioner</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>105012</v>
-      </c>
-      <c r="C7">
-        <v>99.45</v>
-      </c>
-      <c r="D7">
-        <v>201.1</v>
-      </c>
-      <c r="E7">
-        <v>18.01</v>
-      </c>
-      <c r="F7">
-        <v>2858</v>
-      </c>
-      <c r="G7">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Associate Practitioner - Nurse</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>61926.79230769232</v>
-      </c>
-      <c r="C8">
-        <v>39.45</v>
-      </c>
-      <c r="D8">
-        <v>68.97</v>
-      </c>
-      <c r="E8">
-        <v>9.605</v>
-      </c>
-      <c r="F8">
-        <v>779</v>
-      </c>
-      <c r="G8">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Associate Specialist</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>9283.983333333334</v>
-      </c>
-      <c r="C9">
-        <v>54.41</v>
-      </c>
-      <c r="D9">
-        <v>127</v>
-      </c>
-      <c r="E9">
-        <v>15.38</v>
-      </c>
-      <c r="F9">
-        <v>1064</v>
-      </c>
-      <c r="G9">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Asst. Clinical Medical Officer</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>36</v>
-      </c>
-      <c r="C10">
-        <v>18.01</v>
-      </c>
-      <c r="E10">
-        <v>18.01</v>
-      </c>
-      <c r="F10">
-        <v>18.01</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Audiologist</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>470.46</v>
-      </c>
-      <c r="C11">
-        <v>187.8</v>
-      </c>
-      <c r="D11">
-        <v>382.4</v>
-      </c>
-      <c r="E11">
-        <v>78.45999999999999</v>
-      </c>
-      <c r="F11">
-        <v>619.2</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Child Protection worker</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>1890</v>
-      </c>
-      <c r="C12">
-        <v>50.12</v>
-      </c>
-      <c r="D12">
-        <v>72.81999999999999</v>
-      </c>
-      <c r="E12">
-        <v>21.01</v>
-      </c>
-      <c r="F12">
-        <v>359.9</v>
-      </c>
-      <c r="G12">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Chiropodist/Podiatrist</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>5822</v>
-      </c>
-      <c r="C13">
-        <v>42.29</v>
-      </c>
-      <c r="D13">
-        <v>42.93</v>
-      </c>
-      <c r="E13">
-        <v>20.51</v>
-      </c>
-      <c r="F13">
-        <v>225.7</v>
-      </c>
-      <c r="G13">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Chiropodist/Podiatrist Consultant</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>165</v>
-      </c>
-      <c r="C14">
-        <v>36.61</v>
-      </c>
-      <c r="D14">
-        <v>46.47</v>
-      </c>
-      <c r="E14">
-        <v>27.52</v>
-      </c>
-      <c r="F14">
-        <v>108</v>
-      </c>
-      <c r="G14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Chiropodist/Podiatrist Specialist Practitioner</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>385</v>
-      </c>
-      <c r="C15">
-        <v>38.53</v>
-      </c>
-      <c r="D15">
-        <v>15.07</v>
-      </c>
-      <c r="E15">
-        <v>27.52</v>
-      </c>
-      <c r="F15">
-        <v>55.04</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Clinical Director</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>252</v>
-      </c>
-      <c r="C16">
-        <v>21.75</v>
-      </c>
-      <c r="D16">
-        <v>7.216</v>
-      </c>
-      <c r="E16">
-        <v>18.01</v>
-      </c>
-      <c r="F16">
-        <v>36.02</v>
-      </c>
-      <c r="G16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Clinical Director - Medical</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>5004</v>
-      </c>
-      <c r="C17">
-        <v>55.53</v>
-      </c>
-      <c r="D17">
-        <v>40.31</v>
-      </c>
-      <c r="E17">
-        <v>18.01</v>
-      </c>
-      <c r="F17">
-        <v>180.1</v>
-      </c>
-      <c r="G17">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Clinical Medical Officer</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>72</v>
-      </c>
-      <c r="C18">
-        <v>18.01</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>18.01</v>
-      </c>
-      <c r="F18">
-        <v>18.01</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Clinical Psychologist</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>1358.5</v>
-      </c>
-      <c r="C19">
-        <v>135.9</v>
-      </c>
-      <c r="D19">
-        <v>150.5</v>
-      </c>
-      <c r="E19">
-        <v>35.77</v>
-      </c>
-      <c r="F19">
-        <v>393.5</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Community Mental Health Nurse</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>3824.593367346939</v>
-      </c>
-      <c r="C20">
-        <v>44.04</v>
-      </c>
-      <c r="D20">
-        <v>56.51</v>
-      </c>
-      <c r="E20">
-        <v>13.38</v>
-      </c>
-      <c r="F20">
-        <v>267.6</v>
-      </c>
-      <c r="G20">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Community Nurse</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>413235.6038461539</v>
-      </c>
-      <c r="C21">
-        <v>47.16</v>
-      </c>
-      <c r="D21">
-        <v>101.9</v>
-      </c>
-      <c r="E21">
-        <v>9.605</v>
-      </c>
-      <c r="F21">
-        <v>3111</v>
-      </c>
-      <c r="G21">
-        <v>4812</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Community Practitioner</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>2135628</v>
-      </c>
-      <c r="C22">
-        <v>99.48</v>
-      </c>
-      <c r="D22">
-        <v>192.6</v>
-      </c>
-      <c r="E22">
-        <v>18.01</v>
-      </c>
-      <c r="F22">
-        <v>6712</v>
-      </c>
-      <c r="G22">
-        <v>11772</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Consultant</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>176891</v>
-      </c>
-      <c r="C23">
-        <v>187.4</v>
-      </c>
-      <c r="D23">
-        <v>419.6</v>
-      </c>
-      <c r="E23">
-        <v>35.77</v>
-      </c>
-      <c r="F23">
-        <v>4353</v>
-      </c>
-      <c r="G23">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Counsellor</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>7298</v>
-      </c>
-      <c r="C24">
-        <v>106</v>
-      </c>
-      <c r="D24">
-        <v>137.2</v>
-      </c>
-      <c r="E24">
-        <v>20.51</v>
-      </c>
-      <c r="F24">
-        <v>615.4</v>
-      </c>
-      <c r="G24">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Deputising Doctor</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>8928</v>
-      </c>
-      <c r="C25">
-        <v>120.5</v>
-      </c>
-      <c r="D25">
-        <v>304.2</v>
-      </c>
-      <c r="E25">
-        <v>18.01</v>
-      </c>
-      <c r="F25">
-        <v>1948</v>
-      </c>
-      <c r="G25">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Dietitian</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>4510</v>
-      </c>
-      <c r="C26">
-        <v>32.63</v>
-      </c>
-      <c r="D26">
-        <v>44.83</v>
-      </c>
-      <c r="E26">
-        <v>20.51</v>
-      </c>
-      <c r="F26">
-        <v>315.3</v>
-      </c>
-      <c r="G26">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Dietitian Consultant</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>50</v>
-      </c>
-      <c r="C27">
-        <v>25.02</v>
-      </c>
-      <c r="E27">
-        <v>25.02</v>
-      </c>
-      <c r="F27">
-        <v>25.02</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Dietitian Specialist Practitioner</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>41</v>
-      </c>
-      <c r="C28">
-        <v>20.51</v>
-      </c>
-      <c r="E28">
-        <v>20.51</v>
-      </c>
-      <c r="F28">
-        <v>20.51</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Enrolled Nurse</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>43421.7</v>
-      </c>
-      <c r="C29">
-        <v>40.67</v>
-      </c>
-      <c r="D29">
-        <v>53.03</v>
-      </c>
-      <c r="E29">
-        <v>9.605</v>
-      </c>
-      <c r="F29">
-        <v>374.6</v>
-      </c>
-      <c r="G29">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>GP Registrar</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>602532</v>
-      </c>
-      <c r="C30">
-        <v>60.36</v>
-      </c>
-      <c r="D30">
-        <v>160.4</v>
-      </c>
-      <c r="E30">
-        <v>18.01</v>
-      </c>
-      <c r="F30">
-        <v>5260</v>
-      </c>
-      <c r="G30">
-        <v>5512</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>General Medical Practitioner</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>15066072</v>
-      </c>
-      <c r="C31">
-        <v>364.6</v>
-      </c>
-      <c r="D31">
-        <v>494.3</v>
-      </c>
-      <c r="E31">
-        <v>18.01</v>
-      </c>
-      <c r="F31">
-        <v>13150</v>
-      </c>
-      <c r="G31">
-        <v>23947</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Health Care Support Worker</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>930917.4807692309</v>
-      </c>
-      <c r="C32">
-        <v>90.61</v>
-      </c>
-      <c r="D32">
-        <v>286</v>
-      </c>
-      <c r="E32">
-        <v>9.605</v>
-      </c>
-      <c r="F32">
-        <v>14020</v>
-      </c>
-      <c r="G32">
-        <v>5894</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Hospital Practitioner</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>774</v>
-      </c>
-      <c r="C33">
-        <v>83</v>
-      </c>
-      <c r="D33">
-        <v>97.09</v>
-      </c>
-      <c r="E33">
-        <v>21.51</v>
-      </c>
-      <c r="F33">
-        <v>258.5</v>
-      </c>
-      <c r="G33">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Locum GP</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>255816</v>
-      </c>
-      <c r="C34">
-        <v>74.47</v>
-      </c>
-      <c r="D34">
-        <v>214.8</v>
-      </c>
-      <c r="E34">
-        <v>18.01</v>
-      </c>
-      <c r="F34">
-        <v>4931</v>
-      </c>
-      <c r="G34">
-        <v>1851</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Medical Technical Officer</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>576.6</v>
-      </c>
-      <c r="C35">
-        <v>6.752</v>
-      </c>
-      <c r="D35">
-        <v>9.329000000000001</v>
-      </c>
-      <c r="E35">
-        <v>3.102</v>
-      </c>
-      <c r="F35">
-        <v>55.23</v>
-      </c>
-      <c r="G35">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Medical Technical Officer - Pharmacy</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>8382.4</v>
-      </c>
-      <c r="C36">
-        <v>11.72</v>
-      </c>
-      <c r="D36">
-        <v>19.95</v>
-      </c>
-      <c r="E36">
-        <v>3.102</v>
-      </c>
-      <c r="F36">
-        <v>174.2</v>
-      </c>
-      <c r="G36">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Midwife</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>215.1916666666667</v>
-      </c>
-      <c r="C37">
-        <v>17.94</v>
-      </c>
-      <c r="D37">
-        <v>6.279</v>
-      </c>
-      <c r="E37">
-        <v>15.38</v>
-      </c>
-      <c r="F37">
-        <v>30.76</v>
-      </c>
-      <c r="G37">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Modern Matron</t>
-        </is>
-      </c>
-      <c r="B38">
-        <v>6793.908333333334</v>
-      </c>
-      <c r="C38">
-        <v>88.98999999999999</v>
-      </c>
-      <c r="D38">
-        <v>188</v>
-      </c>
-      <c r="E38">
-        <v>15.38</v>
-      </c>
-      <c r="F38">
-        <v>990.7</v>
-      </c>
-      <c r="G38">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Multi Therapist Specialist Practitioner</t>
-        </is>
-      </c>
-      <c r="B39">
-        <v>110</v>
-      </c>
-      <c r="C39">
-        <v>55.04</v>
-      </c>
-      <c r="E39">
-        <v>55.04</v>
-      </c>
-      <c r="F39">
-        <v>55.04</v>
-      </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Nurse Consultant</t>
-        </is>
-      </c>
-      <c r="B40">
-        <v>95503</v>
-      </c>
-      <c r="C40">
-        <v>85.98999999999999</v>
-      </c>
-      <c r="D40">
-        <v>132.8</v>
-      </c>
-      <c r="E40">
-        <v>21.51</v>
-      </c>
-      <c r="F40">
-        <v>1463</v>
-      </c>
-      <c r="G40">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Occupational Therapist</t>
-        </is>
-      </c>
-      <c r="B41">
-        <v>164</v>
-      </c>
-      <c r="C41">
-        <v>30.45</v>
-      </c>
-      <c r="D41">
-        <v>22.26</v>
-      </c>
-      <c r="E41">
-        <v>20.51</v>
-      </c>
-      <c r="F41">
-        <v>59.07</v>
-      </c>
-      <c r="G41">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Optometrist</t>
-        </is>
-      </c>
-      <c r="B42">
-        <v>321.78</v>
-      </c>
-      <c r="C42">
-        <v>53.67</v>
-      </c>
-      <c r="D42">
-        <v>0</v>
-      </c>
-      <c r="E42">
-        <v>53.67</v>
-      </c>
-      <c r="F42">
-        <v>53.67</v>
-      </c>
-      <c r="G42">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Osteopath</t>
-        </is>
-      </c>
-      <c r="B43">
-        <v>7425</v>
-      </c>
-      <c r="C43">
-        <v>406.7</v>
-      </c>
-      <c r="D43">
-        <v>1113</v>
-      </c>
-      <c r="E43">
-        <v>192.6</v>
-      </c>
-      <c r="F43">
-        <v>4109</v>
-      </c>
-      <c r="G43">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Other Community Health Service</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>14878.96666666667</v>
-      </c>
-      <c r="C44">
-        <v>59.45</v>
-      </c>
-      <c r="D44">
-        <v>90.67</v>
-      </c>
-      <c r="E44">
-        <v>15.38</v>
-      </c>
-      <c r="F44">
-        <v>606.4</v>
-      </c>
-      <c r="G44">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Other Community Health Service - Social Care Worker</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>210</v>
-      </c>
-      <c r="C45">
-        <v>110.2</v>
-      </c>
-      <c r="D45">
-        <v>11.65</v>
-      </c>
-      <c r="E45">
-        <v>100.9</v>
-      </c>
-      <c r="F45">
-        <v>117.4</v>
-      </c>
-      <c r="G45">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Paramedic</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>11546</v>
-      </c>
-      <c r="C46">
-        <v>31.5</v>
-      </c>
-      <c r="D46">
-        <v>55.55</v>
-      </c>
-      <c r="E46">
-        <v>11.51</v>
-      </c>
-      <c r="F46">
-        <v>466.7</v>
-      </c>
-      <c r="G46">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Paramedic Consultant</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>347.75</v>
-      </c>
-      <c r="C47">
-        <v>26.46</v>
-      </c>
-      <c r="D47">
-        <v>30.93</v>
-      </c>
-      <c r="E47">
-        <v>13.38</v>
-      </c>
-      <c r="F47">
-        <v>84.95999999999999</v>
-      </c>
-      <c r="G47">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Paramedic Specialist Practitioner</t>
-        </is>
-      </c>
-      <c r="B48">
-        <v>15390</v>
-      </c>
-      <c r="C48">
-        <v>37.63</v>
-      </c>
-      <c r="D48">
-        <v>63.56</v>
-      </c>
-      <c r="E48">
-        <v>14.26</v>
-      </c>
-      <c r="F48">
-        <v>369.1</v>
-      </c>
-      <c r="G48">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Patient Welfare Officer</t>
-        </is>
-      </c>
-      <c r="B49">
-        <v>210</v>
-      </c>
-      <c r="C49">
-        <v>30.01</v>
-      </c>
-      <c r="D49">
-        <v>12.1</v>
-      </c>
-      <c r="E49">
-        <v>21.01</v>
-      </c>
-      <c r="F49">
-        <v>42.03</v>
-      </c>
-      <c r="G49">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Physiotherapist</t>
-        </is>
-      </c>
-      <c r="B50">
-        <v>32472</v>
-      </c>
-      <c r="C50">
-        <v>62.66</v>
-      </c>
-      <c r="D50">
-        <v>61.85</v>
-      </c>
-      <c r="E50">
-        <v>20.51</v>
-      </c>
-      <c r="F50">
-        <v>348.7</v>
-      </c>
-      <c r="G50">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Physiotherapist Consultant</t>
-        </is>
-      </c>
-      <c r="B51">
-        <v>1644.5</v>
-      </c>
-      <c r="C51">
-        <v>58.1</v>
-      </c>
-      <c r="D51">
-        <v>25.24</v>
-      </c>
-      <c r="E51">
-        <v>35.77</v>
-      </c>
-      <c r="F51">
-        <v>107.3</v>
-      </c>
-      <c r="G51">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Physiotherapist Specialist Practitioner</t>
-        </is>
-      </c>
-      <c r="B52">
-        <v>3245</v>
-      </c>
-      <c r="C52">
-        <v>52.5</v>
-      </c>
-      <c r="D52">
-        <v>30.81</v>
-      </c>
-      <c r="E52">
-        <v>27.52</v>
-      </c>
-      <c r="F52">
-        <v>137.6</v>
-      </c>
-      <c r="G52">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Practitioner</t>
-        </is>
-      </c>
-      <c r="B53">
-        <v>10002.78265306123</v>
-      </c>
-      <c r="C53">
-        <v>43.62</v>
-      </c>
-      <c r="D53">
-        <v>54.14</v>
-      </c>
-      <c r="E53">
-        <v>13.38</v>
-      </c>
-      <c r="F53">
-        <v>375.7</v>
-      </c>
-      <c r="G53">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Pre-reg Pharmacist</t>
-        </is>
-      </c>
-      <c r="B54">
-        <v>31</v>
-      </c>
-      <c r="C54">
-        <v>4.355</v>
-      </c>
-      <c r="D54">
-        <v>1.618</v>
-      </c>
-      <c r="E54">
-        <v>3.102</v>
-      </c>
-      <c r="F54">
-        <v>6.204</v>
-      </c>
-      <c r="G54">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Psychotherapist</t>
-        </is>
-      </c>
-      <c r="B55">
-        <v>715</v>
-      </c>
-      <c r="C55">
-        <v>89.44</v>
-      </c>
-      <c r="D55">
-        <v>68.5</v>
-      </c>
-      <c r="E55">
-        <v>35.77</v>
-      </c>
-      <c r="F55">
-        <v>178.9</v>
-      </c>
-      <c r="G55">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Radiologist</t>
-        </is>
-      </c>
-      <c r="B56">
-        <v>770.5</v>
-      </c>
-      <c r="C56">
-        <v>17.88</v>
-      </c>
-      <c r="D56">
-        <v>18.9</v>
-      </c>
-      <c r="E56">
-        <v>5.754</v>
-      </c>
-      <c r="F56">
-        <v>79.25</v>
-      </c>
-      <c r="G56">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Regional Dental Officer</t>
-        </is>
-      </c>
-      <c r="B57">
-        <v>3432</v>
-      </c>
-      <c r="C57">
-        <v>446.6</v>
-      </c>
-      <c r="D57">
-        <v>441.7</v>
-      </c>
-      <c r="E57">
-        <v>61.57</v>
-      </c>
-      <c r="F57">
-        <v>1041</v>
-      </c>
-      <c r="G57">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Salaried General Practitioner</t>
-        </is>
-      </c>
-      <c r="B58">
-        <v>1414584</v>
-      </c>
-      <c r="C58">
-        <v>128.4</v>
-      </c>
-      <c r="D58">
-        <v>273.1</v>
-      </c>
-      <c r="E58">
-        <v>18.01</v>
-      </c>
-      <c r="F58">
-        <v>7889</v>
-      </c>
-      <c r="G58">
-        <v>6131</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Senior House Officer</t>
-        </is>
-      </c>
-      <c r="B59">
-        <v>1620</v>
-      </c>
-      <c r="C59">
-        <v>68.34999999999999</v>
-      </c>
-      <c r="D59">
-        <v>80.79000000000001</v>
-      </c>
-      <c r="E59">
-        <v>18.01</v>
-      </c>
-      <c r="F59">
-        <v>328.7</v>
-      </c>
-      <c r="G59">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Sessional GP</t>
-        </is>
-      </c>
-      <c r="B60">
-        <v>605268</v>
-      </c>
-      <c r="C60">
-        <v>78.52</v>
-      </c>
-      <c r="D60">
-        <v>161.4</v>
-      </c>
-      <c r="E60">
-        <v>18.01</v>
-      </c>
-      <c r="F60">
-        <v>2922</v>
-      </c>
-      <c r="G60">
-        <v>4254</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Sister/Charge Nurse</t>
-        </is>
-      </c>
-      <c r="B61">
-        <v>164561</v>
-      </c>
-      <c r="C61">
-        <v>97.11</v>
-      </c>
-      <c r="D61">
-        <v>164.1</v>
-      </c>
-      <c r="E61">
-        <v>21.51</v>
-      </c>
-      <c r="F61">
-        <v>2111</v>
-      </c>
-      <c r="G61">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Social Care Support Worker</t>
-        </is>
-      </c>
-      <c r="B62">
-        <v>630</v>
-      </c>
-      <c r="C62">
-        <v>105.1</v>
-      </c>
-      <c r="D62">
-        <v>96.3</v>
-      </c>
-      <c r="E62">
-        <v>21.01</v>
-      </c>
-      <c r="F62">
-        <v>210.1</v>
-      </c>
-      <c r="G62">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Social Worker</t>
-        </is>
-      </c>
-      <c r="B63">
-        <v>798</v>
-      </c>
-      <c r="C63">
-        <v>99.98999999999999</v>
-      </c>
-      <c r="D63">
-        <v>48.69</v>
-      </c>
-      <c r="E63">
-        <v>63.04</v>
-      </c>
-      <c r="F63">
-        <v>183</v>
-      </c>
-      <c r="G63">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Specialist Nurse Practitioner</t>
-        </is>
-      </c>
-      <c r="B64">
-        <v>483637.2158163266</v>
-      </c>
-      <c r="C64">
-        <v>57.7</v>
-      </c>
-      <c r="D64">
-        <v>104.1</v>
-      </c>
-      <c r="E64">
-        <v>13.38</v>
-      </c>
-      <c r="F64">
-        <v>2442</v>
-      </c>
-      <c r="G64">
-        <v>4566</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Specialist Practitioner</t>
-        </is>
-      </c>
-      <c r="B65">
-        <v>5379.791666666667</v>
-      </c>
-      <c r="C65">
-        <v>53.42</v>
-      </c>
-      <c r="D65">
-        <v>50.45</v>
-      </c>
-      <c r="E65">
-        <v>15.38</v>
-      </c>
-      <c r="F65">
-        <v>236.4</v>
-      </c>
-      <c r="G65">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Specialist Registrar</t>
-        </is>
-      </c>
-      <c r="B66">
-        <v>144</v>
-      </c>
-      <c r="C66">
-        <v>25.18</v>
-      </c>
-      <c r="D66">
-        <v>9.673</v>
-      </c>
-      <c r="E66">
-        <v>18.01</v>
-      </c>
-      <c r="F66">
-        <v>36.02</v>
-      </c>
-      <c r="G66">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Staff Nurse</t>
-        </is>
-      </c>
-      <c r="B67">
-        <v>432709</v>
-      </c>
-      <c r="C67">
-        <v>98.33</v>
-      </c>
-      <c r="D67">
-        <v>210.5</v>
-      </c>
-      <c r="E67">
-        <v>21.51</v>
-      </c>
-      <c r="F67">
-        <v>6282</v>
-      </c>
-      <c r="G67">
-        <v>2373</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Therapist</t>
-        </is>
-      </c>
-      <c r="B68">
-        <v>3355</v>
-      </c>
-      <c r="C68">
-        <v>156.2</v>
-      </c>
-      <c r="D68">
-        <v>283.9</v>
-      </c>
-      <c r="E68">
-        <v>27.52</v>
-      </c>
-      <c r="F68">
-        <v>1071</v>
-      </c>
-      <c r="G68">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Trainee Practitioner</t>
-        </is>
-      </c>
-      <c r="B69">
-        <v>998.2</v>
-      </c>
-      <c r="C69">
-        <v>18.52</v>
-      </c>
-      <c r="D69">
-        <v>24.46</v>
-      </c>
-      <c r="E69">
-        <v>9.605</v>
-      </c>
-      <c r="F69">
-        <v>109.9</v>
-      </c>
-      <c r="G69">
-        <v>28</v>
+        <v>774.5</v>
       </c>
     </row>
   </sheetData>
@@ -2170,6 +494,1741 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G69"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>specialty</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>tot_visits_costs</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>mean_visits_per_year</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sd_cost_visits_per_year</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>min_cost_visits_per_year</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>max_cost_visits_per_year</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>num_subjects_visited</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Advanced Practitioner</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>13987.84846938776</v>
+      </c>
+      <c r="C2">
+        <v>50.62</v>
+      </c>
+      <c r="D2">
+        <v>68.14</v>
+      </c>
+      <c r="E2">
+        <v>13.38</v>
+      </c>
+      <c r="F2">
+        <v>449.1</v>
+      </c>
+      <c r="G2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Art Therapist</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>8195</v>
+      </c>
+      <c r="C3">
+        <v>217.8</v>
+      </c>
+      <c r="D3">
+        <v>365.2</v>
+      </c>
+      <c r="E3">
+        <v>27.52</v>
+      </c>
+      <c r="F3">
+        <v>1435</v>
+      </c>
+      <c r="G3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Art Therapist Consultant</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>550</v>
+      </c>
+      <c r="C4">
+        <v>62.02</v>
+      </c>
+      <c r="D4">
+        <v>45.12</v>
+      </c>
+      <c r="E4">
+        <v>27.52</v>
+      </c>
+      <c r="F4">
+        <v>137.6</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Art Therapist Specialist Practitioner</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>880</v>
+      </c>
+      <c r="C5">
+        <v>73.38</v>
+      </c>
+      <c r="D5">
+        <v>41.43</v>
+      </c>
+      <c r="E5">
+        <v>27.52</v>
+      </c>
+      <c r="F5">
+        <v>137.6</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Associate Practitioner</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>12204.44166666667</v>
+      </c>
+      <c r="C6">
+        <v>41.45</v>
+      </c>
+      <c r="D6">
+        <v>53.31</v>
+      </c>
+      <c r="E6">
+        <v>15.38</v>
+      </c>
+      <c r="F6">
+        <v>337.4</v>
+      </c>
+      <c r="G6">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Associate Practitioner - General Practitioner</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>105012</v>
+      </c>
+      <c r="C7">
+        <v>99.45</v>
+      </c>
+      <c r="D7">
+        <v>201.1</v>
+      </c>
+      <c r="E7">
+        <v>18.01</v>
+      </c>
+      <c r="F7">
+        <v>2858</v>
+      </c>
+      <c r="G7">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Associate Practitioner - Nurse</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>61926.79230769232</v>
+      </c>
+      <c r="C8">
+        <v>39.45</v>
+      </c>
+      <c r="D8">
+        <v>68.97</v>
+      </c>
+      <c r="E8">
+        <v>9.605</v>
+      </c>
+      <c r="F8">
+        <v>779</v>
+      </c>
+      <c r="G8">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Associate Specialist</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>9283.983333333334</v>
+      </c>
+      <c r="C9">
+        <v>54.41</v>
+      </c>
+      <c r="D9">
+        <v>127</v>
+      </c>
+      <c r="E9">
+        <v>15.38</v>
+      </c>
+      <c r="F9">
+        <v>1064</v>
+      </c>
+      <c r="G9">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Asst. Clinical Medical Officer</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>36</v>
+      </c>
+      <c r="C10">
+        <v>18.01</v>
+      </c>
+      <c r="E10">
+        <v>18.01</v>
+      </c>
+      <c r="F10">
+        <v>18.01</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Audiologist</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>470.46</v>
+      </c>
+      <c r="C11">
+        <v>187.8</v>
+      </c>
+      <c r="D11">
+        <v>382.4</v>
+      </c>
+      <c r="E11">
+        <v>78.45999999999999</v>
+      </c>
+      <c r="F11">
+        <v>619.2</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Child Protection worker</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>1890</v>
+      </c>
+      <c r="C12">
+        <v>50.12</v>
+      </c>
+      <c r="D12">
+        <v>72.81999999999999</v>
+      </c>
+      <c r="E12">
+        <v>21.01</v>
+      </c>
+      <c r="F12">
+        <v>359.9</v>
+      </c>
+      <c r="G12">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiropodist/Podiatrist</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>5822</v>
+      </c>
+      <c r="C13">
+        <v>42.29</v>
+      </c>
+      <c r="D13">
+        <v>42.93</v>
+      </c>
+      <c r="E13">
+        <v>20.51</v>
+      </c>
+      <c r="F13">
+        <v>225.7</v>
+      </c>
+      <c r="G13">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiropodist/Podiatrist Consultant</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>165</v>
+      </c>
+      <c r="C14">
+        <v>36.61</v>
+      </c>
+      <c r="D14">
+        <v>46.47</v>
+      </c>
+      <c r="E14">
+        <v>27.52</v>
+      </c>
+      <c r="F14">
+        <v>108</v>
+      </c>
+      <c r="G14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiropodist/Podiatrist Specialist Practitioner</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>385</v>
+      </c>
+      <c r="C15">
+        <v>38.53</v>
+      </c>
+      <c r="D15">
+        <v>15.07</v>
+      </c>
+      <c r="E15">
+        <v>27.52</v>
+      </c>
+      <c r="F15">
+        <v>55.04</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Clinical Director</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>252</v>
+      </c>
+      <c r="C16">
+        <v>21.75</v>
+      </c>
+      <c r="D16">
+        <v>7.216</v>
+      </c>
+      <c r="E16">
+        <v>18.01</v>
+      </c>
+      <c r="F16">
+        <v>36.02</v>
+      </c>
+      <c r="G16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Clinical Director - Medical</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>5004</v>
+      </c>
+      <c r="C17">
+        <v>55.53</v>
+      </c>
+      <c r="D17">
+        <v>40.31</v>
+      </c>
+      <c r="E17">
+        <v>18.01</v>
+      </c>
+      <c r="F17">
+        <v>180.1</v>
+      </c>
+      <c r="G17">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Clinical Medical Officer</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>72</v>
+      </c>
+      <c r="C18">
+        <v>18.01</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>18.01</v>
+      </c>
+      <c r="F18">
+        <v>18.01</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Clinical Psychologist</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>1358.5</v>
+      </c>
+      <c r="C19">
+        <v>135.9</v>
+      </c>
+      <c r="D19">
+        <v>150.5</v>
+      </c>
+      <c r="E19">
+        <v>35.77</v>
+      </c>
+      <c r="F19">
+        <v>393.5</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Community Mental Health Nurse</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>3824.593367346939</v>
+      </c>
+      <c r="C20">
+        <v>44.04</v>
+      </c>
+      <c r="D20">
+        <v>56.51</v>
+      </c>
+      <c r="E20">
+        <v>13.38</v>
+      </c>
+      <c r="F20">
+        <v>267.6</v>
+      </c>
+      <c r="G20">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Community Nurse</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>413235.6038461539</v>
+      </c>
+      <c r="C21">
+        <v>47.16</v>
+      </c>
+      <c r="D21">
+        <v>101.9</v>
+      </c>
+      <c r="E21">
+        <v>9.605</v>
+      </c>
+      <c r="F21">
+        <v>3111</v>
+      </c>
+      <c r="G21">
+        <v>4812</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Community Practitioner</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>2135628</v>
+      </c>
+      <c r="C22">
+        <v>99.48</v>
+      </c>
+      <c r="D22">
+        <v>192.6</v>
+      </c>
+      <c r="E22">
+        <v>18.01</v>
+      </c>
+      <c r="F22">
+        <v>6712</v>
+      </c>
+      <c r="G22">
+        <v>11772</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Consultant</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>176891</v>
+      </c>
+      <c r="C23">
+        <v>187.4</v>
+      </c>
+      <c r="D23">
+        <v>419.6</v>
+      </c>
+      <c r="E23">
+        <v>35.77</v>
+      </c>
+      <c r="F23">
+        <v>4353</v>
+      </c>
+      <c r="G23">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Counsellor</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>7298</v>
+      </c>
+      <c r="C24">
+        <v>106</v>
+      </c>
+      <c r="D24">
+        <v>137.2</v>
+      </c>
+      <c r="E24">
+        <v>20.51</v>
+      </c>
+      <c r="F24">
+        <v>615.4</v>
+      </c>
+      <c r="G24">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Deputising Doctor</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>8928</v>
+      </c>
+      <c r="C25">
+        <v>120.5</v>
+      </c>
+      <c r="D25">
+        <v>304.2</v>
+      </c>
+      <c r="E25">
+        <v>18.01</v>
+      </c>
+      <c r="F25">
+        <v>1948</v>
+      </c>
+      <c r="G25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Dietitian</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>4510</v>
+      </c>
+      <c r="C26">
+        <v>32.63</v>
+      </c>
+      <c r="D26">
+        <v>44.83</v>
+      </c>
+      <c r="E26">
+        <v>20.51</v>
+      </c>
+      <c r="F26">
+        <v>315.3</v>
+      </c>
+      <c r="G26">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Dietitian Consultant</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>50</v>
+      </c>
+      <c r="C27">
+        <v>25.02</v>
+      </c>
+      <c r="E27">
+        <v>25.02</v>
+      </c>
+      <c r="F27">
+        <v>25.02</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Dietitian Specialist Practitioner</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>41</v>
+      </c>
+      <c r="C28">
+        <v>20.51</v>
+      </c>
+      <c r="E28">
+        <v>20.51</v>
+      </c>
+      <c r="F28">
+        <v>20.51</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Enrolled Nurse</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>43421.7</v>
+      </c>
+      <c r="C29">
+        <v>40.67</v>
+      </c>
+      <c r="D29">
+        <v>53.03</v>
+      </c>
+      <c r="E29">
+        <v>9.605</v>
+      </c>
+      <c r="F29">
+        <v>374.6</v>
+      </c>
+      <c r="G29">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>GP Registrar</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>602532</v>
+      </c>
+      <c r="C30">
+        <v>60.36</v>
+      </c>
+      <c r="D30">
+        <v>160.4</v>
+      </c>
+      <c r="E30">
+        <v>18.01</v>
+      </c>
+      <c r="F30">
+        <v>5260</v>
+      </c>
+      <c r="G30">
+        <v>5512</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>General Medical Practitioner</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>15066072</v>
+      </c>
+      <c r="C31">
+        <v>364.6</v>
+      </c>
+      <c r="D31">
+        <v>494.3</v>
+      </c>
+      <c r="E31">
+        <v>18.01</v>
+      </c>
+      <c r="F31">
+        <v>13150</v>
+      </c>
+      <c r="G31">
+        <v>23947</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Health Care Support Worker</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>930917.4807692309</v>
+      </c>
+      <c r="C32">
+        <v>90.61</v>
+      </c>
+      <c r="D32">
+        <v>286</v>
+      </c>
+      <c r="E32">
+        <v>9.605</v>
+      </c>
+      <c r="F32">
+        <v>14020</v>
+      </c>
+      <c r="G32">
+        <v>5894</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Hospital Practitioner</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>774</v>
+      </c>
+      <c r="C33">
+        <v>83</v>
+      </c>
+      <c r="D33">
+        <v>97.09</v>
+      </c>
+      <c r="E33">
+        <v>21.51</v>
+      </c>
+      <c r="F33">
+        <v>258.5</v>
+      </c>
+      <c r="G33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Locum GP</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>255816</v>
+      </c>
+      <c r="C34">
+        <v>74.47</v>
+      </c>
+      <c r="D34">
+        <v>214.8</v>
+      </c>
+      <c r="E34">
+        <v>18.01</v>
+      </c>
+      <c r="F34">
+        <v>4931</v>
+      </c>
+      <c r="G34">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Medical Technical Officer</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>576.6</v>
+      </c>
+      <c r="C35">
+        <v>6.752</v>
+      </c>
+      <c r="D35">
+        <v>9.329000000000001</v>
+      </c>
+      <c r="E35">
+        <v>3.102</v>
+      </c>
+      <c r="F35">
+        <v>55.23</v>
+      </c>
+      <c r="G35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Medical Technical Officer - Pharmacy</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>8382.4</v>
+      </c>
+      <c r="C36">
+        <v>11.72</v>
+      </c>
+      <c r="D36">
+        <v>19.95</v>
+      </c>
+      <c r="E36">
+        <v>3.102</v>
+      </c>
+      <c r="F36">
+        <v>174.2</v>
+      </c>
+      <c r="G36">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Midwife</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>215.1916666666667</v>
+      </c>
+      <c r="C37">
+        <v>17.94</v>
+      </c>
+      <c r="D37">
+        <v>6.279</v>
+      </c>
+      <c r="E37">
+        <v>15.38</v>
+      </c>
+      <c r="F37">
+        <v>30.76</v>
+      </c>
+      <c r="G37">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Modern Matron</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>6793.908333333334</v>
+      </c>
+      <c r="C38">
+        <v>88.98999999999999</v>
+      </c>
+      <c r="D38">
+        <v>188</v>
+      </c>
+      <c r="E38">
+        <v>15.38</v>
+      </c>
+      <c r="F38">
+        <v>990.7</v>
+      </c>
+      <c r="G38">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Multi Therapist Specialist Practitioner</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>110</v>
+      </c>
+      <c r="C39">
+        <v>55.04</v>
+      </c>
+      <c r="E39">
+        <v>55.04</v>
+      </c>
+      <c r="F39">
+        <v>55.04</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Nurse Consultant</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>95503</v>
+      </c>
+      <c r="C40">
+        <v>85.98999999999999</v>
+      </c>
+      <c r="D40">
+        <v>132.8</v>
+      </c>
+      <c r="E40">
+        <v>21.51</v>
+      </c>
+      <c r="F40">
+        <v>1463</v>
+      </c>
+      <c r="G40">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Occupational Therapist</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>164</v>
+      </c>
+      <c r="C41">
+        <v>30.45</v>
+      </c>
+      <c r="D41">
+        <v>22.26</v>
+      </c>
+      <c r="E41">
+        <v>20.51</v>
+      </c>
+      <c r="F41">
+        <v>59.07</v>
+      </c>
+      <c r="G41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Optometrist</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>321.78</v>
+      </c>
+      <c r="C42">
+        <v>53.67</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>53.67</v>
+      </c>
+      <c r="F42">
+        <v>53.67</v>
+      </c>
+      <c r="G42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Osteopath</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>7425</v>
+      </c>
+      <c r="C43">
+        <v>406.7</v>
+      </c>
+      <c r="D43">
+        <v>1113</v>
+      </c>
+      <c r="E43">
+        <v>192.6</v>
+      </c>
+      <c r="F43">
+        <v>4109</v>
+      </c>
+      <c r="G43">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Other Community Health Service</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>14878.96666666667</v>
+      </c>
+      <c r="C44">
+        <v>59.45</v>
+      </c>
+      <c r="D44">
+        <v>90.67</v>
+      </c>
+      <c r="E44">
+        <v>15.38</v>
+      </c>
+      <c r="F44">
+        <v>606.4</v>
+      </c>
+      <c r="G44">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Other Community Health Service - Social Care Worker</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>210</v>
+      </c>
+      <c r="C45">
+        <v>110.2</v>
+      </c>
+      <c r="D45">
+        <v>11.65</v>
+      </c>
+      <c r="E45">
+        <v>100.9</v>
+      </c>
+      <c r="F45">
+        <v>117.4</v>
+      </c>
+      <c r="G45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Paramedic</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>11546</v>
+      </c>
+      <c r="C46">
+        <v>31.5</v>
+      </c>
+      <c r="D46">
+        <v>55.55</v>
+      </c>
+      <c r="E46">
+        <v>11.51</v>
+      </c>
+      <c r="F46">
+        <v>466.7</v>
+      </c>
+      <c r="G46">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Paramedic Consultant</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>347.75</v>
+      </c>
+      <c r="C47">
+        <v>26.46</v>
+      </c>
+      <c r="D47">
+        <v>30.93</v>
+      </c>
+      <c r="E47">
+        <v>13.38</v>
+      </c>
+      <c r="F47">
+        <v>84.95999999999999</v>
+      </c>
+      <c r="G47">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Paramedic Specialist Practitioner</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>15390</v>
+      </c>
+      <c r="C48">
+        <v>37.63</v>
+      </c>
+      <c r="D48">
+        <v>63.56</v>
+      </c>
+      <c r="E48">
+        <v>14.26</v>
+      </c>
+      <c r="F48">
+        <v>369.1</v>
+      </c>
+      <c r="G48">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Patient Welfare Officer</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>210</v>
+      </c>
+      <c r="C49">
+        <v>30.01</v>
+      </c>
+      <c r="D49">
+        <v>12.1</v>
+      </c>
+      <c r="E49">
+        <v>21.01</v>
+      </c>
+      <c r="F49">
+        <v>42.03</v>
+      </c>
+      <c r="G49">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Physiotherapist</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>32472</v>
+      </c>
+      <c r="C50">
+        <v>62.66</v>
+      </c>
+      <c r="D50">
+        <v>61.85</v>
+      </c>
+      <c r="E50">
+        <v>20.51</v>
+      </c>
+      <c r="F50">
+        <v>348.7</v>
+      </c>
+      <c r="G50">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Physiotherapist Consultant</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>1644.5</v>
+      </c>
+      <c r="C51">
+        <v>58.1</v>
+      </c>
+      <c r="D51">
+        <v>25.24</v>
+      </c>
+      <c r="E51">
+        <v>35.77</v>
+      </c>
+      <c r="F51">
+        <v>107.3</v>
+      </c>
+      <c r="G51">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Physiotherapist Specialist Practitioner</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>3245</v>
+      </c>
+      <c r="C52">
+        <v>52.5</v>
+      </c>
+      <c r="D52">
+        <v>30.81</v>
+      </c>
+      <c r="E52">
+        <v>27.52</v>
+      </c>
+      <c r="F52">
+        <v>137.6</v>
+      </c>
+      <c r="G52">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Practitioner</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>10002.78265306123</v>
+      </c>
+      <c r="C53">
+        <v>43.62</v>
+      </c>
+      <c r="D53">
+        <v>54.14</v>
+      </c>
+      <c r="E53">
+        <v>13.38</v>
+      </c>
+      <c r="F53">
+        <v>375.7</v>
+      </c>
+      <c r="G53">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Pre-reg Pharmacist</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>31</v>
+      </c>
+      <c r="C54">
+        <v>4.355</v>
+      </c>
+      <c r="D54">
+        <v>1.618</v>
+      </c>
+      <c r="E54">
+        <v>3.102</v>
+      </c>
+      <c r="F54">
+        <v>6.204</v>
+      </c>
+      <c r="G54">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Psychotherapist</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>715</v>
+      </c>
+      <c r="C55">
+        <v>89.44</v>
+      </c>
+      <c r="D55">
+        <v>68.5</v>
+      </c>
+      <c r="E55">
+        <v>35.77</v>
+      </c>
+      <c r="F55">
+        <v>178.9</v>
+      </c>
+      <c r="G55">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Radiologist</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>770.5</v>
+      </c>
+      <c r="C56">
+        <v>17.88</v>
+      </c>
+      <c r="D56">
+        <v>18.9</v>
+      </c>
+      <c r="E56">
+        <v>5.754</v>
+      </c>
+      <c r="F56">
+        <v>79.25</v>
+      </c>
+      <c r="G56">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Regional Dental Officer</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>3432</v>
+      </c>
+      <c r="C57">
+        <v>446.6</v>
+      </c>
+      <c r="D57">
+        <v>441.7</v>
+      </c>
+      <c r="E57">
+        <v>61.57</v>
+      </c>
+      <c r="F57">
+        <v>1041</v>
+      </c>
+      <c r="G57">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Salaried General Practitioner</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>1414584</v>
+      </c>
+      <c r="C58">
+        <v>128.4</v>
+      </c>
+      <c r="D58">
+        <v>273.1</v>
+      </c>
+      <c r="E58">
+        <v>18.01</v>
+      </c>
+      <c r="F58">
+        <v>7889</v>
+      </c>
+      <c r="G58">
+        <v>6131</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior House Officer</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>1620</v>
+      </c>
+      <c r="C59">
+        <v>68.34999999999999</v>
+      </c>
+      <c r="D59">
+        <v>80.79000000000001</v>
+      </c>
+      <c r="E59">
+        <v>18.01</v>
+      </c>
+      <c r="F59">
+        <v>328.7</v>
+      </c>
+      <c r="G59">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Sessional GP</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>605268</v>
+      </c>
+      <c r="C60">
+        <v>78.52</v>
+      </c>
+      <c r="D60">
+        <v>161.4</v>
+      </c>
+      <c r="E60">
+        <v>18.01</v>
+      </c>
+      <c r="F60">
+        <v>2922</v>
+      </c>
+      <c r="G60">
+        <v>4254</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Sister/Charge Nurse</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>164561</v>
+      </c>
+      <c r="C61">
+        <v>97.11</v>
+      </c>
+      <c r="D61">
+        <v>164.1</v>
+      </c>
+      <c r="E61">
+        <v>21.51</v>
+      </c>
+      <c r="F61">
+        <v>2111</v>
+      </c>
+      <c r="G61">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Social Care Support Worker</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>630</v>
+      </c>
+      <c r="C62">
+        <v>105.1</v>
+      </c>
+      <c r="D62">
+        <v>96.3</v>
+      </c>
+      <c r="E62">
+        <v>21.01</v>
+      </c>
+      <c r="F62">
+        <v>210.1</v>
+      </c>
+      <c r="G62">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Social Worker</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>798</v>
+      </c>
+      <c r="C63">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="D63">
+        <v>48.69</v>
+      </c>
+      <c r="E63">
+        <v>63.04</v>
+      </c>
+      <c r="F63">
+        <v>183</v>
+      </c>
+      <c r="G63">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Specialist Nurse Practitioner</t>
+        </is>
+      </c>
+      <c r="B64">
+        <v>483637.2158163266</v>
+      </c>
+      <c r="C64">
+        <v>57.7</v>
+      </c>
+      <c r="D64">
+        <v>104.1</v>
+      </c>
+      <c r="E64">
+        <v>13.38</v>
+      </c>
+      <c r="F64">
+        <v>2442</v>
+      </c>
+      <c r="G64">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Specialist Practitioner</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>5379.791666666667</v>
+      </c>
+      <c r="C65">
+        <v>53.42</v>
+      </c>
+      <c r="D65">
+        <v>50.45</v>
+      </c>
+      <c r="E65">
+        <v>15.38</v>
+      </c>
+      <c r="F65">
+        <v>236.4</v>
+      </c>
+      <c r="G65">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Specialist Registrar</t>
+        </is>
+      </c>
+      <c r="B66">
+        <v>144</v>
+      </c>
+      <c r="C66">
+        <v>25.18</v>
+      </c>
+      <c r="D66">
+        <v>9.673</v>
+      </c>
+      <c r="E66">
+        <v>18.01</v>
+      </c>
+      <c r="F66">
+        <v>36.02</v>
+      </c>
+      <c r="G66">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Staff Nurse</t>
+        </is>
+      </c>
+      <c r="B67">
+        <v>432709</v>
+      </c>
+      <c r="C67">
+        <v>98.33</v>
+      </c>
+      <c r="D67">
+        <v>210.5</v>
+      </c>
+      <c r="E67">
+        <v>21.51</v>
+      </c>
+      <c r="F67">
+        <v>6282</v>
+      </c>
+      <c r="G67">
+        <v>2373</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Therapist</t>
+        </is>
+      </c>
+      <c r="B68">
+        <v>3355</v>
+      </c>
+      <c r="C68">
+        <v>156.2</v>
+      </c>
+      <c r="D68">
+        <v>283.9</v>
+      </c>
+      <c r="E68">
+        <v>27.52</v>
+      </c>
+      <c r="F68">
+        <v>1071</v>
+      </c>
+      <c r="G68">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Trainee Practitioner</t>
+        </is>
+      </c>
+      <c r="B69">
+        <v>998.2</v>
+      </c>
+      <c r="C69">
+        <v>18.52</v>
+      </c>
+      <c r="D69">
+        <v>24.46</v>
+      </c>
+      <c r="E69">
+        <v>9.605</v>
+      </c>
+      <c r="F69">
+        <v>109.9</v>
+      </c>
+      <c r="G69">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -2217,10 +2276,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>14013</v>
+        <v>13987.84846938776</v>
       </c>
       <c r="C2">
-        <v>50.71</v>
+        <v>50.62</v>
       </c>
       <c r="D2">
         <v>68.14</v>
@@ -2267,10 +2326,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="C4">
-        <v>62.59</v>
+        <v>62.02</v>
       </c>
       <c r="D4">
         <v>45.12</v>
@@ -2292,10 +2351,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>870</v>
+        <v>880</v>
       </c>
       <c r="C5">
-        <v>72.55</v>
+        <v>73.38</v>
       </c>
       <c r="D5">
         <v>41.43</v>
@@ -2317,10 +2376,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>12169</v>
+        <v>12204.44166666667</v>
       </c>
       <c r="C6">
-        <v>41.33</v>
+        <v>41.45</v>
       </c>
       <c r="D6">
         <v>53.31</v>
@@ -2342,10 +2401,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>105106</v>
+        <v>105012</v>
       </c>
       <c r="C7">
-        <v>99.53</v>
+        <v>99.45</v>
       </c>
       <c r="D7">
         <v>201.1</v>
@@ -2367,10 +2426,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>61768</v>
+        <v>61926.79230769232</v>
       </c>
       <c r="C8">
-        <v>39.35</v>
+        <v>39.45</v>
       </c>
       <c r="D8">
         <v>68.97</v>
@@ -2392,10 +2451,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>9304</v>
+        <v>9283.983333333334</v>
       </c>
       <c r="C9">
-        <v>54.52</v>
+        <v>54.41</v>
       </c>
       <c r="D9">
         <v>127</v>
@@ -2439,10 +2498,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>470</v>
+        <v>470.46</v>
       </c>
       <c r="C11">
-        <v>187.6</v>
+        <v>187.8</v>
       </c>
       <c r="D11">
         <v>382.4</v>
@@ -2464,10 +2523,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>1906</v>
+        <v>1890</v>
       </c>
       <c r="C12">
-        <v>50.55</v>
+        <v>50.12</v>
       </c>
       <c r="D12">
         <v>72.81999999999999</v>
@@ -2489,10 +2548,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>5807</v>
+        <v>5822</v>
       </c>
       <c r="C13">
-        <v>42.18</v>
+        <v>42.29</v>
       </c>
       <c r="D13">
         <v>42.93</v>
@@ -2589,10 +2648,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>4996</v>
+        <v>5004</v>
       </c>
       <c r="C17">
-        <v>55.44</v>
+        <v>55.53</v>
       </c>
       <c r="D17">
         <v>40.31</v>
@@ -2639,10 +2698,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>1364</v>
+        <v>1358.5</v>
       </c>
       <c r="C19">
-        <v>136.5</v>
+        <v>135.9</v>
       </c>
       <c r="D19">
         <v>150.5</v>
@@ -2664,10 +2723,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>3831</v>
+        <v>3824.593367346939</v>
       </c>
       <c r="C20">
-        <v>44.11</v>
+        <v>44.04</v>
       </c>
       <c r="D20">
         <v>56.51</v>
@@ -2689,10 +2748,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>412502</v>
+        <v>413235.6038461539</v>
       </c>
       <c r="C21">
-        <v>47.08</v>
+        <v>47.16</v>
       </c>
       <c r="D21">
         <v>101.9</v>
@@ -2714,10 +2773,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>2135830</v>
+        <v>2135628</v>
       </c>
       <c r="C22">
-        <v>99.48999999999999</v>
+        <v>99.48</v>
       </c>
       <c r="D22">
         <v>192.6</v>
@@ -2739,10 +2798,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>177076</v>
+        <v>176891</v>
       </c>
       <c r="C23">
-        <v>187.6</v>
+        <v>187.4</v>
       </c>
       <c r="D23">
         <v>419.6</v>
@@ -2764,10 +2823,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>7239</v>
+        <v>7298</v>
       </c>
       <c r="C24">
-        <v>105.2</v>
+        <v>106</v>
       </c>
       <c r="D24">
         <v>137.2</v>
@@ -2789,10 +2848,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>8912</v>
+        <v>8928</v>
       </c>
       <c r="C25">
-        <v>120.2</v>
+        <v>120.5</v>
       </c>
       <c r="D25">
         <v>304.2</v>
@@ -2814,10 +2873,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>4497</v>
+        <v>4510</v>
       </c>
       <c r="C26">
-        <v>32.53</v>
+        <v>32.63</v>
       </c>
       <c r="D26">
         <v>44.83</v>
@@ -2883,10 +2942,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>43271</v>
+        <v>43421.7</v>
       </c>
       <c r="C29">
-        <v>40.53</v>
+        <v>40.67</v>
       </c>
       <c r="D29">
         <v>53.03</v>
@@ -2908,10 +2967,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>602734</v>
+        <v>602532</v>
       </c>
       <c r="C30">
-        <v>60.38</v>
+        <v>60.36</v>
       </c>
       <c r="D30">
         <v>160.4</v>
@@ -2933,10 +2992,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>15065028</v>
+        <v>15066072</v>
       </c>
       <c r="C31">
-        <v>364.5</v>
+        <v>364.6</v>
       </c>
       <c r="D31">
         <v>494.3</v>
@@ -2958,10 +3017,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>929596</v>
+        <v>930917.4807692309</v>
       </c>
       <c r="C32">
-        <v>90.48</v>
+        <v>90.61</v>
       </c>
       <c r="D32">
         <v>286</v>
@@ -2983,10 +3042,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>766</v>
+        <v>774</v>
       </c>
       <c r="C33">
-        <v>82.14</v>
+        <v>83</v>
       </c>
       <c r="D33">
         <v>97.09</v>
@@ -3008,10 +3067,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>255942</v>
+        <v>255816</v>
       </c>
       <c r="C34">
-        <v>74.51000000000001</v>
+        <v>74.47</v>
       </c>
       <c r="D34">
         <v>214.8</v>
@@ -3033,10 +3092,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>576.8</v>
+        <v>576.6</v>
       </c>
       <c r="C35">
-        <v>6.755</v>
+        <v>6.752</v>
       </c>
       <c r="D35">
         <v>9.329000000000001</v>
@@ -3058,7 +3117,7 @@
         </is>
       </c>
       <c r="B36">
-        <v>8377.799999999999</v>
+        <v>8382.4</v>
       </c>
       <c r="C36">
         <v>11.72</v>
@@ -3083,10 +3142,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>216</v>
+        <v>215.1916666666667</v>
       </c>
       <c r="C37">
-        <v>18.01</v>
+        <v>17.94</v>
       </c>
       <c r="D37">
         <v>6.279</v>
@@ -3108,10 +3167,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>6795</v>
+        <v>6793.908333333334</v>
       </c>
       <c r="C38">
-        <v>89</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="D38">
         <v>188</v>
@@ -3180,10 +3239,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>95582</v>
+        <v>95503</v>
       </c>
       <c r="C41">
-        <v>86.06</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="D41">
         <v>132.8</v>
@@ -3230,10 +3289,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>330</v>
+        <v>321.78</v>
       </c>
       <c r="C43">
-        <v>55.04</v>
+        <v>53.67</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -3255,10 +3314,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>7400</v>
+        <v>7425</v>
       </c>
       <c r="C44">
-        <v>405.3</v>
+        <v>406.7</v>
       </c>
       <c r="D44">
         <v>1113</v>
@@ -3280,10 +3339,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>14830</v>
+        <v>14878.96666666667</v>
       </c>
       <c r="C45">
-        <v>59.25</v>
+        <v>59.45</v>
       </c>
       <c r="D45">
         <v>90.67</v>
@@ -3305,10 +3364,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C46">
-        <v>112.3</v>
+        <v>110.2</v>
       </c>
       <c r="D46">
         <v>11.65</v>
@@ -3330,10 +3389,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>11542</v>
+        <v>11546</v>
       </c>
       <c r="C47">
-        <v>31.49</v>
+        <v>31.5</v>
       </c>
       <c r="D47">
         <v>55.55</v>
@@ -3355,10 +3414,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>346</v>
+        <v>347.75</v>
       </c>
       <c r="C48">
-        <v>26.33</v>
+        <v>26.46</v>
       </c>
       <c r="D48">
         <v>30.93</v>
@@ -3380,10 +3439,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>15288</v>
+        <v>15390</v>
       </c>
       <c r="C49">
-        <v>37.38</v>
+        <v>37.63</v>
       </c>
       <c r="D49">
         <v>63.56</v>
@@ -3430,10 +3489,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>32395</v>
+        <v>32472</v>
       </c>
       <c r="C51">
-        <v>62.51</v>
+        <v>62.66</v>
       </c>
       <c r="D51">
         <v>61.85</v>
@@ -3455,10 +3514,10 @@
         </is>
       </c>
       <c r="B52">
-        <v>1628</v>
+        <v>1644.5</v>
       </c>
       <c r="C52">
-        <v>57.52</v>
+        <v>58.1</v>
       </c>
       <c r="D52">
         <v>25.24</v>
@@ -3480,10 +3539,10 @@
         </is>
       </c>
       <c r="B53">
-        <v>3235</v>
+        <v>3245</v>
       </c>
       <c r="C53">
-        <v>52.34</v>
+        <v>52.5</v>
       </c>
       <c r="D53">
         <v>30.81</v>
@@ -3505,10 +3564,10 @@
         </is>
       </c>
       <c r="B54">
-        <v>9993</v>
+        <v>10002.78265306123</v>
       </c>
       <c r="C54">
-        <v>43.58</v>
+        <v>43.62</v>
       </c>
       <c r="D54">
         <v>54.14</v>
@@ -3530,10 +3589,10 @@
         </is>
       </c>
       <c r="B55">
-        <v>30.6</v>
+        <v>31</v>
       </c>
       <c r="C55">
-        <v>4.299</v>
+        <v>4.355</v>
       </c>
       <c r="D55">
         <v>1.618</v>
@@ -3555,10 +3614,10 @@
         </is>
       </c>
       <c r="B56">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C56">
-        <v>89.31</v>
+        <v>89.44</v>
       </c>
       <c r="D56">
         <v>68.5</v>
@@ -3580,10 +3639,10 @@
         </is>
       </c>
       <c r="B57">
-        <v>774</v>
+        <v>770.5</v>
       </c>
       <c r="C57">
-        <v>17.96</v>
+        <v>17.88</v>
       </c>
       <c r="D57">
         <v>18.9</v>
@@ -3605,10 +3664,10 @@
         </is>
       </c>
       <c r="B58">
-        <v>3450</v>
+        <v>3432</v>
       </c>
       <c r="C58">
-        <v>448.9</v>
+        <v>446.6</v>
       </c>
       <c r="D58">
         <v>441.7</v>
@@ -3630,10 +3689,10 @@
         </is>
       </c>
       <c r="B59">
-        <v>1413608</v>
+        <v>1414584</v>
       </c>
       <c r="C59">
-        <v>128.3</v>
+        <v>128.4</v>
       </c>
       <c r="D59">
         <v>273.1</v>
@@ -3655,10 +3714,10 @@
         </is>
       </c>
       <c r="B60">
-        <v>1614</v>
+        <v>1620</v>
       </c>
       <c r="C60">
-        <v>68.09999999999999</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="D60">
         <v>80.79000000000001</v>
@@ -3680,10 +3739,10 @@
         </is>
       </c>
       <c r="B61">
-        <v>605354</v>
+        <v>605268</v>
       </c>
       <c r="C61">
-        <v>78.53</v>
+        <v>78.52</v>
       </c>
       <c r="D61">
         <v>161.4</v>
@@ -3705,10 +3764,10 @@
         </is>
       </c>
       <c r="B62">
-        <v>164853</v>
+        <v>164561</v>
       </c>
       <c r="C62">
-        <v>97.29000000000001</v>
+        <v>97.11</v>
       </c>
       <c r="D62">
         <v>164.1</v>
@@ -3730,10 +3789,10 @@
         </is>
       </c>
       <c r="B63">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C63">
-        <v>105.4</v>
+        <v>105.1</v>
       </c>
       <c r="D63">
         <v>96.3</v>
@@ -3755,10 +3814,10 @@
         </is>
       </c>
       <c r="B64">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="C64">
-        <v>100.5</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="D64">
         <v>48.69</v>
@@ -3780,10 +3839,10 @@
         </is>
       </c>
       <c r="B65">
-        <v>483249</v>
+        <v>483637.2158163266</v>
       </c>
       <c r="C65">
-        <v>57.65</v>
+        <v>57.7</v>
       </c>
       <c r="D65">
         <v>104.1</v>
@@ -3805,10 +3864,10 @@
         </is>
       </c>
       <c r="B66">
-        <v>5347</v>
+        <v>5379.791666666667</v>
       </c>
       <c r="C66">
-        <v>53.1</v>
+        <v>53.42</v>
       </c>
       <c r="D66">
         <v>50.45</v>
@@ -3855,10 +3914,10 @@
         </is>
       </c>
       <c r="B68">
-        <v>433189</v>
+        <v>432709</v>
       </c>
       <c r="C68">
-        <v>98.44</v>
+        <v>98.33</v>
       </c>
       <c r="D68">
         <v>210.5</v>
@@ -3880,10 +3939,10 @@
         </is>
       </c>
       <c r="B69">
-        <v>3345</v>
+        <v>3355</v>
       </c>
       <c r="C69">
-        <v>155.7</v>
+        <v>156.2</v>
       </c>
       <c r="D69">
         <v>283.9</v>
@@ -3905,10 +3964,10 @@
         </is>
       </c>
       <c r="B70">
-        <v>989</v>
+        <v>998.2</v>
       </c>
       <c r="C70">
-        <v>18.35</v>
+        <v>18.52</v>
       </c>
       <c r="D70">
         <v>24.46</v>

--- a/CPRD Raw Analysis/Results/Output_costs_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_costs_Raw.xlsx
@@ -360,61 +360,61 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>mean_visit_per_year</t>
+          <t>mean_visit_cost_per_year</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>min_visit_per_year</t>
+          <t>min_visit_cost_per_year</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>max_visit_per_year</t>
+          <t>max_visit_cost_per_year</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>sd_visit_per_year</t>
+          <t>sd_visit_cost_per_year</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>median_visit_per_year</t>
+          <t>median_visit_cost_per_year</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>lower_q_visits_per_year</t>
+          <t>lower_q_visits_cost_per_year</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>upper_q_visits_per_year</t>
+          <t>upper_q_visits_cost_per_year</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2">
-        <v>550.0429584984093</v>
+        <v>550.04</v>
       </c>
       <c r="B2">
-        <v>3.102123287671233</v>
+        <v>3.1</v>
       </c>
       <c r="C2">
-        <v>16654.69759615385</v>
+        <v>16654.7</v>
       </c>
       <c r="D2">
-        <v>674.2</v>
+        <v>674.24</v>
       </c>
       <c r="E2">
-        <v>459.7</v>
+        <v>459.69</v>
       </c>
       <c r="F2">
-        <v>261.8</v>
+        <v>261.78</v>
       </c>
       <c r="G2">
-        <v>788.7</v>
+        <v>788.72</v>
       </c>
     </row>
   </sheetData>
@@ -430,61 +430,61 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>mean_visit_per_year</t>
+          <t>mean_visit_cost_per_year</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>min_visit_per_year</t>
+          <t>min_visit_cost_per_year</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>max_visit_per_year</t>
+          <t>max_visit_cost_per_year</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>sd_visit_per_year</t>
+          <t>sd_visit_cost_per_year</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>median_visit_per_year</t>
+          <t>median_visit_cost_per_year</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>lower_q_visits_per_year</t>
+          <t>lower_q_visits_cost_per_year</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>upper_q_visits_per_year</t>
+          <t>upper_q_visits_cost_per_year</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2">
-        <v>545.120679330498</v>
+        <v>545.12</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>16654.69759615385</v>
+        <v>16654.7</v>
       </c>
       <c r="D2">
-        <v>673.3</v>
+        <v>673.27</v>
       </c>
       <c r="E2">
-        <v>450.3</v>
+        <v>450.31</v>
       </c>
       <c r="F2">
-        <v>252.2</v>
+        <v>252.17</v>
       </c>
       <c r="G2">
-        <v>774.5</v>
+        <v>774.53</v>
       </c>
     </row>
   </sheetData>
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>13987.84846938776</v>
+        <v>13987.85</v>
       </c>
       <c r="C2">
         <v>50.62</v>
@@ -553,7 +553,7 @@
         <v>13.38</v>
       </c>
       <c r="F2">
-        <v>449.1</v>
+        <v>449.14</v>
       </c>
       <c r="G2">
         <v>149</v>
@@ -572,13 +572,13 @@
         <v>217.8</v>
       </c>
       <c r="D3">
-        <v>365.2</v>
+        <v>365.23</v>
       </c>
       <c r="E3">
         <v>27.52</v>
       </c>
       <c r="F3">
-        <v>1435</v>
+        <v>1434.91</v>
       </c>
       <c r="G3">
         <v>22</v>
@@ -603,7 +603,7 @@
         <v>27.52</v>
       </c>
       <c r="F4">
-        <v>137.6</v>
+        <v>137.59</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -628,7 +628,7 @@
         <v>27.52</v>
       </c>
       <c r="F5">
-        <v>137.6</v>
+        <v>137.59</v>
       </c>
       <c r="G5">
         <v>6</v>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>12204.44166666667</v>
+        <v>12204.44</v>
       </c>
       <c r="C6">
         <v>41.45</v>
@@ -653,7 +653,7 @@
         <v>15.38</v>
       </c>
       <c r="F6">
-        <v>337.4</v>
+        <v>337.41</v>
       </c>
       <c r="G6">
         <v>157</v>
@@ -672,13 +672,13 @@
         <v>99.45</v>
       </c>
       <c r="D7">
-        <v>201.1</v>
+        <v>201.08</v>
       </c>
       <c r="E7">
         <v>18.01</v>
       </c>
       <c r="F7">
-        <v>2858</v>
+        <v>2858.48</v>
       </c>
       <c r="G7">
         <v>590</v>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>61926.79230769232</v>
+        <v>61926.79</v>
       </c>
       <c r="C8">
         <v>39.45</v>
@@ -700,10 +700,10 @@
         <v>68.97</v>
       </c>
       <c r="E8">
-        <v>9.605</v>
+        <v>9.6</v>
       </c>
       <c r="F8">
-        <v>779</v>
+        <v>779.04</v>
       </c>
       <c r="G8">
         <v>852</v>
@@ -716,19 +716,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>9283.983333333334</v>
+        <v>9283.98</v>
       </c>
       <c r="C9">
         <v>54.41</v>
       </c>
       <c r="D9">
-        <v>127</v>
+        <v>127.02</v>
       </c>
       <c r="E9">
         <v>15.38</v>
       </c>
       <c r="F9">
-        <v>1064</v>
+        <v>1063.74</v>
       </c>
       <c r="G9">
         <v>92</v>
@@ -769,13 +769,13 @@
         <v>187.8</v>
       </c>
       <c r="D11">
-        <v>382.4</v>
+        <v>382.38</v>
       </c>
       <c r="E11">
         <v>78.45999999999999</v>
       </c>
       <c r="F11">
-        <v>619.2</v>
+        <v>619.23</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -800,7 +800,7 @@
         <v>21.01</v>
       </c>
       <c r="F12">
-        <v>359.9</v>
+        <v>359.89</v>
       </c>
       <c r="G12">
         <v>21</v>
@@ -825,7 +825,7 @@
         <v>20.51</v>
       </c>
       <c r="F13">
-        <v>225.7</v>
+        <v>225.65</v>
       </c>
       <c r="G13">
         <v>74</v>
@@ -894,7 +894,7 @@
         <v>21.75</v>
       </c>
       <c r="D16">
-        <v>7.216</v>
+        <v>7.22</v>
       </c>
       <c r="E16">
         <v>18.01</v>
@@ -925,7 +925,7 @@
         <v>18.01</v>
       </c>
       <c r="F17">
-        <v>180.1</v>
+        <v>180.12</v>
       </c>
       <c r="G17">
         <v>46</v>
@@ -966,16 +966,16 @@
         <v>1358.5</v>
       </c>
       <c r="C19">
-        <v>135.9</v>
+        <v>135.94</v>
       </c>
       <c r="D19">
-        <v>150.5</v>
+        <v>150.51</v>
       </c>
       <c r="E19">
         <v>35.77</v>
       </c>
       <c r="F19">
-        <v>393.5</v>
+        <v>393.52</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>3824.593367346939</v>
+        <v>3824.59</v>
       </c>
       <c r="C20">
         <v>44.04</v>
@@ -1000,7 +1000,7 @@
         <v>13.38</v>
       </c>
       <c r="F20">
-        <v>267.6</v>
+        <v>267.64</v>
       </c>
       <c r="G20">
         <v>47</v>
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="B21">
-        <v>413235.6038461539</v>
+        <v>413235.6</v>
       </c>
       <c r="C21">
         <v>47.16</v>
       </c>
       <c r="D21">
-        <v>101.9</v>
+        <v>101.93</v>
       </c>
       <c r="E21">
-        <v>9.605</v>
+        <v>9.6</v>
       </c>
       <c r="F21">
-        <v>3111</v>
+        <v>3110.69</v>
       </c>
       <c r="G21">
         <v>4812</v>
@@ -1044,13 +1044,13 @@
         <v>99.48</v>
       </c>
       <c r="D22">
-        <v>192.6</v>
+        <v>192.62</v>
       </c>
       <c r="E22">
         <v>18.01</v>
       </c>
       <c r="F22">
-        <v>6712</v>
+        <v>6712.19</v>
       </c>
       <c r="G22">
         <v>11772</v>
@@ -1066,16 +1066,16 @@
         <v>176891</v>
       </c>
       <c r="C23">
-        <v>187.4</v>
+        <v>187.39</v>
       </c>
       <c r="D23">
-        <v>419.6</v>
+        <v>419.57</v>
       </c>
       <c r="E23">
         <v>35.77</v>
       </c>
       <c r="F23">
-        <v>4353</v>
+        <v>4352.56</v>
       </c>
       <c r="G23">
         <v>545</v>
@@ -1091,16 +1091,16 @@
         <v>7298</v>
       </c>
       <c r="C24">
-        <v>106</v>
+        <v>106.04</v>
       </c>
       <c r="D24">
-        <v>137.2</v>
+        <v>137.18</v>
       </c>
       <c r="E24">
         <v>20.51</v>
       </c>
       <c r="F24">
-        <v>615.4</v>
+        <v>615.42</v>
       </c>
       <c r="G24">
         <v>36</v>
@@ -1116,10 +1116,10 @@
         <v>8928</v>
       </c>
       <c r="C25">
-        <v>120.5</v>
+        <v>120.46</v>
       </c>
       <c r="D25">
-        <v>304.2</v>
+        <v>304.22</v>
       </c>
       <c r="E25">
         <v>18.01</v>
@@ -1150,7 +1150,7 @@
         <v>20.51</v>
       </c>
       <c r="F26">
-        <v>315.3</v>
+        <v>315.27</v>
       </c>
       <c r="G26">
         <v>76</v>
@@ -1216,10 +1216,10 @@
         <v>53.03</v>
       </c>
       <c r="E29">
-        <v>9.605</v>
+        <v>9.6</v>
       </c>
       <c r="F29">
-        <v>374.6</v>
+        <v>374.58</v>
       </c>
       <c r="G29">
         <v>574</v>
@@ -1238,13 +1238,13 @@
         <v>60.36</v>
       </c>
       <c r="D30">
-        <v>160.4</v>
+        <v>160.38</v>
       </c>
       <c r="E30">
         <v>18.01</v>
       </c>
       <c r="F30">
-        <v>5260</v>
+        <v>5259.6</v>
       </c>
       <c r="G30">
         <v>5512</v>
@@ -1260,16 +1260,16 @@
         <v>15066072</v>
       </c>
       <c r="C31">
-        <v>364.6</v>
+        <v>364.56</v>
       </c>
       <c r="D31">
-        <v>494.3</v>
+        <v>494.33</v>
       </c>
       <c r="E31">
         <v>18.01</v>
       </c>
       <c r="F31">
-        <v>13150</v>
+        <v>13149</v>
       </c>
       <c r="G31">
         <v>23947</v>
@@ -1282,19 +1282,19 @@
         </is>
       </c>
       <c r="B32">
-        <v>930917.4807692309</v>
+        <v>930917.48</v>
       </c>
       <c r="C32">
         <v>90.61</v>
       </c>
       <c r="D32">
-        <v>286</v>
+        <v>286.02</v>
       </c>
       <c r="E32">
-        <v>9.605</v>
+        <v>9.6</v>
       </c>
       <c r="F32">
-        <v>14020</v>
+        <v>14022.79</v>
       </c>
       <c r="G32">
         <v>5894</v>
@@ -1319,7 +1319,7 @@
         <v>21.51</v>
       </c>
       <c r="F33">
-        <v>258.5</v>
+        <v>258.53</v>
       </c>
       <c r="G33">
         <v>5</v>
@@ -1338,13 +1338,13 @@
         <v>74.47</v>
       </c>
       <c r="D34">
-        <v>214.8</v>
+        <v>214.84</v>
       </c>
       <c r="E34">
         <v>18.01</v>
       </c>
       <c r="F34">
-        <v>4931</v>
+        <v>4930.88</v>
       </c>
       <c r="G34">
         <v>1851</v>
@@ -1360,13 +1360,13 @@
         <v>576.6</v>
       </c>
       <c r="C35">
-        <v>6.752</v>
+        <v>6.75</v>
       </c>
       <c r="D35">
-        <v>9.329000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="E35">
-        <v>3.102</v>
+        <v>3.1</v>
       </c>
       <c r="F35">
         <v>55.23</v>
@@ -1391,7 +1391,7 @@
         <v>19.95</v>
       </c>
       <c r="E36">
-        <v>3.102</v>
+        <v>3.1</v>
       </c>
       <c r="F36">
         <v>174.2</v>
@@ -1407,13 +1407,13 @@
         </is>
       </c>
       <c r="B37">
-        <v>215.1916666666667</v>
+        <v>215.19</v>
       </c>
       <c r="C37">
         <v>17.94</v>
       </c>
       <c r="D37">
-        <v>6.279</v>
+        <v>6.28</v>
       </c>
       <c r="E37">
         <v>15.38</v>
@@ -1432,19 +1432,19 @@
         </is>
       </c>
       <c r="B38">
-        <v>6793.908333333334</v>
+        <v>6793.91</v>
       </c>
       <c r="C38">
         <v>88.98999999999999</v>
       </c>
       <c r="D38">
-        <v>188</v>
+        <v>187.99</v>
       </c>
       <c r="E38">
         <v>15.38</v>
       </c>
       <c r="F38">
-        <v>990.7</v>
+        <v>990.74</v>
       </c>
       <c r="G38">
         <v>48</v>
@@ -1485,7 +1485,7 @@
         <v>85.98999999999999</v>
       </c>
       <c r="D40">
-        <v>132.8</v>
+        <v>132.81</v>
       </c>
       <c r="E40">
         <v>21.51</v>
@@ -1557,16 +1557,16 @@
         <v>7425</v>
       </c>
       <c r="C43">
-        <v>406.7</v>
+        <v>406.72</v>
       </c>
       <c r="D43">
-        <v>1113</v>
+        <v>1113.35</v>
       </c>
       <c r="E43">
-        <v>192.6</v>
+        <v>192.63</v>
       </c>
       <c r="F43">
-        <v>4109</v>
+        <v>4109.06</v>
       </c>
       <c r="G43">
         <v>12</v>
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="B44">
-        <v>14878.96666666667</v>
+        <v>14878.97</v>
       </c>
       <c r="C44">
         <v>59.45</v>
@@ -1591,7 +1591,7 @@
         <v>15.38</v>
       </c>
       <c r="F44">
-        <v>606.4</v>
+        <v>606.4400000000001</v>
       </c>
       <c r="G44">
         <v>139</v>
@@ -1613,7 +1613,7 @@
         <v>11.65</v>
       </c>
       <c r="E45">
-        <v>100.9</v>
+        <v>100.92</v>
       </c>
       <c r="F45">
         <v>117.4</v>
@@ -1641,7 +1641,7 @@
         <v>11.51</v>
       </c>
       <c r="F46">
-        <v>466.7</v>
+        <v>466.71</v>
       </c>
       <c r="G46">
         <v>201</v>
@@ -1691,7 +1691,7 @@
         <v>14.26</v>
       </c>
       <c r="F48">
-        <v>369.1</v>
+        <v>369.14</v>
       </c>
       <c r="G48">
         <v>225</v>
@@ -1741,7 +1741,7 @@
         <v>20.51</v>
       </c>
       <c r="F50">
-        <v>348.7</v>
+        <v>348.74</v>
       </c>
       <c r="G50">
         <v>269</v>
@@ -1766,7 +1766,7 @@
         <v>35.77</v>
       </c>
       <c r="F51">
-        <v>107.3</v>
+        <v>107.32</v>
       </c>
       <c r="G51">
         <v>15</v>
@@ -1791,7 +1791,7 @@
         <v>27.52</v>
       </c>
       <c r="F52">
-        <v>137.6</v>
+        <v>137.59</v>
       </c>
       <c r="G52">
         <v>32</v>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="B53">
-        <v>10002.78265306123</v>
+        <v>10002.78</v>
       </c>
       <c r="C53">
         <v>43.62</v>
@@ -1816,7 +1816,7 @@
         <v>13.38</v>
       </c>
       <c r="F53">
-        <v>375.7</v>
+        <v>375.72</v>
       </c>
       <c r="G53">
         <v>131</v>
@@ -1832,16 +1832,16 @@
         <v>31</v>
       </c>
       <c r="C54">
-        <v>4.355</v>
+        <v>4.35</v>
       </c>
       <c r="D54">
-        <v>1.618</v>
+        <v>1.62</v>
       </c>
       <c r="E54">
-        <v>3.102</v>
+        <v>3.1</v>
       </c>
       <c r="F54">
-        <v>6.204</v>
+        <v>6.2</v>
       </c>
       <c r="G54">
         <v>4</v>
@@ -1866,7 +1866,7 @@
         <v>35.77</v>
       </c>
       <c r="F55">
-        <v>178.9</v>
+        <v>178.87</v>
       </c>
       <c r="G55">
         <v>4</v>
@@ -1888,7 +1888,7 @@
         <v>18.9</v>
       </c>
       <c r="E56">
-        <v>5.754</v>
+        <v>5.75</v>
       </c>
       <c r="F56">
         <v>79.25</v>
@@ -1907,16 +1907,16 @@
         <v>3432</v>
       </c>
       <c r="C57">
-        <v>446.6</v>
+        <v>446.58</v>
       </c>
       <c r="D57">
-        <v>441.7</v>
+        <v>441.66</v>
       </c>
       <c r="E57">
         <v>61.57</v>
       </c>
       <c r="F57">
-        <v>1041</v>
+        <v>1040.71</v>
       </c>
       <c r="G57">
         <v>4</v>
@@ -1935,13 +1935,13 @@
         <v>128.4</v>
       </c>
       <c r="D58">
-        <v>273.1</v>
+        <v>273.12</v>
       </c>
       <c r="E58">
         <v>18.01</v>
       </c>
       <c r="F58">
-        <v>7889</v>
+        <v>7889.4</v>
       </c>
       <c r="G58">
         <v>6131</v>
@@ -1966,7 +1966,7 @@
         <v>18.01</v>
       </c>
       <c r="F59">
-        <v>328.7</v>
+        <v>328.72</v>
       </c>
       <c r="G59">
         <v>15</v>
@@ -1985,7 +1985,7 @@
         <v>78.52</v>
       </c>
       <c r="D60">
-        <v>161.4</v>
+        <v>161.38</v>
       </c>
       <c r="E60">
         <v>18.01</v>
@@ -2010,13 +2010,13 @@
         <v>97.11</v>
       </c>
       <c r="D61">
-        <v>164.1</v>
+        <v>164.14</v>
       </c>
       <c r="E61">
         <v>21.51</v>
       </c>
       <c r="F61">
-        <v>2111</v>
+        <v>2110.55</v>
       </c>
       <c r="G61">
         <v>919</v>
@@ -2032,7 +2032,7 @@
         <v>630</v>
       </c>
       <c r="C62">
-        <v>105.1</v>
+        <v>105.07</v>
       </c>
       <c r="D62">
         <v>96.3</v>
@@ -2041,7 +2041,7 @@
         <v>21.01</v>
       </c>
       <c r="F62">
-        <v>210.1</v>
+        <v>210.14</v>
       </c>
       <c r="G62">
         <v>3</v>
@@ -2066,7 +2066,7 @@
         <v>63.04</v>
       </c>
       <c r="F63">
-        <v>183</v>
+        <v>182.99</v>
       </c>
       <c r="G63">
         <v>5</v>
@@ -2079,19 +2079,19 @@
         </is>
       </c>
       <c r="B64">
-        <v>483637.2158163266</v>
+        <v>483637.22</v>
       </c>
       <c r="C64">
         <v>57.7</v>
       </c>
       <c r="D64">
-        <v>104.1</v>
+        <v>104.07</v>
       </c>
       <c r="E64">
         <v>13.38</v>
       </c>
       <c r="F64">
-        <v>2442</v>
+        <v>2442.19</v>
       </c>
       <c r="G64">
         <v>4566</v>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="B65">
-        <v>5379.791666666667</v>
+        <v>5379.79</v>
       </c>
       <c r="C65">
         <v>53.42</v>
@@ -2116,7 +2116,7 @@
         <v>15.38</v>
       </c>
       <c r="F65">
-        <v>236.4</v>
+        <v>236.39</v>
       </c>
       <c r="G65">
         <v>54</v>
@@ -2135,7 +2135,7 @@
         <v>25.18</v>
       </c>
       <c r="D66">
-        <v>9.673</v>
+        <v>9.67</v>
       </c>
       <c r="E66">
         <v>18.01</v>
@@ -2160,13 +2160,13 @@
         <v>98.33</v>
       </c>
       <c r="D67">
-        <v>210.5</v>
+        <v>210.49</v>
       </c>
       <c r="E67">
         <v>21.51</v>
       </c>
       <c r="F67">
-        <v>6282</v>
+        <v>6282.3</v>
       </c>
       <c r="G67">
         <v>2373</v>
@@ -2185,13 +2185,13 @@
         <v>156.2</v>
       </c>
       <c r="D68">
-        <v>283.9</v>
+        <v>283.93</v>
       </c>
       <c r="E68">
         <v>27.52</v>
       </c>
       <c r="F68">
-        <v>1071</v>
+        <v>1071.4</v>
       </c>
       <c r="G68">
         <v>13</v>
@@ -2213,10 +2213,10 @@
         <v>24.46</v>
       </c>
       <c r="E69">
-        <v>9.605</v>
+        <v>9.6</v>
       </c>
       <c r="F69">
-        <v>109.9</v>
+        <v>109.93</v>
       </c>
       <c r="G69">
         <v>28</v>
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>13987.84846938776</v>
+        <v>13987.85</v>
       </c>
       <c r="C2">
         <v>50.62</v>
@@ -2288,7 +2288,7 @@
         <v>13.38</v>
       </c>
       <c r="F2">
-        <v>449.1</v>
+        <v>449.14</v>
       </c>
       <c r="G2">
         <v>149</v>
@@ -2307,13 +2307,13 @@
         <v>217.8</v>
       </c>
       <c r="D3">
-        <v>365.2</v>
+        <v>365.23</v>
       </c>
       <c r="E3">
         <v>27.52</v>
       </c>
       <c r="F3">
-        <v>1435</v>
+        <v>1434.91</v>
       </c>
       <c r="G3">
         <v>22</v>
@@ -2338,7 +2338,7 @@
         <v>27.52</v>
       </c>
       <c r="F4">
-        <v>137.6</v>
+        <v>137.59</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -2363,7 +2363,7 @@
         <v>27.52</v>
       </c>
       <c r="F5">
-        <v>137.6</v>
+        <v>137.59</v>
       </c>
       <c r="G5">
         <v>6</v>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>12204.44166666667</v>
+        <v>12204.44</v>
       </c>
       <c r="C6">
         <v>41.45</v>
@@ -2388,7 +2388,7 @@
         <v>15.38</v>
       </c>
       <c r="F6">
-        <v>337.4</v>
+        <v>337.41</v>
       </c>
       <c r="G6">
         <v>157</v>
@@ -2407,13 +2407,13 @@
         <v>99.45</v>
       </c>
       <c r="D7">
-        <v>201.1</v>
+        <v>201.08</v>
       </c>
       <c r="E7">
         <v>18.01</v>
       </c>
       <c r="F7">
-        <v>2858</v>
+        <v>2858.48</v>
       </c>
       <c r="G7">
         <v>590</v>
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>61926.79230769232</v>
+        <v>61926.79</v>
       </c>
       <c r="C8">
         <v>39.45</v>
@@ -2435,10 +2435,10 @@
         <v>68.97</v>
       </c>
       <c r="E8">
-        <v>9.605</v>
+        <v>9.6</v>
       </c>
       <c r="F8">
-        <v>779</v>
+        <v>779.04</v>
       </c>
       <c r="G8">
         <v>852</v>
@@ -2451,19 +2451,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>9283.983333333334</v>
+        <v>9283.98</v>
       </c>
       <c r="C9">
         <v>54.41</v>
       </c>
       <c r="D9">
-        <v>127</v>
+        <v>127.02</v>
       </c>
       <c r="E9">
         <v>15.38</v>
       </c>
       <c r="F9">
-        <v>1064</v>
+        <v>1063.74</v>
       </c>
       <c r="G9">
         <v>92</v>
@@ -2504,13 +2504,13 @@
         <v>187.8</v>
       </c>
       <c r="D11">
-        <v>382.4</v>
+        <v>382.38</v>
       </c>
       <c r="E11">
         <v>78.45999999999999</v>
       </c>
       <c r="F11">
-        <v>619.2</v>
+        <v>619.23</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -2535,7 +2535,7 @@
         <v>21.01</v>
       </c>
       <c r="F12">
-        <v>359.9</v>
+        <v>359.89</v>
       </c>
       <c r="G12">
         <v>21</v>
@@ -2560,7 +2560,7 @@
         <v>20.51</v>
       </c>
       <c r="F13">
-        <v>225.7</v>
+        <v>225.65</v>
       </c>
       <c r="G13">
         <v>74</v>
@@ -2629,7 +2629,7 @@
         <v>21.75</v>
       </c>
       <c r="D16">
-        <v>7.216</v>
+        <v>7.22</v>
       </c>
       <c r="E16">
         <v>18.01</v>
@@ -2660,7 +2660,7 @@
         <v>18.01</v>
       </c>
       <c r="F17">
-        <v>180.1</v>
+        <v>180.12</v>
       </c>
       <c r="G17">
         <v>46</v>
@@ -2701,16 +2701,16 @@
         <v>1358.5</v>
       </c>
       <c r="C19">
-        <v>135.9</v>
+        <v>135.94</v>
       </c>
       <c r="D19">
-        <v>150.5</v>
+        <v>150.51</v>
       </c>
       <c r="E19">
         <v>35.77</v>
       </c>
       <c r="F19">
-        <v>393.5</v>
+        <v>393.52</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>3824.593367346939</v>
+        <v>3824.59</v>
       </c>
       <c r="C20">
         <v>44.04</v>
@@ -2735,7 +2735,7 @@
         <v>13.38</v>
       </c>
       <c r="F20">
-        <v>267.6</v>
+        <v>267.64</v>
       </c>
       <c r="G20">
         <v>47</v>
@@ -2748,19 +2748,19 @@
         </is>
       </c>
       <c r="B21">
-        <v>413235.6038461539</v>
+        <v>413235.6</v>
       </c>
       <c r="C21">
         <v>47.16</v>
       </c>
       <c r="D21">
-        <v>101.9</v>
+        <v>101.93</v>
       </c>
       <c r="E21">
-        <v>9.605</v>
+        <v>9.6</v>
       </c>
       <c r="F21">
-        <v>3111</v>
+        <v>3110.69</v>
       </c>
       <c r="G21">
         <v>4812</v>
@@ -2779,13 +2779,13 @@
         <v>99.48</v>
       </c>
       <c r="D22">
-        <v>192.6</v>
+        <v>192.62</v>
       </c>
       <c r="E22">
         <v>18.01</v>
       </c>
       <c r="F22">
-        <v>6712</v>
+        <v>6712.19</v>
       </c>
       <c r="G22">
         <v>11772</v>
@@ -2801,16 +2801,16 @@
         <v>176891</v>
       </c>
       <c r="C23">
-        <v>187.4</v>
+        <v>187.39</v>
       </c>
       <c r="D23">
-        <v>419.6</v>
+        <v>419.57</v>
       </c>
       <c r="E23">
         <v>35.77</v>
       </c>
       <c r="F23">
-        <v>4353</v>
+        <v>4352.56</v>
       </c>
       <c r="G23">
         <v>545</v>
@@ -2826,16 +2826,16 @@
         <v>7298</v>
       </c>
       <c r="C24">
-        <v>106</v>
+        <v>106.04</v>
       </c>
       <c r="D24">
-        <v>137.2</v>
+        <v>137.18</v>
       </c>
       <c r="E24">
         <v>20.51</v>
       </c>
       <c r="F24">
-        <v>615.4</v>
+        <v>615.42</v>
       </c>
       <c r="G24">
         <v>36</v>
@@ -2851,10 +2851,10 @@
         <v>8928</v>
       </c>
       <c r="C25">
-        <v>120.5</v>
+        <v>120.46</v>
       </c>
       <c r="D25">
-        <v>304.2</v>
+        <v>304.22</v>
       </c>
       <c r="E25">
         <v>18.01</v>
@@ -2885,7 +2885,7 @@
         <v>20.51</v>
       </c>
       <c r="F26">
-        <v>315.3</v>
+        <v>315.27</v>
       </c>
       <c r="G26">
         <v>76</v>
@@ -2951,10 +2951,10 @@
         <v>53.03</v>
       </c>
       <c r="E29">
-        <v>9.605</v>
+        <v>9.6</v>
       </c>
       <c r="F29">
-        <v>374.6</v>
+        <v>374.58</v>
       </c>
       <c r="G29">
         <v>574</v>
@@ -2973,13 +2973,13 @@
         <v>60.36</v>
       </c>
       <c r="D30">
-        <v>160.4</v>
+        <v>160.38</v>
       </c>
       <c r="E30">
         <v>18.01</v>
       </c>
       <c r="F30">
-        <v>5260</v>
+        <v>5259.6</v>
       </c>
       <c r="G30">
         <v>5512</v>
@@ -2995,16 +2995,16 @@
         <v>15066072</v>
       </c>
       <c r="C31">
-        <v>364.6</v>
+        <v>364.56</v>
       </c>
       <c r="D31">
-        <v>494.3</v>
+        <v>494.33</v>
       </c>
       <c r="E31">
         <v>18.01</v>
       </c>
       <c r="F31">
-        <v>13150</v>
+        <v>13149</v>
       </c>
       <c r="G31">
         <v>23947</v>
@@ -3017,19 +3017,19 @@
         </is>
       </c>
       <c r="B32">
-        <v>930917.4807692309</v>
+        <v>930917.48</v>
       </c>
       <c r="C32">
         <v>90.61</v>
       </c>
       <c r="D32">
-        <v>286</v>
+        <v>286.02</v>
       </c>
       <c r="E32">
-        <v>9.605</v>
+        <v>9.6</v>
       </c>
       <c r="F32">
-        <v>14020</v>
+        <v>14022.79</v>
       </c>
       <c r="G32">
         <v>5894</v>
@@ -3054,7 +3054,7 @@
         <v>21.51</v>
       </c>
       <c r="F33">
-        <v>258.5</v>
+        <v>258.53</v>
       </c>
       <c r="G33">
         <v>5</v>
@@ -3073,13 +3073,13 @@
         <v>74.47</v>
       </c>
       <c r="D34">
-        <v>214.8</v>
+        <v>214.84</v>
       </c>
       <c r="E34">
         <v>18.01</v>
       </c>
       <c r="F34">
-        <v>4931</v>
+        <v>4930.88</v>
       </c>
       <c r="G34">
         <v>1851</v>
@@ -3095,13 +3095,13 @@
         <v>576.6</v>
       </c>
       <c r="C35">
-        <v>6.752</v>
+        <v>6.75</v>
       </c>
       <c r="D35">
-        <v>9.329000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="E35">
-        <v>3.102</v>
+        <v>3.1</v>
       </c>
       <c r="F35">
         <v>55.23</v>
@@ -3126,7 +3126,7 @@
         <v>19.95</v>
       </c>
       <c r="E36">
-        <v>3.102</v>
+        <v>3.1</v>
       </c>
       <c r="F36">
         <v>174.2</v>
@@ -3142,13 +3142,13 @@
         </is>
       </c>
       <c r="B37">
-        <v>215.1916666666667</v>
+        <v>215.19</v>
       </c>
       <c r="C37">
         <v>17.94</v>
       </c>
       <c r="D37">
-        <v>6.279</v>
+        <v>6.28</v>
       </c>
       <c r="E37">
         <v>15.38</v>
@@ -3167,19 +3167,19 @@
         </is>
       </c>
       <c r="B38">
-        <v>6793.908333333334</v>
+        <v>6793.91</v>
       </c>
       <c r="C38">
         <v>88.98999999999999</v>
       </c>
       <c r="D38">
-        <v>188</v>
+        <v>187.99</v>
       </c>
       <c r="E38">
         <v>15.38</v>
       </c>
       <c r="F38">
-        <v>990.7</v>
+        <v>990.74</v>
       </c>
       <c r="G38">
         <v>48</v>
@@ -3245,7 +3245,7 @@
         <v>85.98999999999999</v>
       </c>
       <c r="D41">
-        <v>132.8</v>
+        <v>132.81</v>
       </c>
       <c r="E41">
         <v>21.51</v>
@@ -3317,16 +3317,16 @@
         <v>7425</v>
       </c>
       <c r="C44">
-        <v>406.7</v>
+        <v>406.72</v>
       </c>
       <c r="D44">
-        <v>1113</v>
+        <v>1113.35</v>
       </c>
       <c r="E44">
-        <v>192.6</v>
+        <v>192.63</v>
       </c>
       <c r="F44">
-        <v>4109</v>
+        <v>4109.06</v>
       </c>
       <c r="G44">
         <v>12</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="B45">
-        <v>14878.96666666667</v>
+        <v>14878.97</v>
       </c>
       <c r="C45">
         <v>59.45</v>
@@ -3351,7 +3351,7 @@
         <v>15.38</v>
       </c>
       <c r="F45">
-        <v>606.4</v>
+        <v>606.4400000000001</v>
       </c>
       <c r="G45">
         <v>139</v>
@@ -3373,7 +3373,7 @@
         <v>11.65</v>
       </c>
       <c r="E46">
-        <v>100.9</v>
+        <v>100.92</v>
       </c>
       <c r="F46">
         <v>117.4</v>
@@ -3401,7 +3401,7 @@
         <v>11.51</v>
       </c>
       <c r="F47">
-        <v>466.7</v>
+        <v>466.71</v>
       </c>
       <c r="G47">
         <v>201</v>
@@ -3451,7 +3451,7 @@
         <v>14.26</v>
       </c>
       <c r="F49">
-        <v>369.1</v>
+        <v>369.14</v>
       </c>
       <c r="G49">
         <v>225</v>
@@ -3501,7 +3501,7 @@
         <v>20.51</v>
       </c>
       <c r="F51">
-        <v>348.7</v>
+        <v>348.74</v>
       </c>
       <c r="G51">
         <v>269</v>
@@ -3526,7 +3526,7 @@
         <v>35.77</v>
       </c>
       <c r="F52">
-        <v>107.3</v>
+        <v>107.32</v>
       </c>
       <c r="G52">
         <v>15</v>
@@ -3551,7 +3551,7 @@
         <v>27.52</v>
       </c>
       <c r="F53">
-        <v>137.6</v>
+        <v>137.59</v>
       </c>
       <c r="G53">
         <v>32</v>
@@ -3564,7 +3564,7 @@
         </is>
       </c>
       <c r="B54">
-        <v>10002.78265306123</v>
+        <v>10002.78</v>
       </c>
       <c r="C54">
         <v>43.62</v>
@@ -3576,7 +3576,7 @@
         <v>13.38</v>
       </c>
       <c r="F54">
-        <v>375.7</v>
+        <v>375.72</v>
       </c>
       <c r="G54">
         <v>131</v>
@@ -3592,16 +3592,16 @@
         <v>31</v>
       </c>
       <c r="C55">
-        <v>4.355</v>
+        <v>4.35</v>
       </c>
       <c r="D55">
-        <v>1.618</v>
+        <v>1.62</v>
       </c>
       <c r="E55">
-        <v>3.102</v>
+        <v>3.1</v>
       </c>
       <c r="F55">
-        <v>6.204</v>
+        <v>6.2</v>
       </c>
       <c r="G55">
         <v>4</v>
@@ -3626,7 +3626,7 @@
         <v>35.77</v>
       </c>
       <c r="F56">
-        <v>178.9</v>
+        <v>178.87</v>
       </c>
       <c r="G56">
         <v>4</v>
@@ -3648,7 +3648,7 @@
         <v>18.9</v>
       </c>
       <c r="E57">
-        <v>5.754</v>
+        <v>5.75</v>
       </c>
       <c r="F57">
         <v>79.25</v>
@@ -3667,16 +3667,16 @@
         <v>3432</v>
       </c>
       <c r="C58">
-        <v>446.6</v>
+        <v>446.58</v>
       </c>
       <c r="D58">
-        <v>441.7</v>
+        <v>441.66</v>
       </c>
       <c r="E58">
         <v>61.57</v>
       </c>
       <c r="F58">
-        <v>1041</v>
+        <v>1040.71</v>
       </c>
       <c r="G58">
         <v>4</v>
@@ -3695,13 +3695,13 @@
         <v>128.4</v>
       </c>
       <c r="D59">
-        <v>273.1</v>
+        <v>273.12</v>
       </c>
       <c r="E59">
         <v>18.01</v>
       </c>
       <c r="F59">
-        <v>7889</v>
+        <v>7889.4</v>
       </c>
       <c r="G59">
         <v>6131</v>
@@ -3726,7 +3726,7 @@
         <v>18.01</v>
       </c>
       <c r="F60">
-        <v>328.7</v>
+        <v>328.72</v>
       </c>
       <c r="G60">
         <v>15</v>
@@ -3745,7 +3745,7 @@
         <v>78.52</v>
       </c>
       <c r="D61">
-        <v>161.4</v>
+        <v>161.38</v>
       </c>
       <c r="E61">
         <v>18.01</v>
@@ -3770,13 +3770,13 @@
         <v>97.11</v>
       </c>
       <c r="D62">
-        <v>164.1</v>
+        <v>164.14</v>
       </c>
       <c r="E62">
         <v>21.51</v>
       </c>
       <c r="F62">
-        <v>2111</v>
+        <v>2110.55</v>
       </c>
       <c r="G62">
         <v>919</v>
@@ -3792,7 +3792,7 @@
         <v>630</v>
       </c>
       <c r="C63">
-        <v>105.1</v>
+        <v>105.07</v>
       </c>
       <c r="D63">
         <v>96.3</v>
@@ -3801,7 +3801,7 @@
         <v>21.01</v>
       </c>
       <c r="F63">
-        <v>210.1</v>
+        <v>210.14</v>
       </c>
       <c r="G63">
         <v>3</v>
@@ -3826,7 +3826,7 @@
         <v>63.04</v>
       </c>
       <c r="F64">
-        <v>183</v>
+        <v>182.99</v>
       </c>
       <c r="G64">
         <v>5</v>
@@ -3839,19 +3839,19 @@
         </is>
       </c>
       <c r="B65">
-        <v>483637.2158163266</v>
+        <v>483637.22</v>
       </c>
       <c r="C65">
         <v>57.7</v>
       </c>
       <c r="D65">
-        <v>104.1</v>
+        <v>104.07</v>
       </c>
       <c r="E65">
         <v>13.38</v>
       </c>
       <c r="F65">
-        <v>2442</v>
+        <v>2442.19</v>
       </c>
       <c r="G65">
         <v>4566</v>
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="B66">
-        <v>5379.791666666667</v>
+        <v>5379.79</v>
       </c>
       <c r="C66">
         <v>53.42</v>
@@ -3876,7 +3876,7 @@
         <v>15.38</v>
       </c>
       <c r="F66">
-        <v>236.4</v>
+        <v>236.39</v>
       </c>
       <c r="G66">
         <v>54</v>
@@ -3895,7 +3895,7 @@
         <v>25.18</v>
       </c>
       <c r="D67">
-        <v>9.673</v>
+        <v>9.67</v>
       </c>
       <c r="E67">
         <v>18.01</v>
@@ -3920,13 +3920,13 @@
         <v>98.33</v>
       </c>
       <c r="D68">
-        <v>210.5</v>
+        <v>210.49</v>
       </c>
       <c r="E68">
         <v>21.51</v>
       </c>
       <c r="F68">
-        <v>6282</v>
+        <v>6282.3</v>
       </c>
       <c r="G68">
         <v>2373</v>
@@ -3945,13 +3945,13 @@
         <v>156.2</v>
       </c>
       <c r="D69">
-        <v>283.9</v>
+        <v>283.93</v>
       </c>
       <c r="E69">
         <v>27.52</v>
       </c>
       <c r="F69">
-        <v>1071</v>
+        <v>1071.4</v>
       </c>
       <c r="G69">
         <v>13</v>
@@ -3973,10 +3973,10 @@
         <v>24.46</v>
       </c>
       <c r="E70">
-        <v>9.605</v>
+        <v>9.6</v>
       </c>
       <c r="F70">
-        <v>109.9</v>
+        <v>109.93</v>
       </c>
       <c r="G70">
         <v>28</v>

--- a/CPRD Raw Analysis/Results/Output_costs_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_costs_Raw.xlsx
@@ -11,6 +11,10 @@
     <sheet name="all_cost_summary_statistics" sheetId="2" r:id="rId2"/>
     <sheet name="user_only_cost_summary" sheetId="3" r:id="rId3"/>
     <sheet name="all_cost_summary" sheetId="4" r:id="rId4"/>
+    <sheet name="user_cost_summary_statistics_" sheetId="5" r:id="rId5"/>
+    <sheet name="all_cost_summary_statistics_r" sheetId="6" r:id="rId6"/>
+    <sheet name="user_only_cost_summary_reduce" sheetId="7" r:id="rId7"/>
+    <sheet name="all_cost_summary_reduced" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3210,7 +3214,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Not_clinically_relevant</t>
+          <t>Not Clinically Relevant</t>
         </is>
       </c>
       <c r="B40">
@@ -3980,6 +3984,415 @@
       </c>
       <c r="G70">
         <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>mean_visit_cost_per_year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>min_visit_cost_per_year</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>max_visit_cost_per_year</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sd_visit_cost_per_year</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>median_visit_cost_per_year</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>lower_q_visits_cost_per_year</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>upper_q_visits_cost_per_year</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>549.77</v>
+      </c>
+      <c r="B2">
+        <v>3.1</v>
+      </c>
+      <c r="C2">
+        <v>16654.7</v>
+      </c>
+      <c r="D2">
+        <v>672.3099999999999</v>
+      </c>
+      <c r="E2">
+        <v>458.9</v>
+      </c>
+      <c r="F2">
+        <v>261.78</v>
+      </c>
+      <c r="G2">
+        <v>787.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>mean_visit_cost_per_year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>min_visit_cost_per_year</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>max_visit_cost_per_year</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sd_visit_cost_per_year</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>median_visit_cost_per_year</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>lower_q_visits_cost_per_year</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>upper_q_visits_cost_per_year</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>544.85</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>16654.7</v>
+      </c>
+      <c r="D2">
+        <v>671.36</v>
+      </c>
+      <c r="E2">
+        <v>450.31</v>
+      </c>
+      <c r="F2">
+        <v>252.17</v>
+      </c>
+      <c r="G2">
+        <v>774.53</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>specialty_reduced</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>tot_visits_costs</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>mean_visits_per_year</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sd_cost_visits_per_year</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>min_cost_visits_per_year</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>max_cost_visits_per_year</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>num_subjects_visited</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>General Practitioner</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>20184912</v>
+      </c>
+      <c r="C2">
+        <v>480.4</v>
+      </c>
+      <c r="D2">
+        <v>594.76</v>
+      </c>
+      <c r="E2">
+        <v>18.01</v>
+      </c>
+      <c r="F2">
+        <v>13149</v>
+      </c>
+      <c r="G2">
+        <v>24444</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Nurse</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>1699248.56</v>
+      </c>
+      <c r="C3">
+        <v>78.81999999999999</v>
+      </c>
+      <c r="D3">
+        <v>156.37</v>
+      </c>
+      <c r="E3">
+        <v>9.6</v>
+      </c>
+      <c r="F3">
+        <v>6282.3</v>
+      </c>
+      <c r="G3">
+        <v>11836</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>1309950.52</v>
+      </c>
+      <c r="C4">
+        <v>94.08</v>
+      </c>
+      <c r="D4">
+        <v>286.17</v>
+      </c>
+      <c r="E4">
+        <v>3.1</v>
+      </c>
+      <c r="F4">
+        <v>14022.79</v>
+      </c>
+      <c r="G4">
+        <v>7908</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>specialty_reduced</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>tot_visits_costs</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>mean_visits_per_year</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sd_cost_visits_per_year</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>min_cost_visits_per_year</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>max_cost_visits_per_year</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>num_subjects_visited</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>General Practitioner</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>20184912</v>
+      </c>
+      <c r="C2">
+        <v>480.4</v>
+      </c>
+      <c r="D2">
+        <v>594.76</v>
+      </c>
+      <c r="E2">
+        <v>18.01</v>
+      </c>
+      <c r="F2">
+        <v>13149</v>
+      </c>
+      <c r="G2">
+        <v>24444</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Not Clinically Relevant</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Nurse</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>1699248.56</v>
+      </c>
+      <c r="C4">
+        <v>78.81999999999999</v>
+      </c>
+      <c r="D4">
+        <v>156.37</v>
+      </c>
+      <c r="E4">
+        <v>9.6</v>
+      </c>
+      <c r="F4">
+        <v>6282.3</v>
+      </c>
+      <c r="G4">
+        <v>11836</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>1309950.52</v>
+      </c>
+      <c r="C5">
+        <v>94.08</v>
+      </c>
+      <c r="D5">
+        <v>286.17</v>
+      </c>
+      <c r="E5">
+        <v>3.1</v>
+      </c>
+      <c r="F5">
+        <v>14022.79</v>
+      </c>
+      <c r="G5">
+        <v>7908</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_costs_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_costs_Raw.xlsx
@@ -400,25 +400,25 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>550.04</v>
+        <v>629.48</v>
       </c>
       <c r="B2">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>16654.7</v>
+        <v>18846.2</v>
       </c>
       <c r="D2">
-        <v>674.24</v>
+        <v>768.8200000000001</v>
       </c>
       <c r="E2">
-        <v>459.69</v>
+        <v>525.36</v>
       </c>
       <c r="F2">
-        <v>261.78</v>
+        <v>297.55</v>
       </c>
       <c r="G2">
-        <v>788.72</v>
+        <v>903.62</v>
       </c>
     </row>
   </sheetData>
@@ -470,25 +470,25 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>545.12</v>
+        <v>623.85</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>16654.7</v>
+        <v>18846.2</v>
       </c>
       <c r="D2">
-        <v>673.27</v>
+        <v>767.76</v>
       </c>
       <c r="E2">
-        <v>450.31</v>
+        <v>514.63</v>
       </c>
       <c r="F2">
-        <v>252.17</v>
+        <v>286.98</v>
       </c>
       <c r="G2">
-        <v>774.53</v>
+        <v>890.39</v>
       </c>
     </row>
   </sheetData>
@@ -570,19 +570,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>8195</v>
+        <v>7897</v>
       </c>
       <c r="C3">
-        <v>217.8</v>
+        <v>209.88</v>
       </c>
       <c r="D3">
-        <v>365.23</v>
+        <v>351.95</v>
       </c>
       <c r="E3">
-        <v>27.52</v>
+        <v>26.52</v>
       </c>
       <c r="F3">
-        <v>1434.91</v>
+        <v>1382.73</v>
       </c>
       <c r="G3">
         <v>22</v>
@@ -595,19 +595,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="C4">
-        <v>62.02</v>
+        <v>59.77</v>
       </c>
       <c r="D4">
-        <v>45.12</v>
+        <v>43.48</v>
       </c>
       <c r="E4">
-        <v>27.52</v>
+        <v>26.52</v>
       </c>
       <c r="F4">
-        <v>137.59</v>
+        <v>132.59</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -620,19 +620,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>880</v>
+        <v>848</v>
       </c>
       <c r="C5">
-        <v>73.38</v>
+        <v>70.72</v>
       </c>
       <c r="D5">
-        <v>41.43</v>
+        <v>39.92</v>
       </c>
       <c r="E5">
-        <v>27.52</v>
+        <v>26.52</v>
       </c>
       <c r="F5">
-        <v>137.59</v>
+        <v>132.59</v>
       </c>
       <c r="G5">
         <v>6</v>
@@ -645,19 +645,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>12204.44</v>
+        <v>12592.84</v>
       </c>
       <c r="C6">
-        <v>41.45</v>
+        <v>42.77</v>
       </c>
       <c r="D6">
-        <v>53.31</v>
+        <v>55.01</v>
       </c>
       <c r="E6">
-        <v>15.38</v>
+        <v>15.87</v>
       </c>
       <c r="F6">
-        <v>337.41</v>
+        <v>348.15</v>
       </c>
       <c r="G6">
         <v>157</v>
@@ -670,19 +670,19 @@
         </is>
       </c>
       <c r="B7">
-        <v>105012</v>
+        <v>122514</v>
       </c>
       <c r="C7">
-        <v>99.45</v>
+        <v>116.02</v>
       </c>
       <c r="D7">
-        <v>201.08</v>
+        <v>234.6</v>
       </c>
       <c r="E7">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F7">
-        <v>2858.48</v>
+        <v>3334.89</v>
       </c>
       <c r="G7">
         <v>590</v>
@@ -720,19 +720,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>9283.98</v>
+        <v>9579.440000000001</v>
       </c>
       <c r="C9">
-        <v>54.41</v>
+        <v>56.14</v>
       </c>
       <c r="D9">
-        <v>127.02</v>
+        <v>131.07</v>
       </c>
       <c r="E9">
-        <v>15.38</v>
+        <v>15.87</v>
       </c>
       <c r="F9">
-        <v>1063.74</v>
+        <v>1097.6</v>
       </c>
       <c r="G9">
         <v>92</v>
@@ -745,16 +745,16 @@
         </is>
       </c>
       <c r="B10">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C10">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="E10">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F10">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -767,19 +767,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>470.46</v>
+        <v>348.3</v>
       </c>
       <c r="C11">
-        <v>187.8</v>
+        <v>139.03</v>
       </c>
       <c r="D11">
-        <v>382.38</v>
+        <v>283.09</v>
       </c>
       <c r="E11">
-        <v>78.45999999999999</v>
+        <v>58.09</v>
       </c>
       <c r="F11">
-        <v>619.23</v>
+        <v>458.44</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -792,19 +792,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>1890</v>
+        <v>1980</v>
       </c>
       <c r="C12">
-        <v>50.12</v>
+        <v>52.51</v>
       </c>
       <c r="D12">
-        <v>72.81999999999999</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="E12">
-        <v>21.01</v>
+        <v>22.02</v>
       </c>
       <c r="F12">
-        <v>359.89</v>
+        <v>377.03</v>
       </c>
       <c r="G12">
         <v>21</v>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C14">
-        <v>36.61</v>
+        <v>35.28</v>
       </c>
       <c r="D14">
-        <v>46.47</v>
+        <v>44.78</v>
       </c>
       <c r="E14">
-        <v>27.52</v>
+        <v>26.52</v>
       </c>
       <c r="F14">
-        <v>108</v>
+        <v>104.08</v>
       </c>
       <c r="G14">
         <v>3</v>
@@ -867,19 +867,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="C15">
-        <v>38.53</v>
+        <v>37.13</v>
       </c>
       <c r="D15">
-        <v>15.07</v>
+        <v>14.52</v>
       </c>
       <c r="E15">
-        <v>27.52</v>
+        <v>26.52</v>
       </c>
       <c r="F15">
-        <v>55.04</v>
+        <v>53.04</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -892,19 +892,19 @@
         </is>
       </c>
       <c r="B16">
-        <v>252</v>
+        <v>294</v>
       </c>
       <c r="C16">
-        <v>21.75</v>
+        <v>25.37</v>
       </c>
       <c r="D16">
-        <v>7.22</v>
+        <v>8.42</v>
       </c>
       <c r="E16">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F16">
-        <v>36.02</v>
+        <v>42.03</v>
       </c>
       <c r="G16">
         <v>6</v>
@@ -917,19 +917,19 @@
         </is>
       </c>
       <c r="B17">
-        <v>5004</v>
+        <v>5838</v>
       </c>
       <c r="C17">
-        <v>55.53</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="D17">
-        <v>40.31</v>
+        <v>47.03</v>
       </c>
       <c r="E17">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F17">
-        <v>180.12</v>
+        <v>210.14</v>
       </c>
       <c r="G17">
         <v>46</v>
@@ -942,19 +942,19 @@
         </is>
       </c>
       <c r="B18">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C18">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F18">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="B22">
-        <v>2135628</v>
+        <v>2491566</v>
       </c>
       <c r="C22">
-        <v>99.48</v>
+        <v>116.06</v>
       </c>
       <c r="D22">
-        <v>192.62</v>
+        <v>224.73</v>
       </c>
       <c r="E22">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F22">
-        <v>6712.19</v>
+        <v>7830.88</v>
       </c>
       <c r="G22">
         <v>11772</v>
@@ -1117,19 +1117,19 @@
         </is>
       </c>
       <c r="B25">
-        <v>8928</v>
+        <v>10416</v>
       </c>
       <c r="C25">
-        <v>120.46</v>
+        <v>140.54</v>
       </c>
       <c r="D25">
-        <v>304.22</v>
+        <v>354.93</v>
       </c>
       <c r="E25">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F25">
-        <v>1948</v>
+        <v>2272.67</v>
       </c>
       <c r="G25">
         <v>42</v>
@@ -1142,19 +1142,19 @@
         </is>
       </c>
       <c r="B26">
-        <v>4510</v>
+        <v>4290</v>
       </c>
       <c r="C26">
-        <v>32.63</v>
+        <v>31.04</v>
       </c>
       <c r="D26">
-        <v>44.83</v>
+        <v>42.64</v>
       </c>
       <c r="E26">
-        <v>20.51</v>
+        <v>19.51</v>
       </c>
       <c r="F26">
-        <v>315.27</v>
+        <v>299.89</v>
       </c>
       <c r="G26">
         <v>76</v>
@@ -1167,16 +1167,16 @@
         </is>
       </c>
       <c r="B27">
-        <v>50</v>
+        <v>41.5</v>
       </c>
       <c r="C27">
-        <v>25.02</v>
+        <v>20.76</v>
       </c>
       <c r="E27">
-        <v>25.02</v>
+        <v>20.76</v>
       </c>
       <c r="F27">
-        <v>25.02</v>
+        <v>20.76</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -1189,16 +1189,16 @@
         </is>
       </c>
       <c r="B28">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C28">
-        <v>20.51</v>
+        <v>19.51</v>
       </c>
       <c r="E28">
-        <v>20.51</v>
+        <v>19.51</v>
       </c>
       <c r="F28">
-        <v>20.51</v>
+        <v>19.51</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1236,19 +1236,19 @@
         </is>
       </c>
       <c r="B30">
-        <v>602532</v>
+        <v>702954</v>
       </c>
       <c r="C30">
-        <v>60.36</v>
+        <v>70.42</v>
       </c>
       <c r="D30">
-        <v>160.38</v>
+        <v>187.11</v>
       </c>
       <c r="E30">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F30">
-        <v>5259.6</v>
+        <v>6136.2</v>
       </c>
       <c r="G30">
         <v>5512</v>
@@ -1261,19 +1261,19 @@
         </is>
       </c>
       <c r="B31">
-        <v>15066072</v>
+        <v>17577084</v>
       </c>
       <c r="C31">
-        <v>364.56</v>
+        <v>425.32</v>
       </c>
       <c r="D31">
-        <v>494.33</v>
+        <v>576.72</v>
       </c>
       <c r="E31">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F31">
-        <v>13149</v>
+        <v>15340.5</v>
       </c>
       <c r="G31">
         <v>23947</v>
@@ -1311,19 +1311,19 @@
         </is>
       </c>
       <c r="B33">
-        <v>774</v>
+        <v>756</v>
       </c>
       <c r="C33">
-        <v>83</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="D33">
-        <v>97.09</v>
+        <v>94.83</v>
       </c>
       <c r="E33">
-        <v>21.51</v>
+        <v>21.01</v>
       </c>
       <c r="F33">
-        <v>258.53</v>
+        <v>252.52</v>
       </c>
       <c r="G33">
         <v>5</v>
@@ -1336,19 +1336,19 @@
         </is>
       </c>
       <c r="B34">
-        <v>255816</v>
+        <v>298452</v>
       </c>
       <c r="C34">
-        <v>74.47</v>
+        <v>86.89</v>
       </c>
       <c r="D34">
-        <v>214.84</v>
+        <v>250.64</v>
       </c>
       <c r="E34">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F34">
-        <v>4930.88</v>
+        <v>5752.69</v>
       </c>
       <c r="G34">
         <v>1851</v>
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="B35">
-        <v>576.6</v>
+        <v>558</v>
       </c>
       <c r="C35">
-        <v>6.75</v>
+        <v>6.53</v>
       </c>
       <c r="D35">
-        <v>9.33</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="E35">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="F35">
-        <v>55.23</v>
+        <v>53.45</v>
       </c>
       <c r="G35">
         <v>47</v>
@@ -1386,19 +1386,19 @@
         </is>
       </c>
       <c r="B36">
-        <v>8382.4</v>
+        <v>8112</v>
       </c>
       <c r="C36">
-        <v>11.72</v>
+        <v>11.34</v>
       </c>
       <c r="D36">
-        <v>19.95</v>
+        <v>19.3</v>
       </c>
       <c r="E36">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="F36">
-        <v>174.2</v>
+        <v>168.58</v>
       </c>
       <c r="G36">
         <v>390</v>
@@ -1411,19 +1411,19 @@
         </is>
       </c>
       <c r="B37">
-        <v>215.19</v>
+        <v>222.04</v>
       </c>
       <c r="C37">
-        <v>17.94</v>
+        <v>18.52</v>
       </c>
       <c r="D37">
-        <v>6.28</v>
+        <v>6.48</v>
       </c>
       <c r="E37">
-        <v>15.38</v>
+        <v>15.87</v>
       </c>
       <c r="F37">
-        <v>30.76</v>
+        <v>31.74</v>
       </c>
       <c r="G37">
         <v>6</v>
@@ -1436,19 +1436,19 @@
         </is>
       </c>
       <c r="B38">
-        <v>6793.91</v>
+        <v>7010.12</v>
       </c>
       <c r="C38">
-        <v>88.98999999999999</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="D38">
-        <v>187.99</v>
+        <v>193.97</v>
       </c>
       <c r="E38">
-        <v>15.38</v>
+        <v>15.87</v>
       </c>
       <c r="F38">
-        <v>990.74</v>
+        <v>1022.27</v>
       </c>
       <c r="G38">
         <v>48</v>
@@ -1461,16 +1461,16 @@
         </is>
       </c>
       <c r="B39">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C39">
-        <v>55.04</v>
+        <v>53.04</v>
       </c>
       <c r="E39">
-        <v>55.04</v>
+        <v>53.04</v>
       </c>
       <c r="F39">
-        <v>55.04</v>
+        <v>53.04</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -1483,19 +1483,19 @@
         </is>
       </c>
       <c r="B40">
-        <v>95503</v>
+        <v>93282</v>
       </c>
       <c r="C40">
-        <v>85.98999999999999</v>
+        <v>83.98999999999999</v>
       </c>
       <c r="D40">
-        <v>132.81</v>
+        <v>129.72</v>
       </c>
       <c r="E40">
-        <v>21.51</v>
+        <v>21.01</v>
       </c>
       <c r="F40">
-        <v>1463</v>
+        <v>1428.98</v>
       </c>
       <c r="G40">
         <v>596</v>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="B42">
-        <v>321.78</v>
+        <v>394.5</v>
       </c>
       <c r="C42">
-        <v>53.67</v>
+        <v>65.8</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>53.67</v>
+        <v>65.8</v>
       </c>
       <c r="F42">
-        <v>53.67</v>
+        <v>65.8</v>
       </c>
       <c r="G42">
         <v>3</v>
@@ -1558,19 +1558,19 @@
         </is>
       </c>
       <c r="B43">
-        <v>7425</v>
+        <v>7155</v>
       </c>
       <c r="C43">
-        <v>406.72</v>
+        <v>391.93</v>
       </c>
       <c r="D43">
-        <v>1113.35</v>
+        <v>1072.87</v>
       </c>
       <c r="E43">
-        <v>192.63</v>
+        <v>185.63</v>
       </c>
       <c r="F43">
-        <v>4109.06</v>
+        <v>3959.64</v>
       </c>
       <c r="G43">
         <v>12</v>
@@ -1583,19 +1583,19 @@
         </is>
       </c>
       <c r="B44">
-        <v>14878.97</v>
+        <v>15352.48</v>
       </c>
       <c r="C44">
-        <v>59.45</v>
+        <v>61.34</v>
       </c>
       <c r="D44">
-        <v>90.67</v>
+        <v>93.56</v>
       </c>
       <c r="E44">
-        <v>15.38</v>
+        <v>15.87</v>
       </c>
       <c r="F44">
-        <v>606.4400000000001</v>
+        <v>625.74</v>
       </c>
       <c r="G44">
         <v>139</v>
@@ -1608,19 +1608,19 @@
         </is>
       </c>
       <c r="B45">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="C45">
-        <v>110.2</v>
+        <v>115.45</v>
       </c>
       <c r="D45">
-        <v>11.65</v>
+        <v>12.21</v>
       </c>
       <c r="E45">
-        <v>100.92</v>
+        <v>105.73</v>
       </c>
       <c r="F45">
-        <v>117.4</v>
+        <v>122.99</v>
       </c>
       <c r="G45">
         <v>2</v>
@@ -1633,19 +1633,19 @@
         </is>
       </c>
       <c r="B46">
-        <v>11546</v>
+        <v>11797</v>
       </c>
       <c r="C46">
-        <v>31.5</v>
+        <v>32.18</v>
       </c>
       <c r="D46">
-        <v>55.55</v>
+        <v>56.76</v>
       </c>
       <c r="E46">
-        <v>11.51</v>
+        <v>11.76</v>
       </c>
       <c r="F46">
-        <v>466.71</v>
+        <v>476.85</v>
       </c>
       <c r="G46">
         <v>201</v>
@@ -1658,19 +1658,19 @@
         </is>
       </c>
       <c r="B47">
-        <v>347.75</v>
+        <v>334.75</v>
       </c>
       <c r="C47">
-        <v>26.46</v>
+        <v>25.47</v>
       </c>
       <c r="D47">
-        <v>30.93</v>
+        <v>29.77</v>
       </c>
       <c r="E47">
-        <v>13.38</v>
+        <v>12.88</v>
       </c>
       <c r="F47">
-        <v>84.95999999999999</v>
+        <v>81.78</v>
       </c>
       <c r="G47">
         <v>8</v>
@@ -1708,19 +1708,19 @@
         </is>
       </c>
       <c r="B49">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="C49">
-        <v>30.01</v>
+        <v>31.44</v>
       </c>
       <c r="D49">
-        <v>12.1</v>
+        <v>12.68</v>
       </c>
       <c r="E49">
-        <v>21.01</v>
+        <v>22.02</v>
       </c>
       <c r="F49">
-        <v>42.03</v>
+        <v>44.03</v>
       </c>
       <c r="G49">
         <v>4</v>
@@ -1783,19 +1783,19 @@
         </is>
       </c>
       <c r="B52">
-        <v>3245</v>
+        <v>3127</v>
       </c>
       <c r="C52">
-        <v>52.5</v>
+        <v>50.6</v>
       </c>
       <c r="D52">
-        <v>30.81</v>
+        <v>29.69</v>
       </c>
       <c r="E52">
-        <v>27.52</v>
+        <v>26.52</v>
       </c>
       <c r="F52">
-        <v>137.59</v>
+        <v>132.59</v>
       </c>
       <c r="G52">
         <v>32</v>
@@ -1833,19 +1833,19 @@
         </is>
       </c>
       <c r="B54">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C54">
-        <v>4.35</v>
+        <v>4.21</v>
       </c>
       <c r="D54">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="E54">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="F54">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="G54">
         <v>4</v>
@@ -1883,19 +1883,19 @@
         </is>
       </c>
       <c r="B56">
-        <v>770.5</v>
+        <v>787.25</v>
       </c>
       <c r="C56">
-        <v>17.88</v>
+        <v>18.27</v>
       </c>
       <c r="D56">
-        <v>18.9</v>
+        <v>19.31</v>
       </c>
       <c r="E56">
-        <v>5.75</v>
+        <v>5.88</v>
       </c>
       <c r="F56">
-        <v>79.25</v>
+        <v>80.98</v>
       </c>
       <c r="G56">
         <v>24</v>
@@ -1908,19 +1908,19 @@
         </is>
       </c>
       <c r="B57">
-        <v>3432</v>
+        <v>3663</v>
       </c>
       <c r="C57">
-        <v>446.58</v>
+        <v>476.63</v>
       </c>
       <c r="D57">
-        <v>441.66</v>
+        <v>471.39</v>
       </c>
       <c r="E57">
-        <v>61.57</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="F57">
-        <v>1040.71</v>
+        <v>1110.76</v>
       </c>
       <c r="G57">
         <v>4</v>
@@ -1933,19 +1933,19 @@
         </is>
       </c>
       <c r="B58">
-        <v>1414584</v>
+        <v>1650348</v>
       </c>
       <c r="C58">
-        <v>128.4</v>
+        <v>149.81</v>
       </c>
       <c r="D58">
-        <v>273.12</v>
+        <v>318.63</v>
       </c>
       <c r="E58">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F58">
-        <v>7889.4</v>
+        <v>9204.299999999999</v>
       </c>
       <c r="G58">
         <v>6131</v>
@@ -1958,19 +1958,19 @@
         </is>
       </c>
       <c r="B59">
-        <v>1620</v>
+        <v>1890</v>
       </c>
       <c r="C59">
-        <v>68.34999999999999</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="D59">
-        <v>80.79000000000001</v>
+        <v>94.25</v>
       </c>
       <c r="E59">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F59">
-        <v>328.72</v>
+        <v>383.51</v>
       </c>
       <c r="G59">
         <v>15</v>
@@ -1983,19 +1983,19 @@
         </is>
       </c>
       <c r="B60">
-        <v>605268</v>
+        <v>706146</v>
       </c>
       <c r="C60">
-        <v>78.52</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D60">
-        <v>161.38</v>
+        <v>188.28</v>
       </c>
       <c r="E60">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F60">
-        <v>2922</v>
+        <v>3409</v>
       </c>
       <c r="G60">
         <v>4254</v>
@@ -2008,19 +2008,19 @@
         </is>
       </c>
       <c r="B61">
-        <v>164561</v>
+        <v>160734</v>
       </c>
       <c r="C61">
-        <v>97.11</v>
+        <v>94.86</v>
       </c>
       <c r="D61">
-        <v>164.14</v>
+        <v>160.33</v>
       </c>
       <c r="E61">
-        <v>21.51</v>
+        <v>21.01</v>
       </c>
       <c r="F61">
-        <v>2110.55</v>
+        <v>2061.46</v>
       </c>
       <c r="G61">
         <v>919</v>
@@ -2033,19 +2033,19 @@
         </is>
       </c>
       <c r="B62">
-        <v>630</v>
+        <v>660</v>
       </c>
       <c r="C62">
-        <v>105.07</v>
+        <v>110.08</v>
       </c>
       <c r="D62">
-        <v>96.3</v>
+        <v>100.89</v>
       </c>
       <c r="E62">
-        <v>21.01</v>
+        <v>22.02</v>
       </c>
       <c r="F62">
-        <v>210.14</v>
+        <v>220.15</v>
       </c>
       <c r="G62">
         <v>3</v>
@@ -2058,19 +2058,19 @@
         </is>
       </c>
       <c r="B63">
-        <v>798</v>
+        <v>836</v>
       </c>
       <c r="C63">
-        <v>99.98999999999999</v>
+        <v>104.75</v>
       </c>
       <c r="D63">
-        <v>48.69</v>
+        <v>51.01</v>
       </c>
       <c r="E63">
-        <v>63.04</v>
+        <v>66.05</v>
       </c>
       <c r="F63">
-        <v>182.99</v>
+        <v>191.7</v>
       </c>
       <c r="G63">
         <v>5</v>
@@ -2108,19 +2108,19 @@
         </is>
       </c>
       <c r="B65">
-        <v>5379.79</v>
+        <v>5551</v>
       </c>
       <c r="C65">
-        <v>53.42</v>
+        <v>55.12</v>
       </c>
       <c r="D65">
-        <v>50.45</v>
+        <v>52.05</v>
       </c>
       <c r="E65">
-        <v>15.38</v>
+        <v>15.87</v>
       </c>
       <c r="F65">
-        <v>236.39</v>
+        <v>243.91</v>
       </c>
       <c r="G65">
         <v>54</v>
@@ -2133,19 +2133,19 @@
         </is>
       </c>
       <c r="B66">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="C66">
-        <v>25.18</v>
+        <v>29.37</v>
       </c>
       <c r="D66">
-        <v>9.67</v>
+        <v>11.29</v>
       </c>
       <c r="E66">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F66">
-        <v>36.02</v>
+        <v>42.03</v>
       </c>
       <c r="G66">
         <v>3</v>
@@ -2158,19 +2158,19 @@
         </is>
       </c>
       <c r="B67">
-        <v>432709</v>
+        <v>422646</v>
       </c>
       <c r="C67">
-        <v>98.33</v>
+        <v>96.04000000000001</v>
       </c>
       <c r="D67">
-        <v>210.49</v>
+        <v>205.59</v>
       </c>
       <c r="E67">
-        <v>21.51</v>
+        <v>21.01</v>
       </c>
       <c r="F67">
-        <v>6282.3</v>
+        <v>6136.2</v>
       </c>
       <c r="G67">
         <v>2373</v>
@@ -2183,19 +2183,19 @@
         </is>
       </c>
       <c r="B68">
-        <v>3355</v>
+        <v>3233</v>
       </c>
       <c r="C68">
-        <v>156.2</v>
+        <v>150.52</v>
       </c>
       <c r="D68">
-        <v>283.93</v>
+        <v>273.6</v>
       </c>
       <c r="E68">
-        <v>27.52</v>
+        <v>26.52</v>
       </c>
       <c r="F68">
-        <v>1071.4</v>
+        <v>1032.44</v>
       </c>
       <c r="G68">
         <v>13</v>
@@ -2305,19 +2305,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>8195</v>
+        <v>7897</v>
       </c>
       <c r="C3">
-        <v>217.8</v>
+        <v>209.88</v>
       </c>
       <c r="D3">
-        <v>365.23</v>
+        <v>351.95</v>
       </c>
       <c r="E3">
-        <v>27.52</v>
+        <v>26.52</v>
       </c>
       <c r="F3">
-        <v>1434.91</v>
+        <v>1382.73</v>
       </c>
       <c r="G3">
         <v>22</v>
@@ -2330,19 +2330,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="C4">
-        <v>62.02</v>
+        <v>59.77</v>
       </c>
       <c r="D4">
-        <v>45.12</v>
+        <v>43.48</v>
       </c>
       <c r="E4">
-        <v>27.52</v>
+        <v>26.52</v>
       </c>
       <c r="F4">
-        <v>137.59</v>
+        <v>132.59</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -2355,19 +2355,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>880</v>
+        <v>848</v>
       </c>
       <c r="C5">
-        <v>73.38</v>
+        <v>70.72</v>
       </c>
       <c r="D5">
-        <v>41.43</v>
+        <v>39.92</v>
       </c>
       <c r="E5">
-        <v>27.52</v>
+        <v>26.52</v>
       </c>
       <c r="F5">
-        <v>137.59</v>
+        <v>132.59</v>
       </c>
       <c r="G5">
         <v>6</v>
@@ -2380,19 +2380,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>12204.44</v>
+        <v>12592.84</v>
       </c>
       <c r="C6">
-        <v>41.45</v>
+        <v>42.77</v>
       </c>
       <c r="D6">
-        <v>53.31</v>
+        <v>55.01</v>
       </c>
       <c r="E6">
-        <v>15.38</v>
+        <v>15.87</v>
       </c>
       <c r="F6">
-        <v>337.41</v>
+        <v>348.15</v>
       </c>
       <c r="G6">
         <v>157</v>
@@ -2405,19 +2405,19 @@
         </is>
       </c>
       <c r="B7">
-        <v>105012</v>
+        <v>122514</v>
       </c>
       <c r="C7">
-        <v>99.45</v>
+        <v>116.02</v>
       </c>
       <c r="D7">
-        <v>201.08</v>
+        <v>234.6</v>
       </c>
       <c r="E7">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F7">
-        <v>2858.48</v>
+        <v>3334.89</v>
       </c>
       <c r="G7">
         <v>590</v>
@@ -2455,19 +2455,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>9283.98</v>
+        <v>9579.440000000001</v>
       </c>
       <c r="C9">
-        <v>54.41</v>
+        <v>56.14</v>
       </c>
       <c r="D9">
-        <v>127.02</v>
+        <v>131.07</v>
       </c>
       <c r="E9">
-        <v>15.38</v>
+        <v>15.87</v>
       </c>
       <c r="F9">
-        <v>1063.74</v>
+        <v>1097.6</v>
       </c>
       <c r="G9">
         <v>92</v>
@@ -2480,16 +2480,16 @@
         </is>
       </c>
       <c r="B10">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C10">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="E10">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F10">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -2502,19 +2502,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>470.46</v>
+        <v>348.3</v>
       </c>
       <c r="C11">
-        <v>187.8</v>
+        <v>139.03</v>
       </c>
       <c r="D11">
-        <v>382.38</v>
+        <v>283.09</v>
       </c>
       <c r="E11">
-        <v>78.45999999999999</v>
+        <v>58.09</v>
       </c>
       <c r="F11">
-        <v>619.23</v>
+        <v>458.44</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -2527,19 +2527,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>1890</v>
+        <v>1980</v>
       </c>
       <c r="C12">
-        <v>50.12</v>
+        <v>52.51</v>
       </c>
       <c r="D12">
-        <v>72.81999999999999</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="E12">
-        <v>21.01</v>
+        <v>22.02</v>
       </c>
       <c r="F12">
-        <v>359.89</v>
+        <v>377.03</v>
       </c>
       <c r="G12">
         <v>21</v>
@@ -2577,19 +2577,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C14">
-        <v>36.61</v>
+        <v>35.28</v>
       </c>
       <c r="D14">
-        <v>46.47</v>
+        <v>44.78</v>
       </c>
       <c r="E14">
-        <v>27.52</v>
+        <v>26.52</v>
       </c>
       <c r="F14">
-        <v>108</v>
+        <v>104.08</v>
       </c>
       <c r="G14">
         <v>3</v>
@@ -2602,19 +2602,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="C15">
-        <v>38.53</v>
+        <v>37.13</v>
       </c>
       <c r="D15">
-        <v>15.07</v>
+        <v>14.52</v>
       </c>
       <c r="E15">
-        <v>27.52</v>
+        <v>26.52</v>
       </c>
       <c r="F15">
-        <v>55.04</v>
+        <v>53.04</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -2627,19 +2627,19 @@
         </is>
       </c>
       <c r="B16">
-        <v>252</v>
+        <v>294</v>
       </c>
       <c r="C16">
-        <v>21.75</v>
+        <v>25.37</v>
       </c>
       <c r="D16">
-        <v>7.22</v>
+        <v>8.42</v>
       </c>
       <c r="E16">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F16">
-        <v>36.02</v>
+        <v>42.03</v>
       </c>
       <c r="G16">
         <v>6</v>
@@ -2652,19 +2652,19 @@
         </is>
       </c>
       <c r="B17">
-        <v>5004</v>
+        <v>5838</v>
       </c>
       <c r="C17">
-        <v>55.53</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="D17">
-        <v>40.31</v>
+        <v>47.03</v>
       </c>
       <c r="E17">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F17">
-        <v>180.12</v>
+        <v>210.14</v>
       </c>
       <c r="G17">
         <v>46</v>
@@ -2677,19 +2677,19 @@
         </is>
       </c>
       <c r="B18">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C18">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F18">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -2777,19 +2777,19 @@
         </is>
       </c>
       <c r="B22">
-        <v>2135628</v>
+        <v>2491566</v>
       </c>
       <c r="C22">
-        <v>99.48</v>
+        <v>116.06</v>
       </c>
       <c r="D22">
-        <v>192.62</v>
+        <v>224.73</v>
       </c>
       <c r="E22">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F22">
-        <v>6712.19</v>
+        <v>7830.88</v>
       </c>
       <c r="G22">
         <v>11772</v>
@@ -2852,19 +2852,19 @@
         </is>
       </c>
       <c r="B25">
-        <v>8928</v>
+        <v>10416</v>
       </c>
       <c r="C25">
-        <v>120.46</v>
+        <v>140.54</v>
       </c>
       <c r="D25">
-        <v>304.22</v>
+        <v>354.93</v>
       </c>
       <c r="E25">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F25">
-        <v>1948</v>
+        <v>2272.67</v>
       </c>
       <c r="G25">
         <v>42</v>
@@ -2877,19 +2877,19 @@
         </is>
       </c>
       <c r="B26">
-        <v>4510</v>
+        <v>4290</v>
       </c>
       <c r="C26">
-        <v>32.63</v>
+        <v>31.04</v>
       </c>
       <c r="D26">
-        <v>44.83</v>
+        <v>42.64</v>
       </c>
       <c r="E26">
-        <v>20.51</v>
+        <v>19.51</v>
       </c>
       <c r="F26">
-        <v>315.27</v>
+        <v>299.89</v>
       </c>
       <c r="G26">
         <v>76</v>
@@ -2902,16 +2902,16 @@
         </is>
       </c>
       <c r="B27">
-        <v>50</v>
+        <v>41.5</v>
       </c>
       <c r="C27">
-        <v>25.02</v>
+        <v>20.76</v>
       </c>
       <c r="E27">
-        <v>25.02</v>
+        <v>20.76</v>
       </c>
       <c r="F27">
-        <v>25.02</v>
+        <v>20.76</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2924,16 +2924,16 @@
         </is>
       </c>
       <c r="B28">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C28">
-        <v>20.51</v>
+        <v>19.51</v>
       </c>
       <c r="E28">
-        <v>20.51</v>
+        <v>19.51</v>
       </c>
       <c r="F28">
-        <v>20.51</v>
+        <v>19.51</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2971,19 +2971,19 @@
         </is>
       </c>
       <c r="B30">
-        <v>602532</v>
+        <v>702954</v>
       </c>
       <c r="C30">
-        <v>60.36</v>
+        <v>70.42</v>
       </c>
       <c r="D30">
-        <v>160.38</v>
+        <v>187.11</v>
       </c>
       <c r="E30">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F30">
-        <v>5259.6</v>
+        <v>6136.2</v>
       </c>
       <c r="G30">
         <v>5512</v>
@@ -2996,19 +2996,19 @@
         </is>
       </c>
       <c r="B31">
-        <v>15066072</v>
+        <v>17577084</v>
       </c>
       <c r="C31">
-        <v>364.56</v>
+        <v>425.32</v>
       </c>
       <c r="D31">
-        <v>494.33</v>
+        <v>576.72</v>
       </c>
       <c r="E31">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F31">
-        <v>13149</v>
+        <v>15340.5</v>
       </c>
       <c r="G31">
         <v>23947</v>
@@ -3046,19 +3046,19 @@
         </is>
       </c>
       <c r="B33">
-        <v>774</v>
+        <v>756</v>
       </c>
       <c r="C33">
-        <v>83</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="D33">
-        <v>97.09</v>
+        <v>94.83</v>
       </c>
       <c r="E33">
-        <v>21.51</v>
+        <v>21.01</v>
       </c>
       <c r="F33">
-        <v>258.53</v>
+        <v>252.52</v>
       </c>
       <c r="G33">
         <v>5</v>
@@ -3071,19 +3071,19 @@
         </is>
       </c>
       <c r="B34">
-        <v>255816</v>
+        <v>298452</v>
       </c>
       <c r="C34">
-        <v>74.47</v>
+        <v>86.89</v>
       </c>
       <c r="D34">
-        <v>214.84</v>
+        <v>250.64</v>
       </c>
       <c r="E34">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F34">
-        <v>4930.88</v>
+        <v>5752.69</v>
       </c>
       <c r="G34">
         <v>1851</v>
@@ -3096,19 +3096,19 @@
         </is>
       </c>
       <c r="B35">
-        <v>576.6</v>
+        <v>558</v>
       </c>
       <c r="C35">
-        <v>6.75</v>
+        <v>6.53</v>
       </c>
       <c r="D35">
-        <v>9.33</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="E35">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="F35">
-        <v>55.23</v>
+        <v>53.45</v>
       </c>
       <c r="G35">
         <v>47</v>
@@ -3121,19 +3121,19 @@
         </is>
       </c>
       <c r="B36">
-        <v>8382.4</v>
+        <v>8112</v>
       </c>
       <c r="C36">
-        <v>11.72</v>
+        <v>11.34</v>
       </c>
       <c r="D36">
-        <v>19.95</v>
+        <v>19.3</v>
       </c>
       <c r="E36">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="F36">
-        <v>174.2</v>
+        <v>168.58</v>
       </c>
       <c r="G36">
         <v>390</v>
@@ -3146,19 +3146,19 @@
         </is>
       </c>
       <c r="B37">
-        <v>215.19</v>
+        <v>222.04</v>
       </c>
       <c r="C37">
-        <v>17.94</v>
+        <v>18.52</v>
       </c>
       <c r="D37">
-        <v>6.28</v>
+        <v>6.48</v>
       </c>
       <c r="E37">
-        <v>15.38</v>
+        <v>15.87</v>
       </c>
       <c r="F37">
-        <v>30.76</v>
+        <v>31.74</v>
       </c>
       <c r="G37">
         <v>6</v>
@@ -3171,19 +3171,19 @@
         </is>
       </c>
       <c r="B38">
-        <v>6793.91</v>
+        <v>7010.12</v>
       </c>
       <c r="C38">
-        <v>88.98999999999999</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="D38">
-        <v>187.99</v>
+        <v>193.97</v>
       </c>
       <c r="E38">
-        <v>15.38</v>
+        <v>15.87</v>
       </c>
       <c r="F38">
-        <v>990.74</v>
+        <v>1022.27</v>
       </c>
       <c r="G38">
         <v>48</v>
@@ -3196,16 +3196,16 @@
         </is>
       </c>
       <c r="B39">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C39">
-        <v>55.04</v>
+        <v>53.04</v>
       </c>
       <c r="E39">
-        <v>55.04</v>
+        <v>53.04</v>
       </c>
       <c r="F39">
-        <v>55.04</v>
+        <v>53.04</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="B41">
-        <v>95503</v>
+        <v>93282</v>
       </c>
       <c r="C41">
-        <v>85.98999999999999</v>
+        <v>83.98999999999999</v>
       </c>
       <c r="D41">
-        <v>132.81</v>
+        <v>129.72</v>
       </c>
       <c r="E41">
-        <v>21.51</v>
+        <v>21.01</v>
       </c>
       <c r="F41">
-        <v>1463</v>
+        <v>1428.98</v>
       </c>
       <c r="G41">
         <v>596</v>
@@ -3293,19 +3293,19 @@
         </is>
       </c>
       <c r="B43">
-        <v>321.78</v>
+        <v>394.5</v>
       </c>
       <c r="C43">
-        <v>53.67</v>
+        <v>65.8</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>53.67</v>
+        <v>65.8</v>
       </c>
       <c r="F43">
-        <v>53.67</v>
+        <v>65.8</v>
       </c>
       <c r="G43">
         <v>3</v>
@@ -3318,19 +3318,19 @@
         </is>
       </c>
       <c r="B44">
-        <v>7425</v>
+        <v>7155</v>
       </c>
       <c r="C44">
-        <v>406.72</v>
+        <v>391.93</v>
       </c>
       <c r="D44">
-        <v>1113.35</v>
+        <v>1072.87</v>
       </c>
       <c r="E44">
-        <v>192.63</v>
+        <v>185.63</v>
       </c>
       <c r="F44">
-        <v>4109.06</v>
+        <v>3959.64</v>
       </c>
       <c r="G44">
         <v>12</v>
@@ -3343,19 +3343,19 @@
         </is>
       </c>
       <c r="B45">
-        <v>14878.97</v>
+        <v>15352.48</v>
       </c>
       <c r="C45">
-        <v>59.45</v>
+        <v>61.34</v>
       </c>
       <c r="D45">
-        <v>90.67</v>
+        <v>93.56</v>
       </c>
       <c r="E45">
-        <v>15.38</v>
+        <v>15.87</v>
       </c>
       <c r="F45">
-        <v>606.4400000000001</v>
+        <v>625.74</v>
       </c>
       <c r="G45">
         <v>139</v>
@@ -3368,19 +3368,19 @@
         </is>
       </c>
       <c r="B46">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="C46">
-        <v>110.2</v>
+        <v>115.45</v>
       </c>
       <c r="D46">
-        <v>11.65</v>
+        <v>12.21</v>
       </c>
       <c r="E46">
-        <v>100.92</v>
+        <v>105.73</v>
       </c>
       <c r="F46">
-        <v>117.4</v>
+        <v>122.99</v>
       </c>
       <c r="G46">
         <v>2</v>
@@ -3393,19 +3393,19 @@
         </is>
       </c>
       <c r="B47">
-        <v>11546</v>
+        <v>11797</v>
       </c>
       <c r="C47">
-        <v>31.5</v>
+        <v>32.18</v>
       </c>
       <c r="D47">
-        <v>55.55</v>
+        <v>56.76</v>
       </c>
       <c r="E47">
-        <v>11.51</v>
+        <v>11.76</v>
       </c>
       <c r="F47">
-        <v>466.71</v>
+        <v>476.85</v>
       </c>
       <c r="G47">
         <v>201</v>
@@ -3418,19 +3418,19 @@
         </is>
       </c>
       <c r="B48">
-        <v>347.75</v>
+        <v>334.75</v>
       </c>
       <c r="C48">
-        <v>26.46</v>
+        <v>25.47</v>
       </c>
       <c r="D48">
-        <v>30.93</v>
+        <v>29.77</v>
       </c>
       <c r="E48">
-        <v>13.38</v>
+        <v>12.88</v>
       </c>
       <c r="F48">
-        <v>84.95999999999999</v>
+        <v>81.78</v>
       </c>
       <c r="G48">
         <v>8</v>
@@ -3468,19 +3468,19 @@
         </is>
       </c>
       <c r="B50">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="C50">
-        <v>30.01</v>
+        <v>31.44</v>
       </c>
       <c r="D50">
-        <v>12.1</v>
+        <v>12.68</v>
       </c>
       <c r="E50">
-        <v>21.01</v>
+        <v>22.02</v>
       </c>
       <c r="F50">
-        <v>42.03</v>
+        <v>44.03</v>
       </c>
       <c r="G50">
         <v>4</v>
@@ -3543,19 +3543,19 @@
         </is>
       </c>
       <c r="B53">
-        <v>3245</v>
+        <v>3127</v>
       </c>
       <c r="C53">
-        <v>52.5</v>
+        <v>50.6</v>
       </c>
       <c r="D53">
-        <v>30.81</v>
+        <v>29.69</v>
       </c>
       <c r="E53">
-        <v>27.52</v>
+        <v>26.52</v>
       </c>
       <c r="F53">
-        <v>137.59</v>
+        <v>132.59</v>
       </c>
       <c r="G53">
         <v>32</v>
@@ -3593,19 +3593,19 @@
         </is>
       </c>
       <c r="B55">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C55">
-        <v>4.35</v>
+        <v>4.21</v>
       </c>
       <c r="D55">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="E55">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="F55">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="G55">
         <v>4</v>
@@ -3643,19 +3643,19 @@
         </is>
       </c>
       <c r="B57">
-        <v>770.5</v>
+        <v>787.25</v>
       </c>
       <c r="C57">
-        <v>17.88</v>
+        <v>18.27</v>
       </c>
       <c r="D57">
-        <v>18.9</v>
+        <v>19.31</v>
       </c>
       <c r="E57">
-        <v>5.75</v>
+        <v>5.88</v>
       </c>
       <c r="F57">
-        <v>79.25</v>
+        <v>80.98</v>
       </c>
       <c r="G57">
         <v>24</v>
@@ -3668,19 +3668,19 @@
         </is>
       </c>
       <c r="B58">
-        <v>3432</v>
+        <v>3663</v>
       </c>
       <c r="C58">
-        <v>446.58</v>
+        <v>476.63</v>
       </c>
       <c r="D58">
-        <v>441.66</v>
+        <v>471.39</v>
       </c>
       <c r="E58">
-        <v>61.57</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="F58">
-        <v>1040.71</v>
+        <v>1110.76</v>
       </c>
       <c r="G58">
         <v>4</v>
@@ -3693,19 +3693,19 @@
         </is>
       </c>
       <c r="B59">
-        <v>1414584</v>
+        <v>1650348</v>
       </c>
       <c r="C59">
-        <v>128.4</v>
+        <v>149.81</v>
       </c>
       <c r="D59">
-        <v>273.12</v>
+        <v>318.63</v>
       </c>
       <c r="E59">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F59">
-        <v>7889.4</v>
+        <v>9204.299999999999</v>
       </c>
       <c r="G59">
         <v>6131</v>
@@ -3718,19 +3718,19 @@
         </is>
       </c>
       <c r="B60">
-        <v>1620</v>
+        <v>1890</v>
       </c>
       <c r="C60">
-        <v>68.34999999999999</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="D60">
-        <v>80.79000000000001</v>
+        <v>94.25</v>
       </c>
       <c r="E60">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F60">
-        <v>328.72</v>
+        <v>383.51</v>
       </c>
       <c r="G60">
         <v>15</v>
@@ -3743,19 +3743,19 @@
         </is>
       </c>
       <c r="B61">
-        <v>605268</v>
+        <v>706146</v>
       </c>
       <c r="C61">
-        <v>78.52</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D61">
-        <v>161.38</v>
+        <v>188.28</v>
       </c>
       <c r="E61">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F61">
-        <v>2922</v>
+        <v>3409</v>
       </c>
       <c r="G61">
         <v>4254</v>
@@ -3768,19 +3768,19 @@
         </is>
       </c>
       <c r="B62">
-        <v>164561</v>
+        <v>160734</v>
       </c>
       <c r="C62">
-        <v>97.11</v>
+        <v>94.86</v>
       </c>
       <c r="D62">
-        <v>164.14</v>
+        <v>160.33</v>
       </c>
       <c r="E62">
-        <v>21.51</v>
+        <v>21.01</v>
       </c>
       <c r="F62">
-        <v>2110.55</v>
+        <v>2061.46</v>
       </c>
       <c r="G62">
         <v>919</v>
@@ -3793,19 +3793,19 @@
         </is>
       </c>
       <c r="B63">
-        <v>630</v>
+        <v>660</v>
       </c>
       <c r="C63">
-        <v>105.07</v>
+        <v>110.08</v>
       </c>
       <c r="D63">
-        <v>96.3</v>
+        <v>100.89</v>
       </c>
       <c r="E63">
-        <v>21.01</v>
+        <v>22.02</v>
       </c>
       <c r="F63">
-        <v>210.14</v>
+        <v>220.15</v>
       </c>
       <c r="G63">
         <v>3</v>
@@ -3818,19 +3818,19 @@
         </is>
       </c>
       <c r="B64">
-        <v>798</v>
+        <v>836</v>
       </c>
       <c r="C64">
-        <v>99.98999999999999</v>
+        <v>104.75</v>
       </c>
       <c r="D64">
-        <v>48.69</v>
+        <v>51.01</v>
       </c>
       <c r="E64">
-        <v>63.04</v>
+        <v>66.05</v>
       </c>
       <c r="F64">
-        <v>182.99</v>
+        <v>191.7</v>
       </c>
       <c r="G64">
         <v>5</v>
@@ -3868,19 +3868,19 @@
         </is>
       </c>
       <c r="B66">
-        <v>5379.79</v>
+        <v>5551</v>
       </c>
       <c r="C66">
-        <v>53.42</v>
+        <v>55.12</v>
       </c>
       <c r="D66">
-        <v>50.45</v>
+        <v>52.05</v>
       </c>
       <c r="E66">
-        <v>15.38</v>
+        <v>15.87</v>
       </c>
       <c r="F66">
-        <v>236.39</v>
+        <v>243.91</v>
       </c>
       <c r="G66">
         <v>54</v>
@@ -3893,19 +3893,19 @@
         </is>
       </c>
       <c r="B67">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="C67">
-        <v>25.18</v>
+        <v>29.37</v>
       </c>
       <c r="D67">
-        <v>9.67</v>
+        <v>11.29</v>
       </c>
       <c r="E67">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F67">
-        <v>36.02</v>
+        <v>42.03</v>
       </c>
       <c r="G67">
         <v>3</v>
@@ -3918,19 +3918,19 @@
         </is>
       </c>
       <c r="B68">
-        <v>432709</v>
+        <v>422646</v>
       </c>
       <c r="C68">
-        <v>98.33</v>
+        <v>96.04000000000001</v>
       </c>
       <c r="D68">
-        <v>210.49</v>
+        <v>205.59</v>
       </c>
       <c r="E68">
-        <v>21.51</v>
+        <v>21.01</v>
       </c>
       <c r="F68">
-        <v>6282.3</v>
+        <v>6136.2</v>
       </c>
       <c r="G68">
         <v>2373</v>
@@ -3943,19 +3943,19 @@
         </is>
       </c>
       <c r="B69">
-        <v>3355</v>
+        <v>3233</v>
       </c>
       <c r="C69">
-        <v>156.2</v>
+        <v>150.52</v>
       </c>
       <c r="D69">
-        <v>283.93</v>
+        <v>273.6</v>
       </c>
       <c r="E69">
-        <v>27.52</v>
+        <v>26.52</v>
       </c>
       <c r="F69">
-        <v>1071.4</v>
+        <v>1032.44</v>
       </c>
       <c r="G69">
         <v>13</v>
@@ -4035,25 +4035,25 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>549.77</v>
+        <v>629.22</v>
       </c>
       <c r="B2">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>16654.7</v>
+        <v>18846.2</v>
       </c>
       <c r="D2">
-        <v>672.3099999999999</v>
+        <v>766.88</v>
       </c>
       <c r="E2">
-        <v>458.9</v>
+        <v>525.36</v>
       </c>
       <c r="F2">
-        <v>261.78</v>
+        <v>297.16</v>
       </c>
       <c r="G2">
-        <v>787.7</v>
+        <v>902.38</v>
       </c>
     </row>
   </sheetData>
@@ -4105,25 +4105,25 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>544.85</v>
+        <v>623.59</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>16654.7</v>
+        <v>18846.2</v>
       </c>
       <c r="D2">
-        <v>671.36</v>
+        <v>765.84</v>
       </c>
       <c r="E2">
-        <v>450.31</v>
+        <v>513.95</v>
       </c>
       <c r="F2">
-        <v>252.17</v>
+        <v>286.98</v>
       </c>
       <c r="G2">
-        <v>774.53</v>
+        <v>888.6</v>
       </c>
     </row>
   </sheetData>
@@ -4180,19 +4180,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>20184912</v>
+        <v>23549064</v>
       </c>
       <c r="C2">
-        <v>480.4</v>
+        <v>560.47</v>
       </c>
       <c r="D2">
-        <v>594.76</v>
+        <v>693.89</v>
       </c>
       <c r="E2">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F2">
-        <v>13149</v>
+        <v>15340.5</v>
       </c>
       <c r="G2">
         <v>24444</v>
@@ -4205,19 +4205,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>1699248.56</v>
+        <v>1683620.97</v>
       </c>
       <c r="C3">
-        <v>78.81999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="D3">
-        <v>156.37</v>
+        <v>154.12</v>
       </c>
       <c r="E3">
         <v>9.6</v>
       </c>
       <c r="F3">
-        <v>6282.3</v>
+        <v>6136.2</v>
       </c>
       <c r="G3">
         <v>11836</v>
@@ -4230,16 +4230,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>1309950.52</v>
+        <v>1313232.94</v>
       </c>
       <c r="C4">
-        <v>94.08</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="D4">
-        <v>286.17</v>
+        <v>286.21</v>
       </c>
       <c r="E4">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>14022.79</v>
@@ -4302,19 +4302,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>20184912</v>
+        <v>23549064</v>
       </c>
       <c r="C2">
-        <v>480.4</v>
+        <v>560.47</v>
       </c>
       <c r="D2">
-        <v>594.76</v>
+        <v>693.89</v>
       </c>
       <c r="E2">
-        <v>18.01</v>
+        <v>21.01</v>
       </c>
       <c r="F2">
-        <v>13149</v>
+        <v>15340.5</v>
       </c>
       <c r="G2">
         <v>24444</v>
@@ -4352,19 +4352,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>1699248.56</v>
+        <v>1683620.97</v>
       </c>
       <c r="C4">
-        <v>78.81999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="D4">
-        <v>156.37</v>
+        <v>154.12</v>
       </c>
       <c r="E4">
         <v>9.6</v>
       </c>
       <c r="F4">
-        <v>6282.3</v>
+        <v>6136.2</v>
       </c>
       <c r="G4">
         <v>11836</v>
@@ -4377,16 +4377,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>1309950.52</v>
+        <v>1313232.94</v>
       </c>
       <c r="C5">
-        <v>94.08</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="D5">
-        <v>286.17</v>
+        <v>286.21</v>
       </c>
       <c r="E5">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="F5">
         <v>14022.79</v>

--- a/CPRD Raw Analysis/Results/Output_costs_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_costs_Raw.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -401,19 +401,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>10113.58</v>
+        <v>7804.41</v>
       </c>
       <c r="C2">
-        <v>83.84</v>
+        <v>64.7</v>
       </c>
       <c r="D2">
-        <v>119.78</v>
+        <v>92.09</v>
       </c>
       <c r="E2">
         <v>14.63</v>
       </c>
       <c r="F2">
-        <v>628.88</v>
+        <v>490.86</v>
       </c>
       <c r="G2">
         <v>81</v>
@@ -422,975 +422,775 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Assistant Practitioner</t>
+          <t>Associate Practitioner - General Practitioner</t>
         </is>
       </c>
       <c r="B3">
-        <v>644.02</v>
+        <v>89124</v>
       </c>
       <c r="C3">
-        <v>3.08</v>
+        <v>133.47</v>
       </c>
       <c r="D3">
-        <v>6.02</v>
+        <v>261.88</v>
       </c>
       <c r="E3">
-        <v>0.55</v>
+        <v>21.01</v>
       </c>
       <c r="F3">
-        <v>34.99</v>
+        <v>3334.89</v>
       </c>
       <c r="G3">
-        <v>134</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Associate Practitioner - General Practitioner</t>
+          <t>Associate Practitioner - Nurse</t>
         </is>
       </c>
       <c r="B4">
-        <v>125832</v>
+        <v>37432.5</v>
       </c>
       <c r="C4">
-        <v>188.44</v>
+        <v>38.71</v>
       </c>
       <c r="D4">
-        <v>451.05</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="E4">
-        <v>21.01</v>
+        <v>9.6</v>
       </c>
       <c r="F4">
-        <v>6336.29</v>
+        <v>855.05</v>
       </c>
       <c r="G4">
-        <v>452</v>
+        <v>627</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate Practitioner - Nurse</t>
+          <t>Associate Specialist</t>
         </is>
       </c>
       <c r="B5">
-        <v>47164.95</v>
+        <v>5612.16</v>
       </c>
       <c r="C5">
-        <v>48.78</v>
+        <v>61.97</v>
       </c>
       <c r="D5">
-        <v>106.87</v>
+        <v>153.98</v>
       </c>
       <c r="E5">
-        <v>9.6</v>
+        <v>14.63</v>
       </c>
       <c r="F5">
-        <v>1090.66</v>
+        <v>1011.43</v>
       </c>
       <c r="G5">
-        <v>627</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Associate Specialist</t>
+          <t>Chiropodist/Podiatrist</t>
         </is>
       </c>
       <c r="B6">
-        <v>5962.92</v>
+        <v>4551</v>
       </c>
       <c r="C6">
-        <v>65.84</v>
+        <v>44.34</v>
       </c>
       <c r="D6">
-        <v>168.48</v>
+        <v>48.09</v>
       </c>
       <c r="E6">
-        <v>14.63</v>
+        <v>20.51</v>
       </c>
       <c r="F6">
-        <v>1123.82</v>
+        <v>225.65</v>
       </c>
       <c r="G6">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chiropodist/Podiatrist</t>
+          <t>Clinical Psychologist</t>
         </is>
       </c>
       <c r="B7">
-        <v>4879</v>
+        <v>572</v>
       </c>
       <c r="C7">
-        <v>47.53</v>
+        <v>71.55</v>
       </c>
       <c r="D7">
-        <v>48.22</v>
+        <v>50.59</v>
       </c>
       <c r="E7">
-        <v>20.51</v>
+        <v>35.77</v>
       </c>
       <c r="F7">
-        <v>225.65</v>
+        <v>143.1</v>
       </c>
       <c r="G7">
-        <v>60</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Clinical Assistant</t>
+          <t>Community Mental Health Nurse</t>
         </is>
       </c>
       <c r="B8">
-        <v>551.86</v>
+        <v>2407.09</v>
       </c>
       <c r="C8">
-        <v>2.45</v>
+        <v>59.3</v>
       </c>
       <c r="D8">
-        <v>3.73</v>
+        <v>104.19</v>
       </c>
       <c r="E8">
-        <v>0.48</v>
+        <v>13.38</v>
       </c>
       <c r="F8">
-        <v>24.25</v>
+        <v>375.72</v>
       </c>
       <c r="G8">
-        <v>146</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Clinical Psychologist</t>
+          <t>Community Nurse</t>
         </is>
       </c>
       <c r="B9">
-        <v>572</v>
+        <v>294526.59</v>
       </c>
       <c r="C9">
-        <v>71.55</v>
+        <v>51.55</v>
       </c>
       <c r="D9">
-        <v>50.59</v>
+        <v>113.8</v>
       </c>
       <c r="E9">
-        <v>35.77</v>
+        <v>9.6</v>
       </c>
       <c r="F9">
-        <v>143.1</v>
+        <v>3110.69</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>3742</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Community Mental Health Nurse</t>
+          <t>Community Practitioner</t>
         </is>
       </c>
       <c r="B10">
-        <v>2487.32</v>
+        <v>1818054</v>
       </c>
       <c r="C10">
-        <v>61.27</v>
+        <v>123.54</v>
       </c>
       <c r="D10">
-        <v>104.3</v>
+        <v>229.39</v>
       </c>
       <c r="E10">
-        <v>13.38</v>
+        <v>21.01</v>
       </c>
       <c r="F10">
-        <v>375.72</v>
+        <v>7830.88</v>
       </c>
       <c r="G10">
-        <v>29</v>
+        <v>9496</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Community Nurse</t>
+          <t>Consultant</t>
         </is>
       </c>
       <c r="B11">
-        <v>359006.47</v>
+        <v>101031.48</v>
       </c>
       <c r="C11">
-        <v>62.84</v>
+        <v>141.51</v>
       </c>
       <c r="D11">
-        <v>153.16</v>
+        <v>291.97</v>
       </c>
       <c r="E11">
-        <v>9.6</v>
+        <v>24.71</v>
       </c>
       <c r="F11">
-        <v>3505.7</v>
+        <v>2254.51</v>
       </c>
       <c r="G11">
-        <v>3742</v>
+        <v>465</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Community Practitioner</t>
+          <t>Counsellor</t>
         </is>
       </c>
       <c r="B12">
-        <v>2075682</v>
+        <v>5248</v>
       </c>
       <c r="C12">
-        <v>141.05</v>
+        <v>108.97</v>
       </c>
       <c r="D12">
-        <v>278.65</v>
+        <v>131.43</v>
       </c>
       <c r="E12">
-        <v>21.01</v>
+        <v>20.51</v>
       </c>
       <c r="F12">
-        <v>8312.780000000001</v>
+        <v>615.42</v>
       </c>
       <c r="G12">
-        <v>9496</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Consultant</t>
+          <t>Dietitian</t>
         </is>
       </c>
       <c r="B13">
-        <v>110216.16</v>
+        <v>3081</v>
       </c>
       <c r="C13">
-        <v>154.38</v>
+        <v>33.95</v>
       </c>
       <c r="D13">
-        <v>343.03</v>
+        <v>56.83</v>
       </c>
       <c r="E13">
-        <v>24.71</v>
+        <v>19.51</v>
       </c>
       <c r="F13">
-        <v>2686.22</v>
+        <v>344.08</v>
       </c>
       <c r="G13">
-        <v>465</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Counsellor</t>
+          <t>GP Registrar</t>
         </is>
       </c>
       <c r="B14">
-        <v>6232</v>
+        <v>588658.98</v>
       </c>
       <c r="C14">
-        <v>129.41</v>
+        <v>91.3</v>
       </c>
       <c r="D14">
-        <v>172.33</v>
+        <v>185.88</v>
       </c>
       <c r="E14">
-        <v>20.51</v>
+        <v>24.71</v>
       </c>
       <c r="F14">
-        <v>800.05</v>
+        <v>3519.23</v>
       </c>
       <c r="G14">
-        <v>28</v>
+        <v>4204</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dietitian</t>
+          <t>General Medical Practitioner</t>
         </is>
       </c>
       <c r="B15">
-        <v>3159</v>
+        <v>12767202</v>
       </c>
       <c r="C15">
-        <v>34.81</v>
+        <v>440.9</v>
       </c>
       <c r="D15">
-        <v>67.83</v>
+        <v>512.78</v>
       </c>
       <c r="E15">
-        <v>19.51</v>
+        <v>21.01</v>
       </c>
       <c r="F15">
-        <v>347.43</v>
+        <v>6976.78</v>
       </c>
       <c r="G15">
-        <v>55</v>
+        <v>21488</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GP Registrar</t>
+          <t>Health Care Support Worker</t>
         </is>
       </c>
       <c r="B16">
-        <v>708553.62</v>
+        <v>726727.99</v>
       </c>
       <c r="C16">
-        <v>109.9</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="D16">
-        <v>252.96</v>
+        <v>186.01</v>
       </c>
       <c r="E16">
-        <v>24.71</v>
+        <v>9.6</v>
       </c>
       <c r="F16">
-        <v>5718.75</v>
+        <v>2164.59</v>
       </c>
       <c r="G16">
-        <v>4204</v>
+        <v>5023</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>General Medical Practitioner</t>
+          <t>Locum GP</t>
         </is>
       </c>
       <c r="B17">
-        <v>16849224</v>
+        <v>235295.7</v>
       </c>
       <c r="C17">
-        <v>581.86</v>
+        <v>120.15</v>
       </c>
       <c r="D17">
-        <v>746.2</v>
+        <v>256.23</v>
       </c>
       <c r="E17">
-        <v>21.01</v>
+        <v>24.71</v>
       </c>
       <c r="F17">
-        <v>10496.13</v>
+        <v>3435.44</v>
       </c>
       <c r="G17">
-        <v>21488</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Health Care Support Worker</t>
+          <t>Medical Technical Officer - Pharmacy</t>
         </is>
       </c>
       <c r="B18">
-        <v>888973.88</v>
+        <v>5022</v>
       </c>
       <c r="C18">
-        <v>120.62</v>
+        <v>12.64</v>
       </c>
       <c r="D18">
-        <v>265.76</v>
+        <v>21.39</v>
       </c>
       <c r="E18">
-        <v>9.6</v>
+        <v>3</v>
       </c>
       <c r="F18">
-        <v>3795.88</v>
+        <v>141.39</v>
       </c>
       <c r="G18">
-        <v>5023</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Healthcare Assistant</t>
+          <t>Midwife</t>
         </is>
       </c>
       <c r="B19">
-        <v>27772.75</v>
+        <v>95.16</v>
       </c>
       <c r="C19">
-        <v>2.47</v>
+        <v>15.87</v>
       </c>
       <c r="D19">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>0.48</v>
+        <v>15.87</v>
       </c>
       <c r="F19">
-        <v>80.42</v>
+        <v>15.87</v>
       </c>
       <c r="G19">
-        <v>7339</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Locum GP</t>
+          <t>Modern Matron</t>
         </is>
       </c>
       <c r="B20">
-        <v>297514.5</v>
+        <v>7814.32</v>
       </c>
       <c r="C20">
-        <v>151.92</v>
+        <v>134.3</v>
       </c>
       <c r="D20">
-        <v>393.15</v>
+        <v>234.46</v>
       </c>
       <c r="E20">
-        <v>24.71</v>
+        <v>18.44</v>
       </c>
       <c r="F20">
-        <v>8159.16</v>
+        <v>1187.92</v>
       </c>
       <c r="G20">
-        <v>1302</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Medical Technical Officer - Pharmacy</t>
+          <t>Nurse Consultant</t>
         </is>
       </c>
       <c r="B21">
-        <v>5238</v>
+        <v>58238.8</v>
       </c>
       <c r="C21">
-        <v>13.18</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="D21">
-        <v>22.69</v>
+        <v>201.2</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>18.44</v>
       </c>
       <c r="F21">
-        <v>141.39</v>
+        <v>2839.88</v>
       </c>
       <c r="G21">
-        <v>263</v>
+        <v>468</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Midwife</t>
+          <t>Other Community Health Service</t>
         </is>
       </c>
       <c r="B22">
-        <v>95.16</v>
+        <v>10594.48</v>
       </c>
       <c r="C22">
-        <v>15.87</v>
+        <v>61.63</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>109.34</v>
       </c>
       <c r="E22">
         <v>15.87</v>
       </c>
       <c r="F22">
-        <v>15.87</v>
+        <v>731.14</v>
       </c>
       <c r="G22">
-        <v>3</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Modern Matron</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="B23">
-        <v>8256.639999999999</v>
+        <v>5486</v>
       </c>
       <c r="C23">
-        <v>141.9</v>
+        <v>35.69</v>
       </c>
       <c r="D23">
-        <v>247.18</v>
+        <v>84.93000000000001</v>
       </c>
       <c r="E23">
-        <v>18.44</v>
+        <v>13.01</v>
       </c>
       <c r="F23">
-        <v>1187.92</v>
+        <v>575.55</v>
       </c>
       <c r="G23">
-        <v>42</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nurse Consultant</t>
+          <t>Paramedic Specialist Practitioner</t>
         </is>
       </c>
       <c r="B24">
-        <v>70623.75999999999</v>
+        <v>5642</v>
       </c>
       <c r="C24">
-        <v>95.72</v>
+        <v>40.42</v>
       </c>
       <c r="D24">
-        <v>236.23</v>
+        <v>65.59</v>
       </c>
       <c r="E24">
-        <v>18.44</v>
+        <v>13.01</v>
       </c>
       <c r="F24">
-        <v>2839.88</v>
+        <v>336.76</v>
       </c>
       <c r="G24">
-        <v>468</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nurse Manager</t>
+          <t>Physiotherapist</t>
         </is>
       </c>
       <c r="B25">
-        <v>6037.51</v>
+        <v>19434</v>
       </c>
       <c r="C25">
-        <v>6.21</v>
+        <v>70.27</v>
       </c>
       <c r="D25">
-        <v>14.97</v>
+        <v>115.1</v>
       </c>
       <c r="E25">
-        <v>1.12</v>
+        <v>20.51</v>
       </c>
       <c r="F25">
-        <v>190.29</v>
+        <v>981.98</v>
       </c>
       <c r="G25">
-        <v>616</v>
+        <v>178</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Other Community Health Service</t>
+          <t>Salaried General Practitioner</t>
         </is>
       </c>
       <c r="B26">
-        <v>11324.04</v>
+        <v>1107246</v>
       </c>
       <c r="C26">
-        <v>65.87</v>
+        <v>157.17</v>
       </c>
       <c r="D26">
-        <v>114.65</v>
+        <v>281.93</v>
       </c>
       <c r="E26">
-        <v>15.87</v>
+        <v>21.01</v>
       </c>
       <c r="F26">
-        <v>787.38</v>
+        <v>3409</v>
       </c>
       <c r="G26">
-        <v>121</v>
+        <v>4903</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Paramedic</t>
+          <t>Sessional GP</t>
         </is>
       </c>
       <c r="B27">
-        <v>6630</v>
+        <v>609398.58</v>
       </c>
       <c r="C27">
-        <v>43.14</v>
+        <v>120.62</v>
       </c>
       <c r="D27">
-        <v>105.76</v>
+        <v>234.71</v>
       </c>
       <c r="E27">
-        <v>13.01</v>
+        <v>24.71</v>
       </c>
       <c r="F27">
-        <v>575.55</v>
+        <v>2661.06</v>
       </c>
       <c r="G27">
-        <v>116</v>
+        <v>3311</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Paramedic Specialist Practitioner</t>
+          <t>Sister/Charge Nurse</t>
         </is>
       </c>
       <c r="B28">
-        <v>7046</v>
+        <v>104160</v>
       </c>
       <c r="C28">
-        <v>50.48</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="D28">
-        <v>127.39</v>
+        <v>194.11</v>
       </c>
       <c r="E28">
-        <v>13.01</v>
+        <v>21.01</v>
       </c>
       <c r="F28">
-        <v>1144.97</v>
+        <v>2206.51</v>
       </c>
       <c r="G28">
-        <v>110</v>
+        <v>702</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pharmacist</t>
+          <t>Social Worker</t>
         </is>
       </c>
       <c r="B29">
-        <v>9893.4</v>
+        <v>308</v>
       </c>
       <c r="C29">
-        <v>2.84</v>
+        <v>155.17</v>
       </c>
       <c r="D29">
-        <v>5.67</v>
+        <v>84.36</v>
       </c>
       <c r="E29">
-        <v>0.82</v>
+        <v>72.39</v>
       </c>
       <c r="F29">
-        <v>60.82</v>
+        <v>191.7</v>
       </c>
       <c r="G29">
-        <v>2412</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Phlebotomist</t>
+          <t>Specialist Nurse Practitioner</t>
         </is>
       </c>
       <c r="B30">
-        <v>12580.47</v>
+        <v>320543.72</v>
       </c>
       <c r="C30">
-        <v>4.32</v>
+        <v>61.43</v>
       </c>
       <c r="D30">
-        <v>7.57</v>
+        <v>114.86</v>
       </c>
       <c r="E30">
-        <v>0.95</v>
+        <v>13.38</v>
       </c>
       <c r="F30">
-        <v>92.54000000000001</v>
+        <v>1594.9</v>
       </c>
       <c r="G30">
-        <v>1865</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Physician Assistant</t>
+          <t>Specialist Practitioner</t>
         </is>
       </c>
       <c r="B31">
-        <v>20.93</v>
+        <v>3946.05</v>
       </c>
       <c r="C31">
-        <v>1.33</v>
+        <v>62.21</v>
       </c>
       <c r="D31">
-        <v>1.3</v>
+        <v>110.58</v>
       </c>
       <c r="E31">
-        <v>0.48</v>
+        <v>14.63</v>
       </c>
       <c r="F31">
-        <v>4.28</v>
+        <v>577.09</v>
       </c>
       <c r="G31">
-        <v>9</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Physiotherapist</t>
+          <t>Staff Nurse</t>
         </is>
       </c>
       <c r="B32">
-        <v>20213</v>
+        <v>296982</v>
       </c>
       <c r="C32">
-        <v>73.08</v>
+        <v>103.96</v>
       </c>
       <c r="D32">
-        <v>117.04</v>
+        <v>244.82</v>
       </c>
       <c r="E32">
-        <v>20.51</v>
+        <v>21.01</v>
       </c>
       <c r="F32">
-        <v>981.98</v>
+        <v>6136.2</v>
       </c>
       <c r="G32">
-        <v>178</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Radiographer</t>
+          <t>Therapist</t>
         </is>
       </c>
       <c r="B33">
-        <v>59.84</v>
+        <v>2703</v>
       </c>
       <c r="C33">
-        <v>4.84</v>
+        <v>178.95</v>
       </c>
       <c r="D33">
-        <v>3.41</v>
+        <v>270.76</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>26.52</v>
       </c>
       <c r="F33">
-        <v>10.98</v>
+        <v>1032.44</v>
       </c>
       <c r="G33">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Salaried General Practitioner</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>1423044</v>
-      </c>
-      <c r="C34">
-        <v>202</v>
-      </c>
-      <c r="D34">
-        <v>400.38</v>
-      </c>
-      <c r="E34">
-        <v>21.01</v>
-      </c>
-      <c r="F34">
-        <v>6008.36</v>
-      </c>
-      <c r="G34">
-        <v>4903</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Sessional GP</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>756550.98</v>
-      </c>
-      <c r="C35">
-        <v>149.75</v>
-      </c>
-      <c r="D35">
-        <v>310.58</v>
-      </c>
-      <c r="E35">
-        <v>24.71</v>
-      </c>
-      <c r="F35">
-        <v>3755.45</v>
-      </c>
-      <c r="G35">
-        <v>3311</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Sister/Charge Nurse</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>124530</v>
-      </c>
-      <c r="C36">
-        <v>112.68</v>
-      </c>
-      <c r="D36">
-        <v>232</v>
-      </c>
-      <c r="E36">
-        <v>21.01</v>
-      </c>
-      <c r="F36">
-        <v>2521.73</v>
-      </c>
-      <c r="G36">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Social Worker</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>396</v>
-      </c>
-      <c r="C37">
-        <v>199.5</v>
-      </c>
-      <c r="D37">
-        <v>129.55</v>
-      </c>
-      <c r="E37">
-        <v>72.39</v>
-      </c>
-      <c r="F37">
-        <v>255.6</v>
-      </c>
-      <c r="G37">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Specialist Nurse Practitioner</t>
-        </is>
-      </c>
-      <c r="B38">
-        <v>394895.95</v>
-      </c>
-      <c r="C38">
-        <v>75.67</v>
-      </c>
-      <c r="D38">
-        <v>150.4</v>
-      </c>
-      <c r="E38">
-        <v>13.38</v>
-      </c>
-      <c r="F38">
-        <v>2744.94</v>
-      </c>
-      <c r="G38">
-        <v>3450</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Specialist Practitioner</t>
-        </is>
-      </c>
-      <c r="B39">
-        <v>4092.2</v>
-      </c>
-      <c r="C39">
-        <v>64.51000000000001</v>
-      </c>
-      <c r="D39">
-        <v>109.93</v>
-      </c>
-      <c r="E39">
-        <v>14.63</v>
-      </c>
-      <c r="F39">
-        <v>577.09</v>
-      </c>
-      <c r="G39">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Staff Nurse</t>
-        </is>
-      </c>
-      <c r="B40">
-        <v>348012</v>
-      </c>
-      <c r="C40">
-        <v>121.82</v>
-      </c>
-      <c r="D40">
-        <v>293.43</v>
-      </c>
-      <c r="E40">
-        <v>21.01</v>
-      </c>
-      <c r="F40">
-        <v>6477.1</v>
-      </c>
-      <c r="G40">
-        <v>1845</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Therapist</t>
-        </is>
-      </c>
-      <c r="B41">
-        <v>2703</v>
-      </c>
-      <c r="C41">
-        <v>178.95</v>
-      </c>
-      <c r="D41">
-        <v>270.76</v>
-      </c>
-      <c r="E41">
-        <v>26.52</v>
-      </c>
-      <c r="F41">
-        <v>1032.44</v>
-      </c>
-      <c r="G41">
         <v>13</v>
       </c>
     </row>
@@ -1401,7 +1201,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1453,19 +1253,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>10113.58</v>
+        <v>7804.41</v>
       </c>
       <c r="C2">
-        <v>83.84</v>
+        <v>64.7</v>
       </c>
       <c r="D2">
-        <v>119.78</v>
+        <v>92.09</v>
       </c>
       <c r="E2">
         <v>14.63</v>
       </c>
       <c r="F2">
-        <v>628.88</v>
+        <v>490.86</v>
       </c>
       <c r="G2">
         <v>81</v>
@@ -1477,26 +1277,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Associate Practitioner - General Practitioner</t>
         </is>
       </c>
       <c r="B3">
-        <v>100.55</v>
+        <v>89124</v>
       </c>
       <c r="C3">
-        <v>1.8</v>
+        <v>133.47</v>
       </c>
       <c r="D3">
-        <v>12.28</v>
+        <v>261.88</v>
       </c>
       <c r="E3">
-        <v>0.64</v>
+        <v>21.01</v>
       </c>
       <c r="F3">
-        <v>72.63</v>
+        <v>3334.89</v>
       </c>
       <c r="G3">
-        <v>35</v>
+        <v>452</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1505,26 +1305,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Assistant Practitioner</t>
+          <t>Associate Practitioner - Nurse</t>
         </is>
       </c>
       <c r="B4">
-        <v>644.02</v>
+        <v>37432.5</v>
       </c>
       <c r="C4">
-        <v>3.08</v>
+        <v>38.71</v>
       </c>
       <c r="D4">
-        <v>6.02</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="E4">
-        <v>0.55</v>
+        <v>9.6</v>
       </c>
       <c r="F4">
-        <v>34.99</v>
+        <v>855.05</v>
       </c>
       <c r="G4">
-        <v>134</v>
+        <v>627</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1533,26 +1333,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate Practitioner - General Practitioner</t>
+          <t>Associate Specialist</t>
         </is>
       </c>
       <c r="B5">
-        <v>125832</v>
+        <v>5612.16</v>
       </c>
       <c r="C5">
-        <v>188.44</v>
+        <v>61.97</v>
       </c>
       <c r="D5">
-        <v>451.05</v>
+        <v>153.98</v>
       </c>
       <c r="E5">
-        <v>21.01</v>
+        <v>14.63</v>
       </c>
       <c r="F5">
-        <v>6336.29</v>
+        <v>1011.43</v>
       </c>
       <c r="G5">
-        <v>452</v>
+        <v>62</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1561,26 +1361,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Associate Practitioner - Nurse</t>
+          <t>Chiropodist/Podiatrist</t>
         </is>
       </c>
       <c r="B6">
-        <v>47164.95</v>
+        <v>4551</v>
       </c>
       <c r="C6">
-        <v>48.78</v>
+        <v>44.34</v>
       </c>
       <c r="D6">
-        <v>106.87</v>
+        <v>48.09</v>
       </c>
       <c r="E6">
-        <v>9.6</v>
+        <v>20.51</v>
       </c>
       <c r="F6">
-        <v>1090.66</v>
+        <v>225.65</v>
       </c>
       <c r="G6">
-        <v>627</v>
+        <v>60</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1589,26 +1389,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Associate Specialist</t>
+          <t>Clinical Psychologist</t>
         </is>
       </c>
       <c r="B7">
-        <v>5962.92</v>
+        <v>572</v>
       </c>
       <c r="C7">
-        <v>65.84</v>
+        <v>71.55</v>
       </c>
       <c r="D7">
-        <v>168.48</v>
+        <v>50.59</v>
       </c>
       <c r="E7">
-        <v>14.63</v>
+        <v>35.77</v>
       </c>
       <c r="F7">
-        <v>1123.82</v>
+        <v>143.1</v>
       </c>
       <c r="G7">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1617,26 +1417,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Chiropodist/Podiatrist</t>
+          <t>Community Mental Health Nurse</t>
         </is>
       </c>
       <c r="B8">
-        <v>4879</v>
+        <v>2407.09</v>
       </c>
       <c r="C8">
-        <v>47.53</v>
+        <v>59.3</v>
       </c>
       <c r="D8">
-        <v>48.22</v>
+        <v>104.19</v>
       </c>
       <c r="E8">
-        <v>20.51</v>
+        <v>13.38</v>
       </c>
       <c r="F8">
-        <v>225.65</v>
+        <v>375.72</v>
       </c>
       <c r="G8">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1645,54 +1445,54 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Clerical Worker</t>
+          <t>Community Nurse</t>
         </is>
       </c>
       <c r="B9">
-        <v>67247.09</v>
+        <v>294526.59</v>
       </c>
       <c r="C9">
-        <v>5.8</v>
+        <v>51.55</v>
       </c>
       <c r="D9">
-        <v>13.47</v>
+        <v>113.8</v>
       </c>
       <c r="E9">
-        <v>0.64</v>
+        <v>9.6</v>
       </c>
       <c r="F9">
-        <v>415.93</v>
+        <v>3110.69</v>
       </c>
       <c r="G9">
-        <v>8053</v>
+        <v>3742</v>
       </c>
       <c r="H9">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Clinical Assistant</t>
+          <t>Community Practitioner</t>
         </is>
       </c>
       <c r="B10">
-        <v>551.86</v>
+        <v>1818054</v>
       </c>
       <c r="C10">
-        <v>2.45</v>
+        <v>123.54</v>
       </c>
       <c r="D10">
-        <v>3.73</v>
+        <v>229.39</v>
       </c>
       <c r="E10">
-        <v>0.48</v>
+        <v>21.01</v>
       </c>
       <c r="F10">
-        <v>24.25</v>
+        <v>7830.88</v>
       </c>
       <c r="G10">
-        <v>146</v>
+        <v>9496</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1701,54 +1501,54 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Clinical Coder</t>
+          <t>Consultant</t>
         </is>
       </c>
       <c r="B11">
-        <v>8808.43</v>
+        <v>101031.48</v>
       </c>
       <c r="C11">
-        <v>6.9</v>
+        <v>141.51</v>
       </c>
       <c r="D11">
-        <v>15.1</v>
+        <v>291.97</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>24.71</v>
       </c>
       <c r="F11">
-        <v>154.12</v>
+        <v>2254.51</v>
       </c>
       <c r="G11">
-        <v>911</v>
+        <v>465</v>
       </c>
       <c r="H11">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Clinical Psychologist</t>
+          <t>Counsellor</t>
         </is>
       </c>
       <c r="B12">
-        <v>572</v>
+        <v>5248</v>
       </c>
       <c r="C12">
-        <v>71.55</v>
+        <v>108.97</v>
       </c>
       <c r="D12">
-        <v>50.59</v>
+        <v>131.43</v>
       </c>
       <c r="E12">
-        <v>35.77</v>
+        <v>20.51</v>
       </c>
       <c r="F12">
-        <v>143.1</v>
+        <v>615.42</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1757,54 +1557,54 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Community Administrator</t>
+          <t>Dietitian</t>
         </is>
       </c>
       <c r="B13">
-        <v>32697.64</v>
+        <v>3081</v>
       </c>
       <c r="C13">
-        <v>7.86</v>
+        <v>33.95</v>
       </c>
       <c r="D13">
-        <v>23.24</v>
+        <v>56.83</v>
       </c>
       <c r="E13">
-        <v>0.64</v>
+        <v>19.51</v>
       </c>
       <c r="F13">
-        <v>939.76</v>
+        <v>344.08</v>
       </c>
       <c r="G13">
-        <v>2828</v>
+        <v>55</v>
       </c>
       <c r="H13">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Community Mental Health Nurse</t>
+          <t>GP Registrar</t>
         </is>
       </c>
       <c r="B14">
-        <v>2487.32</v>
+        <v>588658.98</v>
       </c>
       <c r="C14">
-        <v>61.27</v>
+        <v>91.3</v>
       </c>
       <c r="D14">
-        <v>104.3</v>
+        <v>185.88</v>
       </c>
       <c r="E14">
-        <v>13.38</v>
+        <v>24.71</v>
       </c>
       <c r="F14">
-        <v>375.72</v>
+        <v>3519.23</v>
       </c>
       <c r="G14">
-        <v>29</v>
+        <v>4204</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -1813,26 +1613,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Community Nurse</t>
+          <t>General Medical Practitioner</t>
         </is>
       </c>
       <c r="B15">
-        <v>359006.47</v>
+        <v>12767202</v>
       </c>
       <c r="C15">
-        <v>62.84</v>
+        <v>440.9</v>
       </c>
       <c r="D15">
-        <v>153.16</v>
+        <v>512.78</v>
       </c>
       <c r="E15">
-        <v>9.6</v>
+        <v>21.01</v>
       </c>
       <c r="F15">
-        <v>3505.7</v>
+        <v>6976.78</v>
       </c>
       <c r="G15">
-        <v>3742</v>
+        <v>21488</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -1841,26 +1641,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Community Practitioner</t>
+          <t>Health Care Support Worker</t>
         </is>
       </c>
       <c r="B16">
-        <v>2075682</v>
+        <v>726727.99</v>
       </c>
       <c r="C16">
-        <v>141.05</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="D16">
-        <v>278.65</v>
+        <v>186.01</v>
       </c>
       <c r="E16">
-        <v>21.01</v>
+        <v>9.6</v>
       </c>
       <c r="F16">
-        <v>8312.780000000001</v>
+        <v>2164.59</v>
       </c>
       <c r="G16">
-        <v>9496</v>
+        <v>5023</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -1869,26 +1669,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Consultant</t>
+          <t>Locum GP</t>
         </is>
       </c>
       <c r="B17">
-        <v>110216.16</v>
+        <v>235295.7</v>
       </c>
       <c r="C17">
-        <v>154.38</v>
+        <v>120.15</v>
       </c>
       <c r="D17">
-        <v>343.03</v>
+        <v>256.23</v>
       </c>
       <c r="E17">
         <v>24.71</v>
       </c>
       <c r="F17">
-        <v>2686.22</v>
+        <v>3435.44</v>
       </c>
       <c r="G17">
-        <v>465</v>
+        <v>1302</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -1897,26 +1697,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Counsellor</t>
+          <t>Medical Technical Officer - Pharmacy</t>
         </is>
       </c>
       <c r="B18">
-        <v>6232</v>
+        <v>5022</v>
       </c>
       <c r="C18">
-        <v>129.41</v>
+        <v>12.64</v>
       </c>
       <c r="D18">
-        <v>172.33</v>
+        <v>21.39</v>
       </c>
       <c r="E18">
-        <v>20.51</v>
+        <v>3</v>
       </c>
       <c r="F18">
-        <v>800.05</v>
+        <v>141.39</v>
       </c>
       <c r="G18">
-        <v>28</v>
+        <v>263</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -1925,138 +1725,138 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Desktop Support Administrator</t>
+          <t>Midwife</t>
         </is>
       </c>
       <c r="B19">
-        <v>31206</v>
+        <v>95.16</v>
       </c>
       <c r="C19">
-        <v>9.16</v>
+        <v>15.87</v>
       </c>
       <c r="D19">
-        <v>14.92</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>0.64</v>
+        <v>15.87</v>
       </c>
       <c r="F19">
-        <v>123.96</v>
+        <v>15.87</v>
       </c>
       <c r="G19">
-        <v>2486</v>
+        <v>3</v>
       </c>
       <c r="H19">
-        <v>68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Desktop Support Technician</t>
+          <t>Modern Matron</t>
         </is>
       </c>
       <c r="B20">
-        <v>1397.45</v>
+        <v>7814.32</v>
       </c>
       <c r="C20">
-        <v>10.13</v>
+        <v>134.3</v>
       </c>
       <c r="D20">
-        <v>14.38</v>
+        <v>234.46</v>
       </c>
       <c r="E20">
-        <v>0.64</v>
+        <v>18.44</v>
       </c>
       <c r="F20">
-        <v>66.41</v>
+        <v>1187.92</v>
       </c>
       <c r="G20">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dietitian</t>
+          <t>Not Clinically Relevant</t>
         </is>
       </c>
       <c r="B21">
-        <v>3159</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>34.81</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>67.83</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>19.51</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>347.43</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>55</v>
+        <v>22620</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>699</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dispenser</t>
+          <t>Nurse Consultant</t>
         </is>
       </c>
       <c r="B22">
-        <v>5486.23</v>
+        <v>58238.8</v>
       </c>
       <c r="C22">
-        <v>4.01</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="D22">
-        <v>8.550000000000001</v>
+        <v>201.2</v>
       </c>
       <c r="E22">
-        <v>0.48</v>
+        <v>18.44</v>
       </c>
       <c r="F22">
-        <v>127.14</v>
+        <v>2839.88</v>
       </c>
       <c r="G22">
-        <v>903</v>
+        <v>468</v>
       </c>
       <c r="H22">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GP Registrar</t>
+          <t>Other Community Health Service</t>
         </is>
       </c>
       <c r="B23">
-        <v>708553.62</v>
+        <v>10594.48</v>
       </c>
       <c r="C23">
-        <v>109.9</v>
+        <v>61.63</v>
       </c>
       <c r="D23">
-        <v>252.96</v>
+        <v>109.34</v>
       </c>
       <c r="E23">
-        <v>24.71</v>
+        <v>15.87</v>
       </c>
       <c r="F23">
-        <v>5718.75</v>
+        <v>731.14</v>
       </c>
       <c r="G23">
-        <v>4204</v>
+        <v>121</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -2065,26 +1865,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>General Medical Practitioner</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="B24">
-        <v>16849224</v>
+        <v>5486</v>
       </c>
       <c r="C24">
-        <v>581.86</v>
+        <v>35.69</v>
       </c>
       <c r="D24">
-        <v>746.2</v>
+        <v>84.93000000000001</v>
       </c>
       <c r="E24">
-        <v>21.01</v>
+        <v>13.01</v>
       </c>
       <c r="F24">
-        <v>10496.13</v>
+        <v>575.55</v>
       </c>
       <c r="G24">
-        <v>21488</v>
+        <v>116</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -2093,26 +1893,26 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Health Care Support Worker</t>
+          <t>Paramedic Specialist Practitioner</t>
         </is>
       </c>
       <c r="B25">
-        <v>888973.88</v>
+        <v>5642</v>
       </c>
       <c r="C25">
-        <v>120.62</v>
+        <v>40.42</v>
       </c>
       <c r="D25">
-        <v>265.76</v>
+        <v>65.59</v>
       </c>
       <c r="E25">
-        <v>9.6</v>
+        <v>13.01</v>
       </c>
       <c r="F25">
-        <v>3795.88</v>
+        <v>336.76</v>
       </c>
       <c r="G25">
-        <v>5023</v>
+        <v>110</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -2121,54 +1921,54 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Health Records Administrator</t>
+          <t>Physiotherapist</t>
         </is>
       </c>
       <c r="B26">
-        <v>688.55</v>
+        <v>19434</v>
       </c>
       <c r="C26">
-        <v>2.53</v>
+        <v>70.27</v>
       </c>
       <c r="D26">
-        <v>4.75</v>
+        <v>115.1</v>
       </c>
       <c r="E26">
-        <v>0.64</v>
+        <v>20.51</v>
       </c>
       <c r="F26">
-        <v>37.19</v>
+        <v>981.98</v>
       </c>
       <c r="G26">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H26">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Healthcare Assistant</t>
+          <t>Salaried General Practitioner</t>
         </is>
       </c>
       <c r="B27">
-        <v>27772.75</v>
+        <v>1107246</v>
       </c>
       <c r="C27">
-        <v>2.47</v>
+        <v>157.17</v>
       </c>
       <c r="D27">
-        <v>4.39</v>
+        <v>281.93</v>
       </c>
       <c r="E27">
-        <v>0.48</v>
+        <v>21.01</v>
       </c>
       <c r="F27">
-        <v>80.42</v>
+        <v>3409</v>
       </c>
       <c r="G27">
-        <v>7339</v>
+        <v>4903</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -2177,54 +1977,54 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Helpdesk Administrator</t>
+          <t>Sessional GP</t>
         </is>
       </c>
       <c r="B28">
-        <v>1559.09</v>
+        <v>609398.58</v>
       </c>
       <c r="C28">
-        <v>6.54</v>
+        <v>120.62</v>
       </c>
       <c r="D28">
-        <v>17.21</v>
+        <v>234.71</v>
       </c>
       <c r="E28">
-        <v>0.64</v>
+        <v>24.71</v>
       </c>
       <c r="F28">
-        <v>147.4</v>
+        <v>2661.06</v>
       </c>
       <c r="G28">
-        <v>165</v>
+        <v>3311</v>
       </c>
       <c r="H28">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Locum GP</t>
+          <t>Sister/Charge Nurse</t>
         </is>
       </c>
       <c r="B29">
-        <v>297514.5</v>
+        <v>104160</v>
       </c>
       <c r="C29">
-        <v>151.92</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="D29">
-        <v>393.15</v>
+        <v>194.11</v>
       </c>
       <c r="E29">
-        <v>24.71</v>
+        <v>21.01</v>
       </c>
       <c r="F29">
-        <v>8159.16</v>
+        <v>2206.51</v>
       </c>
       <c r="G29">
-        <v>1302</v>
+        <v>702</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -2233,868 +2033,140 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Social Worker</t>
         </is>
       </c>
       <c r="B30">
-        <v>224965.26</v>
+        <v>308</v>
       </c>
       <c r="C30">
-        <v>14.51</v>
+        <v>155.17</v>
       </c>
       <c r="D30">
-        <v>29.02</v>
+        <v>84.36</v>
       </c>
       <c r="E30">
-        <v>1.32</v>
+        <v>72.39</v>
       </c>
       <c r="F30">
-        <v>630.48</v>
+        <v>191.7</v>
       </c>
       <c r="G30">
-        <v>11066</v>
+        <v>2</v>
       </c>
       <c r="H30">
-        <v>212</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Medical Records Clerk</t>
+          <t>Specialist Nurse Practitioner</t>
         </is>
       </c>
       <c r="B31">
-        <v>1286.73</v>
+        <v>320543.72</v>
       </c>
       <c r="C31">
-        <v>4.58</v>
+        <v>61.43</v>
       </c>
       <c r="D31">
-        <v>9.31</v>
+        <v>114.86</v>
       </c>
       <c r="E31">
-        <v>0.64</v>
+        <v>13.38</v>
       </c>
       <c r="F31">
-        <v>63.87</v>
+        <v>1594.9</v>
       </c>
       <c r="G31">
-        <v>195</v>
+        <v>3450</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Medical Secretary</t>
+          <t>Specialist Practitioner</t>
         </is>
       </c>
       <c r="B32">
-        <v>20134.55</v>
+        <v>3946.05</v>
       </c>
       <c r="C32">
-        <v>3.18</v>
+        <v>62.21</v>
       </c>
       <c r="D32">
-        <v>8.369999999999999</v>
+        <v>110.58</v>
       </c>
       <c r="E32">
-        <v>0.64</v>
+        <v>14.63</v>
       </c>
       <c r="F32">
-        <v>150.4</v>
+        <v>577.09</v>
       </c>
       <c r="G32">
-        <v>4259</v>
+        <v>41</v>
       </c>
       <c r="H32">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Medical Student</t>
+          <t>Staff Nurse</t>
         </is>
       </c>
       <c r="B33">
-        <v>265.15</v>
+        <v>296982</v>
       </c>
       <c r="C33">
-        <v>0.88</v>
+        <v>103.96</v>
       </c>
       <c r="D33">
-        <v>1.59</v>
+        <v>244.82</v>
       </c>
       <c r="E33">
-        <v>0.5600000000000001</v>
+        <v>21.01</v>
       </c>
       <c r="F33">
-        <v>12.82</v>
+        <v>6136.2</v>
       </c>
       <c r="G33">
-        <v>193</v>
+        <v>1845</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Medical Technical Officer - Pharmacy</t>
+          <t>Therapist</t>
         </is>
       </c>
       <c r="B34">
-        <v>5238</v>
+        <v>2703</v>
       </c>
       <c r="C34">
-        <v>13.18</v>
+        <v>178.95</v>
       </c>
       <c r="D34">
-        <v>22.69</v>
+        <v>270.76</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>26.52</v>
       </c>
       <c r="F34">
-        <v>141.39</v>
+        <v>1032.44</v>
       </c>
       <c r="G34">
-        <v>263</v>
+        <v>13</v>
       </c>
       <c r="H34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Midwife</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>95.16</v>
-      </c>
-      <c r="C35">
-        <v>15.87</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35">
-        <v>15.87</v>
-      </c>
-      <c r="F35">
-        <v>15.87</v>
-      </c>
-      <c r="G35">
-        <v>3</v>
-      </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Modern Matron</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>8256.639999999999</v>
-      </c>
-      <c r="C36">
-        <v>141.9</v>
-      </c>
-      <c r="D36">
-        <v>247.18</v>
-      </c>
-      <c r="E36">
-        <v>18.44</v>
-      </c>
-      <c r="F36">
-        <v>1187.92</v>
-      </c>
-      <c r="G36">
-        <v>42</v>
-      </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Nurse Consultant</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>70623.75999999999</v>
-      </c>
-      <c r="C37">
-        <v>95.72</v>
-      </c>
-      <c r="D37">
-        <v>236.23</v>
-      </c>
-      <c r="E37">
-        <v>18.44</v>
-      </c>
-      <c r="F37">
-        <v>2839.88</v>
-      </c>
-      <c r="G37">
-        <v>468</v>
-      </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Nurse Manager</t>
-        </is>
-      </c>
-      <c r="B38">
-        <v>6037.51</v>
-      </c>
-      <c r="C38">
-        <v>6.21</v>
-      </c>
-      <c r="D38">
-        <v>14.97</v>
-      </c>
-      <c r="E38">
-        <v>1.12</v>
-      </c>
-      <c r="F38">
-        <v>190.29</v>
-      </c>
-      <c r="G38">
-        <v>616</v>
-      </c>
-      <c r="H38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Other Community Health Service</t>
-        </is>
-      </c>
-      <c r="B39">
-        <v>11324.04</v>
-      </c>
-      <c r="C39">
-        <v>65.87</v>
-      </c>
-      <c r="D39">
-        <v>114.65</v>
-      </c>
-      <c r="E39">
-        <v>15.87</v>
-      </c>
-      <c r="F39">
-        <v>787.38</v>
-      </c>
-      <c r="G39">
-        <v>121</v>
-      </c>
-      <c r="H39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Paramedic</t>
-        </is>
-      </c>
-      <c r="B40">
-        <v>6630</v>
-      </c>
-      <c r="C40">
-        <v>43.14</v>
-      </c>
-      <c r="D40">
-        <v>105.76</v>
-      </c>
-      <c r="E40">
-        <v>13.01</v>
-      </c>
-      <c r="F40">
-        <v>575.55</v>
-      </c>
-      <c r="G40">
-        <v>116</v>
-      </c>
-      <c r="H40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Paramedic Specialist Practitioner</t>
-        </is>
-      </c>
-      <c r="B41">
-        <v>7046</v>
-      </c>
-      <c r="C41">
-        <v>50.48</v>
-      </c>
-      <c r="D41">
-        <v>127.39</v>
-      </c>
-      <c r="E41">
-        <v>13.01</v>
-      </c>
-      <c r="F41">
-        <v>1144.97</v>
-      </c>
-      <c r="G41">
-        <v>110</v>
-      </c>
-      <c r="H41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Pharmacist</t>
-        </is>
-      </c>
-      <c r="B42">
-        <v>9893.4</v>
-      </c>
-      <c r="C42">
-        <v>2.84</v>
-      </c>
-      <c r="D42">
-        <v>5.67</v>
-      </c>
-      <c r="E42">
-        <v>0.82</v>
-      </c>
-      <c r="F42">
-        <v>60.82</v>
-      </c>
-      <c r="G42">
-        <v>2412</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Phlebotomist</t>
-        </is>
-      </c>
-      <c r="B43">
-        <v>12580.47</v>
-      </c>
-      <c r="C43">
-        <v>4.32</v>
-      </c>
-      <c r="D43">
-        <v>7.57</v>
-      </c>
-      <c r="E43">
-        <v>0.95</v>
-      </c>
-      <c r="F43">
-        <v>92.54000000000001</v>
-      </c>
-      <c r="G43">
-        <v>1865</v>
-      </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Physician Assistant</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>20.93</v>
-      </c>
-      <c r="C44">
-        <v>1.33</v>
-      </c>
-      <c r="D44">
-        <v>1.3</v>
-      </c>
-      <c r="E44">
-        <v>0.48</v>
-      </c>
-      <c r="F44">
-        <v>4.28</v>
-      </c>
-      <c r="G44">
-        <v>9</v>
-      </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Physiotherapist</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>20213</v>
-      </c>
-      <c r="C45">
-        <v>73.08</v>
-      </c>
-      <c r="D45">
-        <v>117.04</v>
-      </c>
-      <c r="E45">
-        <v>20.51</v>
-      </c>
-      <c r="F45">
-        <v>981.98</v>
-      </c>
-      <c r="G45">
-        <v>178</v>
-      </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Radiographer</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>59.84</v>
-      </c>
-      <c r="C46">
-        <v>4.84</v>
-      </c>
-      <c r="D46">
-        <v>3.41</v>
-      </c>
-      <c r="E46">
-        <v>1</v>
-      </c>
-      <c r="F46">
-        <v>10.98</v>
-      </c>
-      <c r="G46">
-        <v>7</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Receptionist</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>129463.09</v>
-      </c>
-      <c r="C47">
-        <v>7.72</v>
-      </c>
-      <c r="D47">
-        <v>15.97</v>
-      </c>
-      <c r="E47">
-        <v>0.64</v>
-      </c>
-      <c r="F47">
-        <v>542.55</v>
-      </c>
-      <c r="G47">
-        <v>11764</v>
-      </c>
-      <c r="H47">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Salaried General Practitioner</t>
-        </is>
-      </c>
-      <c r="B48">
-        <v>1423044</v>
-      </c>
-      <c r="C48">
-        <v>202</v>
-      </c>
-      <c r="D48">
-        <v>400.38</v>
-      </c>
-      <c r="E48">
-        <v>21.01</v>
-      </c>
-      <c r="F48">
-        <v>6008.36</v>
-      </c>
-      <c r="G48">
-        <v>4903</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Secretary</t>
-        </is>
-      </c>
-      <c r="B49">
-        <v>17202.18</v>
-      </c>
-      <c r="C49">
-        <v>3.16</v>
-      </c>
-      <c r="D49">
-        <v>6.33</v>
-      </c>
-      <c r="E49">
-        <v>0.64</v>
-      </c>
-      <c r="F49">
-        <v>82.38</v>
-      </c>
-      <c r="G49">
-        <v>3619</v>
-      </c>
-      <c r="H49">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Senior Administrator</t>
-        </is>
-      </c>
-      <c r="B50">
-        <v>71282.37</v>
-      </c>
-      <c r="C50">
-        <v>14.68</v>
-      </c>
-      <c r="D50">
-        <v>35.85</v>
-      </c>
-      <c r="E50">
-        <v>1.92</v>
-      </c>
-      <c r="F50">
-        <v>1050.62</v>
-      </c>
-      <c r="G50">
-        <v>3355</v>
-      </c>
-      <c r="H50">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Senior Manager</t>
-        </is>
-      </c>
-      <c r="B51">
-        <v>15150.81</v>
-      </c>
-      <c r="C51">
-        <v>10.88</v>
-      </c>
-      <c r="D51">
-        <v>23.36</v>
-      </c>
-      <c r="E51">
-        <v>1.92</v>
-      </c>
-      <c r="F51">
-        <v>375.49</v>
-      </c>
-      <c r="G51">
-        <v>942</v>
-      </c>
-      <c r="H51">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Sessional GP</t>
-        </is>
-      </c>
-      <c r="B52">
-        <v>756550.98</v>
-      </c>
-      <c r="C52">
-        <v>149.75</v>
-      </c>
-      <c r="D52">
-        <v>310.58</v>
-      </c>
-      <c r="E52">
-        <v>24.71</v>
-      </c>
-      <c r="F52">
-        <v>3755.45</v>
-      </c>
-      <c r="G52">
-        <v>3311</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Sister/Charge Nurse</t>
-        </is>
-      </c>
-      <c r="B53">
-        <v>124530</v>
-      </c>
-      <c r="C53">
-        <v>112.68</v>
-      </c>
-      <c r="D53">
-        <v>232</v>
-      </c>
-      <c r="E53">
-        <v>21.01</v>
-      </c>
-      <c r="F53">
-        <v>2521.73</v>
-      </c>
-      <c r="G53">
-        <v>702</v>
-      </c>
-      <c r="H53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Social Worker</t>
-        </is>
-      </c>
-      <c r="B54">
-        <v>396</v>
-      </c>
-      <c r="C54">
-        <v>199.5</v>
-      </c>
-      <c r="D54">
-        <v>129.55</v>
-      </c>
-      <c r="E54">
-        <v>72.39</v>
-      </c>
-      <c r="F54">
-        <v>255.6</v>
-      </c>
-      <c r="G54">
-        <v>2</v>
-      </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Specialist Nurse Practitioner</t>
-        </is>
-      </c>
-      <c r="B55">
-        <v>394895.95</v>
-      </c>
-      <c r="C55">
-        <v>75.67</v>
-      </c>
-      <c r="D55">
-        <v>150.4</v>
-      </c>
-      <c r="E55">
-        <v>13.38</v>
-      </c>
-      <c r="F55">
-        <v>2744.94</v>
-      </c>
-      <c r="G55">
-        <v>3450</v>
-      </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Specialist Practitioner</t>
-        </is>
-      </c>
-      <c r="B56">
-        <v>4092.2</v>
-      </c>
-      <c r="C56">
-        <v>64.51000000000001</v>
-      </c>
-      <c r="D56">
-        <v>109.93</v>
-      </c>
-      <c r="E56">
-        <v>14.63</v>
-      </c>
-      <c r="F56">
-        <v>577.09</v>
-      </c>
-      <c r="G56">
-        <v>41</v>
-      </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Staff Nurse</t>
-        </is>
-      </c>
-      <c r="B57">
-        <v>348012</v>
-      </c>
-      <c r="C57">
-        <v>121.82</v>
-      </c>
-      <c r="D57">
-        <v>293.43</v>
-      </c>
-      <c r="E57">
-        <v>21.01</v>
-      </c>
-      <c r="F57">
-        <v>6477.1</v>
-      </c>
-      <c r="G57">
-        <v>1845</v>
-      </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>System Administrator</t>
-        </is>
-      </c>
-      <c r="B58">
-        <v>70680.91</v>
-      </c>
-      <c r="C58">
-        <v>9</v>
-      </c>
-      <c r="D58">
-        <v>15.17</v>
-      </c>
-      <c r="E58">
-        <v>0.64</v>
-      </c>
-      <c r="F58">
-        <v>172.66</v>
-      </c>
-      <c r="G58">
-        <v>5805</v>
-      </c>
-      <c r="H58">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>System Worker</t>
-        </is>
-      </c>
-      <c r="B59">
-        <v>3231.75</v>
-      </c>
-      <c r="C59">
-        <v>14.95</v>
-      </c>
-      <c r="D59">
-        <v>25.54</v>
-      </c>
-      <c r="E59">
-        <v>1.29</v>
-      </c>
-      <c r="F59">
-        <v>171.56</v>
-      </c>
-      <c r="G59">
-        <v>152</v>
-      </c>
-      <c r="H59">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Therapist</t>
-        </is>
-      </c>
-      <c r="B60">
-        <v>2703</v>
-      </c>
-      <c r="C60">
-        <v>178.95</v>
-      </c>
-      <c r="D60">
-        <v>270.76</v>
-      </c>
-      <c r="E60">
-        <v>26.52</v>
-      </c>
-      <c r="F60">
-        <v>1032.44</v>
-      </c>
-      <c r="G60">
-        <v>13</v>
-      </c>
-      <c r="H60">
         <v>0</v>
       </c>
     </row>
@@ -3152,22 +2224,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>20166409.08</v>
+        <v>17218949.7</v>
       </c>
       <c r="C2">
-        <v>684.2</v>
+        <v>582.42</v>
       </c>
       <c r="D2">
-        <v>827.66</v>
+        <v>627.09</v>
       </c>
       <c r="E2">
         <v>21.01</v>
       </c>
       <c r="F2">
-        <v>11071.84</v>
+        <v>9638.01</v>
       </c>
       <c r="G2">
-        <v>22067</v>
+        <v>22167</v>
       </c>
     </row>
     <row r="3">
@@ -3177,22 +2249,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>3439105.22</v>
+        <v>1120830.61</v>
       </c>
       <c r="C3">
-        <v>145.3</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="D3">
-        <v>306.7</v>
+        <v>186.65</v>
       </c>
       <c r="E3">
-        <v>1.12</v>
+        <v>9.6</v>
       </c>
       <c r="F3">
-        <v>9506.790000000001</v>
+        <v>6136.2</v>
       </c>
       <c r="G3">
-        <v>15734</v>
+        <v>9078</v>
       </c>
     </row>
     <row r="4">
@@ -3202,22 +2274,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>1206414.23</v>
+        <v>904178.12</v>
       </c>
       <c r="C4">
-        <v>60.78</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="D4">
-        <v>209.8</v>
+        <v>197.18</v>
       </c>
       <c r="E4">
-        <v>0.48</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>4172.33</v>
+        <v>2254.51</v>
       </c>
       <c r="G4">
-        <v>13580</v>
+        <v>6181</v>
       </c>
     </row>
   </sheetData>
@@ -3275,57 +2347,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>General Practitioner</t>
         </is>
       </c>
       <c r="B2">
-        <v>708663.28</v>
+        <v>17218949.7</v>
       </c>
       <c r="C2">
-        <v>24.23</v>
+        <v>582.42</v>
       </c>
       <c r="D2">
-        <v>42.81</v>
+        <v>627.09</v>
       </c>
       <c r="E2">
-        <v>0.48</v>
+        <v>21.01</v>
       </c>
       <c r="F2">
-        <v>1282.34</v>
+        <v>9638.01</v>
       </c>
       <c r="G2">
-        <v>22096</v>
+        <v>22167</v>
       </c>
       <c r="H2">
-        <v>545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Not Clinically Relevant</t>
         </is>
       </c>
       <c r="B3">
-        <v>20166409.08</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>684.2</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>827.66</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>21.01</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>11071.84</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>22067</v>
+        <v>22620</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>699</v>
       </c>
     </row>
     <row r="4">
@@ -3335,22 +2407,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>3439105.22</v>
+        <v>1120830.61</v>
       </c>
       <c r="C4">
-        <v>145.3</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="D4">
-        <v>306.7</v>
+        <v>186.65</v>
       </c>
       <c r="E4">
-        <v>1.12</v>
+        <v>9.6</v>
       </c>
       <c r="F4">
-        <v>9506.790000000001</v>
+        <v>6136.2</v>
       </c>
       <c r="G4">
-        <v>15734</v>
+        <v>9078</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -3363,22 +2435,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>1206414.23</v>
+        <v>904178.12</v>
       </c>
       <c r="C5">
-        <v>60.78</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="D5">
-        <v>209.8</v>
+        <v>197.18</v>
       </c>
       <c r="E5">
-        <v>0.48</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>4172.33</v>
+        <v>2254.51</v>
       </c>
       <c r="G5">
-        <v>13580</v>
+        <v>6181</v>
       </c>
       <c r="H5">
         <v>0</v>
